--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU53"/>
+  <dimension ref="A1:AU58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G48">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G49">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:45:00</t>
+          <t>2026-09-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -8906,151 +8906,966 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Zrinjski</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BSK Banja Luka</t>
+        </is>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53">
+        <v>0</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>0</v>
+      </c>
+      <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>-1</v>
+      </c>
+      <c r="AN53">
+        <v>-1</v>
+      </c>
+      <c r="AO53">
+        <v>-1</v>
+      </c>
+      <c r="AP53">
+        <v>-1</v>
+      </c>
+      <c r="AQ53">
+        <v>0</v>
+      </c>
+      <c r="AR53">
+        <v>0</v>
+      </c>
+      <c r="AS53">
+        <v>0</v>
+      </c>
+      <c r="AT53">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>2026-09-01 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sloga Doboj</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Čelik</t>
+        </is>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <v>0</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>0</v>
+      </c>
+      <c r="AK54">
+        <v>0</v>
+      </c>
+      <c r="AL54">
+        <v>0</v>
+      </c>
+      <c r="AM54">
+        <v>-1</v>
+      </c>
+      <c r="AN54">
+        <v>-1</v>
+      </c>
+      <c r="AO54">
+        <v>-1</v>
+      </c>
+      <c r="AP54">
+        <v>-1</v>
+      </c>
+      <c r="AQ54">
+        <v>0</v>
+      </c>
+      <c r="AR54">
+        <v>0</v>
+      </c>
+      <c r="AS54">
+        <v>0</v>
+      </c>
+      <c r="AT54">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>2026-09-01 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Velež</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Radnik Bijeljina</t>
+        </is>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <v>0</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>0</v>
+      </c>
+      <c r="AK55">
+        <v>0</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>-1</v>
+      </c>
+      <c r="AN55">
+        <v>-1</v>
+      </c>
+      <c r="AO55">
+        <v>-1</v>
+      </c>
+      <c r="AP55">
+        <v>-1</v>
+      </c>
+      <c r="AQ55">
+        <v>0</v>
+      </c>
+      <c r="AR55">
+        <v>0</v>
+      </c>
+      <c r="AS55">
+        <v>0</v>
+      </c>
+      <c r="AT55">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>2026-09-01 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Široki Brijeg</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>0</v>
+      </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>-1</v>
+      </c>
+      <c r="AN56">
+        <v>-1</v>
+      </c>
+      <c r="AO56">
+        <v>-1</v>
+      </c>
+      <c r="AP56">
+        <v>-1</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>0</v>
+      </c>
+      <c r="AS56">
+        <v>0</v>
+      </c>
+      <c r="AT56">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>2026-09-01 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Borac Banja Luka</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Željezničar</t>
+        </is>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>0</v>
+      </c>
+      <c r="AK57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>-1</v>
+      </c>
+      <c r="AN57">
+        <v>-1</v>
+      </c>
+      <c r="AO57">
+        <v>-1</v>
+      </c>
+      <c r="AP57">
+        <v>-1</v>
+      </c>
+      <c r="AQ57">
+        <v>0</v>
+      </c>
+      <c r="AR57">
+        <v>0</v>
+      </c>
+      <c r="AS57">
+        <v>0</v>
+      </c>
+      <c r="AT57">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>2026-09-01 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>LDU Quito</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Mushuc Runa SC</t>
         </is>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>0</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53" t="inlineStr">
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>0</v>
-      </c>
-      <c r="P53">
-        <v>0</v>
-      </c>
-      <c r="Q53">
-        <v>0</v>
-      </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
-        <v>0</v>
-      </c>
-      <c r="T53">
-        <v>0</v>
-      </c>
-      <c r="U53">
-        <v>0</v>
-      </c>
-      <c r="V53">
-        <v>0</v>
-      </c>
-      <c r="W53">
-        <v>0</v>
-      </c>
-      <c r="X53">
-        <v>0</v>
-      </c>
-      <c r="Y53">
-        <v>0</v>
-      </c>
-      <c r="Z53">
-        <v>0</v>
-      </c>
-      <c r="AA53">
-        <v>0</v>
-      </c>
-      <c r="AB53">
-        <v>0</v>
-      </c>
-      <c r="AC53">
-        <v>0</v>
-      </c>
-      <c r="AD53">
-        <v>0</v>
-      </c>
-      <c r="AE53">
-        <v>0</v>
-      </c>
-      <c r="AF53">
-        <v>0</v>
-      </c>
-      <c r="AG53">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>0</v>
-      </c>
-      <c r="AK53">
-        <v>0</v>
-      </c>
-      <c r="AL53">
-        <v>0</v>
-      </c>
-      <c r="AM53">
-        <v>-1</v>
-      </c>
-      <c r="AN53">
-        <v>-1</v>
-      </c>
-      <c r="AO53">
-        <v>-1</v>
-      </c>
-      <c r="AP53">
-        <v>-1</v>
-      </c>
-      <c r="AQ53">
-        <v>0</v>
-      </c>
-      <c r="AR53">
-        <v>0</v>
-      </c>
-      <c r="AS53">
-        <v>0</v>
-      </c>
-      <c r="AT53">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <v>0</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>0</v>
+      </c>
+      <c r="AK58">
+        <v>0</v>
+      </c>
+      <c r="AL58">
+        <v>0</v>
+      </c>
+      <c r="AM58">
+        <v>-1</v>
+      </c>
+      <c r="AN58">
+        <v>-1</v>
+      </c>
+      <c r="AO58">
+        <v>-1</v>
+      </c>
+      <c r="AP58">
+        <v>-1</v>
+      </c>
+      <c r="AQ58">
+        <v>0</v>
+      </c>
+      <c r="AR58">
+        <v>0</v>
+      </c>
+      <c r="AS58">
+        <v>0</v>
+      </c>
+      <c r="AT58">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
         <is>
           <t>2026-09-01 21:00:00</t>
         </is>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G7">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G39">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G48">

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G21">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G35">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G40">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G48">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G57">

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G21">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G35">

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G35">

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G35">

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU58"/>
+  <dimension ref="A1:AU59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2707,27 +2707,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-01 14:15:00</t>
+          <t>2026-09-01 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G16">
@@ -3038,22 +3038,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G21">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:00:00</t>
+          <t>2026-09-01 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:30:00</t>
+          <t>2026-09-01 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:45:00</t>
+          <t>2026-09-01 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G48">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G49">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-01 16:00:00</t>
+          <t>2026-09-01 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G50">
@@ -8575,27 +8575,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-09-01 18:30:00</t>
+          <t>2026-09-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G52">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-09-01 19:30:00</t>
+          <t>2026-09-01 18:30:00</t>
         </is>
       </c>
     </row>
@@ -8901,27 +8901,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G53">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-09-01 21:00:00</t>
+          <t>2026-09-01 19:30:00</t>
         </is>
       </c>
     </row>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,151 +9721,314 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Široki Brijeg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Sarajevo</t>
+        </is>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <v>0</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>0</v>
+      </c>
+      <c r="AK58">
+        <v>0</v>
+      </c>
+      <c r="AL58">
+        <v>0</v>
+      </c>
+      <c r="AM58">
+        <v>-1</v>
+      </c>
+      <c r="AN58">
+        <v>-1</v>
+      </c>
+      <c r="AO58">
+        <v>-1</v>
+      </c>
+      <c r="AP58">
+        <v>-1</v>
+      </c>
+      <c r="AQ58">
+        <v>0</v>
+      </c>
+      <c r="AR58">
+        <v>0</v>
+      </c>
+      <c r="AS58">
+        <v>0</v>
+      </c>
+      <c r="AT58">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>2026-09-01 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>LDU Quito</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Mushuc Runa SC</t>
         </is>
       </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>0</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58" t="inlineStr">
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
-        <v>0</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
-        <v>0</v>
-      </c>
-      <c r="T58">
-        <v>0</v>
-      </c>
-      <c r="U58">
-        <v>0</v>
-      </c>
-      <c r="V58">
-        <v>0</v>
-      </c>
-      <c r="W58">
-        <v>0</v>
-      </c>
-      <c r="X58">
-        <v>0</v>
-      </c>
-      <c r="Y58">
-        <v>0</v>
-      </c>
-      <c r="Z58">
-        <v>0</v>
-      </c>
-      <c r="AA58">
-        <v>0</v>
-      </c>
-      <c r="AB58">
-        <v>0</v>
-      </c>
-      <c r="AC58">
-        <v>0</v>
-      </c>
-      <c r="AD58">
-        <v>0</v>
-      </c>
-      <c r="AE58">
-        <v>0</v>
-      </c>
-      <c r="AF58">
-        <v>0</v>
-      </c>
-      <c r="AG58">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>0</v>
-      </c>
-      <c r="AK58">
-        <v>0</v>
-      </c>
-      <c r="AL58">
-        <v>0</v>
-      </c>
-      <c r="AM58">
-        <v>-1</v>
-      </c>
-      <c r="AN58">
-        <v>-1</v>
-      </c>
-      <c r="AO58">
-        <v>-1</v>
-      </c>
-      <c r="AP58">
-        <v>-1</v>
-      </c>
-      <c r="AQ58">
-        <v>0</v>
-      </c>
-      <c r="AR58">
-        <v>0</v>
-      </c>
-      <c r="AS58">
-        <v>0</v>
-      </c>
-      <c r="AT58">
-        <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59">
+        <v>0</v>
+      </c>
+      <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>-1</v>
+      </c>
+      <c r="AN59">
+        <v>-1</v>
+      </c>
+      <c r="AO59">
+        <v>-1</v>
+      </c>
+      <c r="AP59">
+        <v>-1</v>
+      </c>
+      <c r="AQ59">
+        <v>0</v>
+      </c>
+      <c r="AR59">
+        <v>0</v>
+      </c>
+      <c r="AS59">
+        <v>0</v>
+      </c>
+      <c r="AT59">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
         <is>
           <t>2026-09-01 21:00:00</t>
         </is>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G49">

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G49">

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU59"/>
+  <dimension ref="A1:AU58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="G9">
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G10">
@@ -2060,22 +2060,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G12">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G13">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-01 14:00:00</t>
+          <t>2026-09-01 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G15">
@@ -2875,22 +2875,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3038,22 +3038,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G21">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-09-01 14:30:00</t>
+          <t>2026-09-01 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:00:00</t>
+          <t>2026-09-01 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:30:00</t>
+          <t>2026-09-01 15:45:00</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G48">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G49">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:45:00</t>
+          <t>2026-09-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G50">
@@ -8575,27 +8575,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-09-01 16:00:00</t>
+          <t>2026-09-01 18:30:00</t>
         </is>
       </c>
     </row>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G52">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-09-01 18:30:00</t>
+          <t>2026-09-01 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8901,27 +8901,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G53">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-09-01 19:30:00</t>
+          <t>2026-09-01 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G58">
@@ -9866,169 +9866,6 @@
         <v>0</v>
       </c>
       <c r="AU58" t="inlineStr">
-        <is>
-          <t>2026-09-01 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Mushuc Runa SC</t>
-        </is>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>0</v>
-      </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
-        <v>0</v>
-      </c>
-      <c r="T59">
-        <v>0</v>
-      </c>
-      <c r="U59">
-        <v>0</v>
-      </c>
-      <c r="V59">
-        <v>0</v>
-      </c>
-      <c r="W59">
-        <v>0</v>
-      </c>
-      <c r="X59">
-        <v>0</v>
-      </c>
-      <c r="Y59">
-        <v>0</v>
-      </c>
-      <c r="Z59">
-        <v>0</v>
-      </c>
-      <c r="AA59">
-        <v>0</v>
-      </c>
-      <c r="AB59">
-        <v>0</v>
-      </c>
-      <c r="AC59">
-        <v>0</v>
-      </c>
-      <c r="AD59">
-        <v>0</v>
-      </c>
-      <c r="AE59">
-        <v>0</v>
-      </c>
-      <c r="AF59">
-        <v>0</v>
-      </c>
-      <c r="AG59">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ59">
-        <v>0</v>
-      </c>
-      <c r="AK59">
-        <v>0</v>
-      </c>
-      <c r="AL59">
-        <v>0</v>
-      </c>
-      <c r="AM59">
-        <v>-1</v>
-      </c>
-      <c r="AN59">
-        <v>-1</v>
-      </c>
-      <c r="AO59">
-        <v>-1</v>
-      </c>
-      <c r="AP59">
-        <v>-1</v>
-      </c>
-      <c r="AQ59">
-        <v>0</v>
-      </c>
-      <c r="AR59">
-        <v>0</v>
-      </c>
-      <c r="AS59">
-        <v>0</v>
-      </c>
-      <c r="AT59">
-        <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
         <is>
           <t>2026-09-01 21:00:00</t>
         </is>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -644,55 +644,55 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -1157,31 +1157,31 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2947,7 +2947,7 @@
         <v>1.36</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
         <v>1.01</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -1145,16 +1145,16 @@
         <v>2.45</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
         <v>1.36</v>
@@ -1175,7 +1175,7 @@
         <v>1.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
         <v>1.86</v>
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G48">

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G11">
@@ -2111,71 +2111,71 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S11">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T11">
+        <v>2.96</v>
+      </c>
+      <c r="U11">
+        <v>2.63</v>
+      </c>
+      <c r="V11">
+        <v>1.44</v>
+      </c>
+      <c r="W11">
+        <v>1.06</v>
+      </c>
+      <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>1.22</v>
+      </c>
+      <c r="Z11">
+        <v>3.55</v>
+      </c>
+      <c r="AA11">
+        <v>1.74</v>
+      </c>
+      <c r="AB11">
+        <v>1.98</v>
+      </c>
+      <c r="AC11">
         <v>2.78</v>
       </c>
-      <c r="U11">
-        <v>2.88</v>
-      </c>
-      <c r="V11">
-        <v>1.36</v>
-      </c>
-      <c r="W11">
+      <c r="AD11">
+        <v>1.34</v>
+      </c>
+      <c r="AE11">
+        <v>1.09</v>
+      </c>
+      <c r="AF11">
+        <v>1.79</v>
+      </c>
+      <c r="AG11">
+        <v>1.9</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.17</v>
+      </c>
+      <c r="AK11">
         <v>1.08</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
-        <v>1.24</v>
-      </c>
-      <c r="Z11">
-        <v>3.34</v>
-      </c>
-      <c r="AA11">
-        <v>1.82</v>
-      </c>
-      <c r="AB11">
-        <v>1.81</v>
-      </c>
-      <c r="AC11">
-        <v>3.05</v>
-      </c>
-      <c r="AD11">
-        <v>1.3</v>
-      </c>
-      <c r="AE11">
-        <v>1.06</v>
-      </c>
-      <c r="AF11">
-        <v>1.68</v>
-      </c>
-      <c r="AG11">
-        <v>2.04</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.26</v>
-      </c>
-      <c r="AK11">
-        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G12">
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="R12">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="U12">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
+        <v>1.08</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
+        <v>1.24</v>
+      </c>
+      <c r="Z12">
+        <v>3.34</v>
+      </c>
+      <c r="AA12">
+        <v>1.82</v>
+      </c>
+      <c r="AB12">
+        <v>1.81</v>
+      </c>
+      <c r="AC12">
+        <v>3.05</v>
+      </c>
+      <c r="AD12">
+        <v>1.3</v>
+      </c>
+      <c r="AE12">
         <v>1.06</v>
       </c>
-      <c r="X12">
-        <v>1.02</v>
-      </c>
-      <c r="Y12">
-        <v>1.22</v>
-      </c>
-      <c r="Z12">
-        <v>3.55</v>
-      </c>
-      <c r="AA12">
-        <v>1.74</v>
-      </c>
-      <c r="AB12">
-        <v>1.98</v>
-      </c>
-      <c r="AC12">
-        <v>2.78</v>
-      </c>
-      <c r="AD12">
-        <v>1.34</v>
-      </c>
-      <c r="AE12">
-        <v>1.09</v>
-      </c>
       <c r="AF12">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AG12">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G50">
@@ -8794,55 +8794,55 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G35">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G39">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G41">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G48">

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41">

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q2">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="R2">
         <v>2.04</v>
       </c>
       <c r="S2">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
         <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.04</v>
@@ -668,13 +668,13 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z2">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA2">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB2">
         <v>1.73</v>
@@ -689,10 +689,10 @@
         <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG2">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.26</v>
       </c>
       <c r="AK2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P4">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,61 +1124,61 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O5">
         <v>3.1</v>
       </c>
       <c r="P5">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q5">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="R5">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S5">
         <v>1.41</v>
       </c>
       <c r="T5">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="U5">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z5">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AB5">
         <v>1.58</v>
       </c>
       <c r="AC5">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="AD5">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE5">
         <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
         <v>1.78</v>
@@ -1197,7 +1197,7 @@
         <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G48">

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -1148,10 +1148,10 @@
         <v>3.2</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -2102,22 +2102,22 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q11">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="R11">
         <v>2.21</v>
       </c>
       <c r="S11">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
         <v>2.96</v>
@@ -2129,16 +2129,16 @@
         <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>3.55</v>
+        <v>3.78</v>
       </c>
       <c r="AA11">
         <v>1.74</v>
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q12">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
         <v>1.36</v>
       </c>
       <c r="T12">
+        <v>2.88</v>
+      </c>
+      <c r="U12">
         <v>2.78</v>
-      </c>
-      <c r="U12">
-        <v>2.88</v>
       </c>
       <c r="V12">
         <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2304,19 +2304,19 @@
         <v>3.34</v>
       </c>
       <c r="AA12">
+        <v>1.88</v>
+      </c>
+      <c r="AB12">
         <v>1.82</v>
       </c>
-      <c r="AB12">
-        <v>1.81</v>
-      </c>
       <c r="AC12">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
         <v>1.68</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -8794,43 +8794,43 @@
         <v>0</v>
       </c>
       <c r="Q52">
+        <v>3.6</v>
+      </c>
+      <c r="R52">
+        <v>1.91</v>
+      </c>
+      <c r="S52">
+        <v>1.56</v>
+      </c>
+      <c r="T52">
+        <v>2.36</v>
+      </c>
+      <c r="U52">
         <v>3.52</v>
       </c>
-      <c r="R52">
-        <v>1.79</v>
-      </c>
-      <c r="S52">
-        <v>1.6</v>
-      </c>
-      <c r="T52">
-        <v>2.23</v>
-      </c>
-      <c r="U52">
-        <v>3.6</v>
-      </c>
       <c r="V52">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X52">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y52">
         <v>1.51</v>
       </c>
       <c r="Z52">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AA52">
-        <v>2.67</v>
+        <v>2.32</v>
       </c>
       <c r="AB52">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC52">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AD52">
         <v>1.12</v>
@@ -8839,10 +8839,10 @@
         <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG52">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -644,25 +644,25 @@
         <v>2.37</v>
       </c>
       <c r="Q2">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="R2">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
         <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
         <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
         <v>1.02</v>
@@ -677,19 +677,19 @@
         <v>2.02</v>
       </c>
       <c r="AB2">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AC2">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE2">
         <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG2">
         <v>1.86</v>
@@ -708,7 +708,7 @@
         <v>1.26</v>
       </c>
       <c r="AK2">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
         <v>2.6</v>
@@ -970,55 +970,55 @@
         <v>2.8</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1136,22 +1136,22 @@
         <v>3.07</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S5">
         <v>1.41</v>
       </c>
       <c r="T5">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="U5">
         <v>3.2</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1197,7 +1197,7 @@
         <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O11">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P11">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q11">
-        <v>5.8</v>
+        <v>4.79</v>
       </c>
       <c r="R11">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T11">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="U11">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="V11">
         <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="AA11">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB11">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AC11">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="AD11">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AE11">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,61 +2268,61 @@
         <v>2.15</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
         <v>2.9</v>
       </c>
       <c r="Q12">
-        <v>3.26</v>
+        <v>2.91</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="U12">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="V12">
         <v>1.36</v>
       </c>
       <c r="W12">
+        <v>1.05</v>
+      </c>
+      <c r="X12">
         <v>1.03</v>
       </c>
-      <c r="X12">
-        <v>1.01</v>
-      </c>
       <c r="Y12">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z12">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AA12">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AB12">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC12">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AD12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q21">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -1939,61 +1939,61 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="O10">
         <v>3.6</v>
       </c>
       <c r="P10">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q10">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="R10">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z10">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="AA10">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB10">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
         <v>2.49</v>
       </c>
       <c r="AD10">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE10">
         <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG10">
         <v>2.26</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK10">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2917,34 +2917,34 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O16">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P16">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="Q16">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="R16">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="S16">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="U16">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V16">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="W16">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X16">
         <v>1</v>
@@ -2956,25 +2956,25 @@
         <v>10</v>
       </c>
       <c r="AA16">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AB16">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="AC16">
         <v>1.47</v>
       </c>
       <c r="AD16">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AE16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF16">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AG16">
-        <v>4.16</v>
+        <v>4.09</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,55 +3083,55 @@
         <v>3.8</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q17">
         <v>3.9</v>
       </c>
       <c r="R17">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S17">
         <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U17">
         <v>2.27</v>
       </c>
       <c r="V17">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z17">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AA17">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB17">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC17">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="AD17">
         <v>1.48</v>
       </c>
       <c r="AE17">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
         <v>1.54</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="AK17">
         <v>1.2</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G48">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8800,37 +8800,37 @@
         <v>1.91</v>
       </c>
       <c r="S52">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="T52">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="U52">
         <v>3.52</v>
       </c>
       <c r="V52">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W52">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X52">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y52">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z52">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AA52">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AB52">
         <v>1.44</v>
       </c>
       <c r="AC52">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AD52">
         <v>1.12</v>
@@ -8839,10 +8839,10 @@
         <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG52">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU58"/>
+  <dimension ref="A1:AU56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1245,22 +1245,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>1.15</v>
       </c>
       <c r="O6">
-        <v>3.07</v>
+        <v>6.5</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
       <c r="P7">
-        <v>4.42</v>
+        <v>2.1</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:00</t>
+          <t>2026-09-01 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-01 14:00:00</t>
+          <t>2026-09-01 12:45:00</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-01 14:00:00</t>
+          <t>2026-09-01 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
+        <v>2.17</v>
+      </c>
+      <c r="O12">
+        <v>3.6</v>
+      </c>
+      <c r="P12">
+        <v>2.95</v>
+      </c>
+      <c r="Q12">
+        <v>2.5</v>
+      </c>
+      <c r="R12">
+        <v>2.38</v>
+      </c>
+      <c r="S12">
+        <v>1.3</v>
+      </c>
+      <c r="T12">
+        <v>3.25</v>
+      </c>
+      <c r="U12">
+        <v>2.3</v>
+      </c>
+      <c r="V12">
+        <v>1.55</v>
+      </c>
+      <c r="W12">
+        <v>1.09</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.16</v>
+      </c>
+      <c r="Z12">
+        <v>4.05</v>
+      </c>
+      <c r="AA12">
+        <v>1.66</v>
+      </c>
+      <c r="AB12">
         <v>2.15</v>
       </c>
-      <c r="O12">
-        <v>3.1</v>
-      </c>
-      <c r="P12">
-        <v>2.9</v>
-      </c>
-      <c r="Q12">
-        <v>2.91</v>
-      </c>
-      <c r="R12">
-        <v>2.16</v>
-      </c>
-      <c r="S12">
-        <v>1.41</v>
-      </c>
-      <c r="T12">
-        <v>2.61</v>
-      </c>
-      <c r="U12">
-        <v>2.72</v>
-      </c>
-      <c r="V12">
-        <v>1.36</v>
-      </c>
-      <c r="W12">
-        <v>1.05</v>
-      </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
-      <c r="Y12">
-        <v>1.27</v>
-      </c>
-      <c r="Z12">
-        <v>3.14</v>
-      </c>
-      <c r="AA12">
-        <v>1.96</v>
-      </c>
-      <c r="AB12">
-        <v>1.75</v>
-      </c>
       <c r="AC12">
-        <v>3.55</v>
+        <v>2.49</v>
       </c>
       <c r="AD12">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-01 14:30:00</t>
+          <t>2026-09-01 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-01 14:30:00</t>
+          <t>2026-09-01 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2875,22 +2875,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:00:00</t>
+          <t>2026-09-01 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:30:00</t>
+          <t>2026-09-01 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:45:00</t>
+          <t>2026-09-01 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:45:00</t>
+          <t>2026-09-01 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G43">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G48">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G49">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-01 16:00:00</t>
+          <t>2026-09-01 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G50">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-09-01 16:00:00</t>
+          <t>2026-09-01 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8575,27 +8575,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC51">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK51">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-09-01 18:30:00</t>
+          <t>2026-09-01 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8738,27 +8738,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G52">
@@ -8794,55 +8794,55 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-09-01 19:30:00</t>
+          <t>2026-09-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G53">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-09-01 21:00:00</t>
+          <t>2026-09-01 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-09-01 21:00:00</t>
+          <t>2026-09-01 18:30:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G55">
@@ -9283,55 +9283,55 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-09-01 21:00:00</t>
+          <t>2026-09-01 19:30:00</t>
         </is>
       </c>
     </row>
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G56">
@@ -9540,332 +9540,6 @@
         <v>0</v>
       </c>
       <c r="AU56" t="inlineStr">
-        <is>
-          <t>2026-09-01 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Široki Brijeg</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Sarajevo</t>
-        </is>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <v>0</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>0</v>
-      </c>
-      <c r="P57">
-        <v>0</v>
-      </c>
-      <c r="Q57">
-        <v>0</v>
-      </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57">
-        <v>0</v>
-      </c>
-      <c r="T57">
-        <v>0</v>
-      </c>
-      <c r="U57">
-        <v>0</v>
-      </c>
-      <c r="V57">
-        <v>0</v>
-      </c>
-      <c r="W57">
-        <v>0</v>
-      </c>
-      <c r="X57">
-        <v>0</v>
-      </c>
-      <c r="Y57">
-        <v>0</v>
-      </c>
-      <c r="Z57">
-        <v>0</v>
-      </c>
-      <c r="AA57">
-        <v>0</v>
-      </c>
-      <c r="AB57">
-        <v>0</v>
-      </c>
-      <c r="AC57">
-        <v>0</v>
-      </c>
-      <c r="AD57">
-        <v>0</v>
-      </c>
-      <c r="AE57">
-        <v>0</v>
-      </c>
-      <c r="AF57">
-        <v>0</v>
-      </c>
-      <c r="AG57">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57">
-        <v>0</v>
-      </c>
-      <c r="AK57">
-        <v>0</v>
-      </c>
-      <c r="AL57">
-        <v>0</v>
-      </c>
-      <c r="AM57">
-        <v>-1</v>
-      </c>
-      <c r="AN57">
-        <v>-1</v>
-      </c>
-      <c r="AO57">
-        <v>-1</v>
-      </c>
-      <c r="AP57">
-        <v>-1</v>
-      </c>
-      <c r="AQ57">
-        <v>0</v>
-      </c>
-      <c r="AR57">
-        <v>0</v>
-      </c>
-      <c r="AS57">
-        <v>0</v>
-      </c>
-      <c r="AT57">
-        <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>2026-09-01 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Mushuc Runa SC</t>
-        </is>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <v>0</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
-        <v>0</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
-        <v>0</v>
-      </c>
-      <c r="T58">
-        <v>0</v>
-      </c>
-      <c r="U58">
-        <v>0</v>
-      </c>
-      <c r="V58">
-        <v>0</v>
-      </c>
-      <c r="W58">
-        <v>0</v>
-      </c>
-      <c r="X58">
-        <v>0</v>
-      </c>
-      <c r="Y58">
-        <v>0</v>
-      </c>
-      <c r="Z58">
-        <v>0</v>
-      </c>
-      <c r="AA58">
-        <v>0</v>
-      </c>
-      <c r="AB58">
-        <v>0</v>
-      </c>
-      <c r="AC58">
-        <v>0</v>
-      </c>
-      <c r="AD58">
-        <v>0</v>
-      </c>
-      <c r="AE58">
-        <v>0</v>
-      </c>
-      <c r="AF58">
-        <v>0</v>
-      </c>
-      <c r="AG58">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>0</v>
-      </c>
-      <c r="AK58">
-        <v>0</v>
-      </c>
-      <c r="AL58">
-        <v>0</v>
-      </c>
-      <c r="AM58">
-        <v>-1</v>
-      </c>
-      <c r="AN58">
-        <v>-1</v>
-      </c>
-      <c r="AO58">
-        <v>-1</v>
-      </c>
-      <c r="AP58">
-        <v>-1</v>
-      </c>
-      <c r="AQ58">
-        <v>0</v>
-      </c>
-      <c r="AR58">
-        <v>0</v>
-      </c>
-      <c r="AS58">
-        <v>0</v>
-      </c>
-      <c r="AT58">
-        <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
         <is>
           <t>2026-09-01 21:00:00</t>
         </is>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -2268,16 +2268,16 @@
         <v>2.17</v>
       </c>
       <c r="O12">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="Q12">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
         <v>1.3</v>
@@ -2286,43 +2286,43 @@
         <v>3.25</v>
       </c>
       <c r="U12">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="V12">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
         <v>1.16</v>
       </c>
       <c r="Z12">
-        <v>4.05</v>
+        <v>4.35</v>
       </c>
       <c r="AA12">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB12">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC12">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AD12">
         <v>1.46</v>
       </c>
       <c r="AE12">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF12">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q53">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O2">
         <v>3.2</v>
@@ -708,7 +708,7 @@
         <v>1.26</v>
       </c>
       <c r="AK2">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O3">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="P3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
         <v>2.99</v>
       </c>
       <c r="R3">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="S3">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="T3">
         <v>2.1</v>
@@ -825,25 +825,25 @@
         <v>1.2</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
         <v>1.1</v>
       </c>
       <c r="Y3">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Z3">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AA3">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AB3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC3">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AD3">
         <v>1.1</v>
@@ -855,7 +855,7 @@
         <v>2.19</v>
       </c>
       <c r="AG3">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,34 +961,34 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="O4">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="P4">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="Q4">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R4">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="S4">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="U4">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V4">
         <v>1.17</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
         <v>1.12</v>
@@ -1000,22 +1000,22 @@
         <v>2.07</v>
       </c>
       <c r="AA4">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC4">
-        <v>6.55</v>
+        <v>5.65</v>
       </c>
       <c r="AD4">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG4">
         <v>1.53</v>
@@ -1034,7 +1034,7 @@
         <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1157,13 +1157,13 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z5">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AB5">
         <v>1.58</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK5">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2434,58 +2434,58 @@
         <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q13">
-        <v>4.79</v>
+        <v>4.5</v>
       </c>
       <c r="R13">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U13">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="V13">
         <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="AA13">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB13">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AC13">
         <v>2.65</v>
       </c>
       <c r="AD13">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG13">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2600,49 +2600,49 @@
         <v>2.9</v>
       </c>
       <c r="Q14">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="R14">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="S14">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T14">
-        <v>2.61</v>
+        <v>2.86</v>
       </c>
       <c r="U14">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z14">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AB14">
         <v>1.75</v>
       </c>
       <c r="AC14">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AD14">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
         <v>1.75</v>
@@ -2664,7 +2664,7 @@
         <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3406,37 +3406,37 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.8</v>
+        <v>4.12</v>
       </c>
       <c r="O19">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="P19">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="Q19">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T19">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U19">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
         <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.14</v>
@@ -3445,25 +3445,25 @@
         <v>4.45</v>
       </c>
       <c r="AA19">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AB19">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AC19">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AD19">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE19">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF19">
         <v>1.54</v>
       </c>
       <c r="AG19">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="O23">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P23">
-        <v>4.81</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O39">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="P39">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="O43">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="P43">
-        <v>6.6</v>
+        <v>5.58</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O52">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P52">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P53">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL53">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -807,71 +807,71 @@
         <v>3.6</v>
       </c>
       <c r="Q3">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="R3">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="S3">
         <v>1.6</v>
       </c>
       <c r="T3">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="U3">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="V3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y3">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Z3">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AA3">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="AB3">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC3">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="AD3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE3">
         <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AG3">
+        <v>1.61</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.35</v>
+      </c>
+      <c r="AK3">
         <v>1.57</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.36</v>
-      </c>
-      <c r="AK3">
-        <v>1.56</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="O4">
         <v>2.65</v>
       </c>
       <c r="P4">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1009,7 +1009,7 @@
         <v>5.65</v>
       </c>
       <c r="AD4">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
@@ -1018,7 +1018,7 @@
         <v>2.38</v>
       </c>
       <c r="AG4">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK4">
         <v>1.4</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="O6">
-        <v>6.5</v>
+        <v>7.44</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>9.02</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="O18">
         <v>3.9</v>
@@ -3252,7 +3252,7 @@
         <v>2.22</v>
       </c>
       <c r="Q18">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="R18">
         <v>2.64</v>
@@ -3261,16 +3261,16 @@
         <v>1.11</v>
       </c>
       <c r="T18">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="U18">
         <v>1.62</v>
       </c>
       <c r="V18">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="W18">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X18">
         <v>1</v>
@@ -3282,25 +3282,25 @@
         <v>10</v>
       </c>
       <c r="AA18">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AB18">
-        <v>4.16</v>
+        <v>4.3</v>
       </c>
       <c r="AC18">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AD18">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AE18">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AF18">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AG18">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="AK18">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,34 +6666,34 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="O39">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="Q39">
-        <v>2.36</v>
+        <v>2.71</v>
       </c>
       <c r="R39">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="U39">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="V39">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
         <v>1</v>
@@ -6705,41 +6705,41 @@
         <v>3.62</v>
       </c>
       <c r="AA39">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AB39">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC39">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AD39">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
+        <v>1.64</v>
+      </c>
+      <c r="AG39">
+        <v>2.13</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.29</v>
+      </c>
+      <c r="AK39">
         <v>1.68</v>
-      </c>
-      <c r="AG39">
-        <v>2.06</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.26</v>
-      </c>
-      <c r="AK39">
-        <v>1.95</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="O40">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="P40">
+        <v>3.95</v>
+      </c>
+      <c r="Q40">
+        <v>2.36</v>
+      </c>
+      <c r="R40">
+        <v>2.18</v>
+      </c>
+      <c r="S40">
+        <v>1.34</v>
+      </c>
+      <c r="T40">
+        <v>2.99</v>
+      </c>
+      <c r="U40">
+        <v>2.59</v>
+      </c>
+      <c r="V40">
+        <v>1.44</v>
+      </c>
+      <c r="W40">
+        <v>1.06</v>
+      </c>
+      <c r="X40">
+        <v>1</v>
+      </c>
+      <c r="Y40">
+        <v>1.21</v>
+      </c>
+      <c r="Z40">
+        <v>3.62</v>
+      </c>
+      <c r="AA40">
+        <v>1.78</v>
+      </c>
+      <c r="AB40">
+        <v>2</v>
+      </c>
+      <c r="AC40">
         <v>2.8</v>
       </c>
-      <c r="Q40">
-        <v>3.18</v>
-      </c>
-      <c r="R40">
-        <v>2.01</v>
-      </c>
-      <c r="S40">
-        <v>1.43</v>
-      </c>
-      <c r="T40">
-        <v>2.62</v>
-      </c>
-      <c r="U40">
-        <v>2.85</v>
-      </c>
-      <c r="V40">
-        <v>1.37</v>
-      </c>
-      <c r="W40">
-        <v>1.04</v>
-      </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.28</v>
-      </c>
-      <c r="Z40">
-        <v>3.12</v>
-      </c>
-      <c r="AA40">
-        <v>1.99</v>
-      </c>
-      <c r="AB40">
-        <v>1.79</v>
-      </c>
-      <c r="AC40">
-        <v>3.24</v>
-      </c>
       <c r="AD40">
+        <v>1.34</v>
+      </c>
+      <c r="AE40">
+        <v>1.1</v>
+      </c>
+      <c r="AF40">
+        <v>1.68</v>
+      </c>
+      <c r="AG40">
+        <v>2.06</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.26</v>
       </c>
-      <c r="AE40">
-        <v>1.06</v>
-      </c>
-      <c r="AF40">
-        <v>1.73</v>
-      </c>
-      <c r="AG40">
-        <v>2</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.33</v>
-      </c>
       <c r="AK40">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O41">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q41">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="R41">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="S41">
+        <v>1.43</v>
+      </c>
+      <c r="T41">
+        <v>2.62</v>
+      </c>
+      <c r="U41">
+        <v>2.85</v>
+      </c>
+      <c r="V41">
         <v>1.37</v>
       </c>
-      <c r="T41">
-        <v>2.85</v>
-      </c>
-      <c r="U41">
-        <v>2.69</v>
-      </c>
-      <c r="V41">
-        <v>1.41</v>
-      </c>
       <c r="W41">
+        <v>1.04</v>
+      </c>
+      <c r="X41">
+        <v>1.02</v>
+      </c>
+      <c r="Y41">
+        <v>1.28</v>
+      </c>
+      <c r="Z41">
+        <v>3.12</v>
+      </c>
+      <c r="AA41">
+        <v>1.99</v>
+      </c>
+      <c r="AB41">
+        <v>1.79</v>
+      </c>
+      <c r="AC41">
+        <v>3.24</v>
+      </c>
+      <c r="AD41">
+        <v>1.26</v>
+      </c>
+      <c r="AE41">
         <v>1.06</v>
       </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.29</v>
-      </c>
-      <c r="Z41">
-        <v>3.38</v>
-      </c>
-      <c r="AA41">
-        <v>1.87</v>
-      </c>
-      <c r="AB41">
-        <v>1.9</v>
-      </c>
-      <c r="AC41">
-        <v>2.99</v>
-      </c>
-      <c r="AD41">
-        <v>1.3</v>
-      </c>
-      <c r="AE41">
-        <v>1.08</v>
-      </c>
       <c r="AF41">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG41">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK41">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P42">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q42">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T42">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U42">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="V42">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="AA42">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB42">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC42">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="AD42">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE42">
         <v>1.08</v>
       </c>
       <c r="AF42">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG42">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -9123,19 +9123,19 @@
         <v>2.76</v>
       </c>
       <c r="R54">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="S54">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T54">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="U54">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="V54">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W54">
         <v>1.02</v>
@@ -9144,13 +9144,13 @@
         <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z54">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="AA54">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AB54">
         <v>1.56</v>
@@ -9168,7 +9168,7 @@
         <v>1.98</v>
       </c>
       <c r="AG54">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK54">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9289,28 +9289,28 @@
         <v>1.91</v>
       </c>
       <c r="S55">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="T55">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="U55">
-        <v>3.52</v>
+        <v>3.9</v>
       </c>
       <c r="V55">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W55">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X55">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y55">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z55">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AA55">
         <v>2.3</v>
@@ -9319,7 +9319,7 @@
         <v>1.44</v>
       </c>
       <c r="AC55">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AD55">
         <v>1.12</v>
@@ -9328,7 +9328,7 @@
         <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG55">
         <v>1.69</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK55">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AL55">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O2">
         <v>3.2</v>
@@ -644,25 +644,25 @@
         <v>2.37</v>
       </c>
       <c r="Q2">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="U2">
         <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
         <v>1.02</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AK2">
         <v>1.36</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O5">
         <v>3.1</v>
@@ -1136,7 +1136,7 @@
         <v>3.07</v>
       </c>
       <c r="R5">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S5">
         <v>1.41</v>
@@ -1157,10 +1157,10 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z5">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA5">
         <v>2.14</v>
@@ -1197,7 +1197,7 @@
         <v>1.34</v>
       </c>
       <c r="AK5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O13">
         <v>3.6</v>
       </c>
       <c r="P13">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Q13">
         <v>4.5</v>
@@ -2452,40 +2452,40 @@
         <v>2.63</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB13">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AC13">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AD13">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE13">
         <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="AK13">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB14">
         <v>1.75</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -9295,16 +9295,16 @@
         <v>2.25</v>
       </c>
       <c r="U55">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="V55">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W55">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y55">
         <v>1.4</v>
@@ -9322,7 +9322,7 @@
         <v>4.7</v>
       </c>
       <c r="AD55">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE55">
         <v>1.04</v>
@@ -9347,7 +9347,7 @@
         <v>1.44</v>
       </c>
       <c r="AK55">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL55">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -9144,7 +9144,7 @@
         <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z54">
         <v>2.58</v>
@@ -9159,13 +9159,13 @@
         <v>4.3</v>
       </c>
       <c r="AD54">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE54">
         <v>1.01</v>
       </c>
       <c r="AF54">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG54">
         <v>1.7</v>
@@ -9184,7 +9184,7 @@
         <v>1.32</v>
       </c>
       <c r="AK54">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q56">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -650,7 +650,7 @@
         <v>2.06</v>
       </c>
       <c r="S2">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
         <v>2.66</v>
@@ -659,22 +659,22 @@
         <v>2.88</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA2">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB2">
         <v>1.64</v>
@@ -689,7 +689,7 @@
         <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG2">
         <v>1.86</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
         <v>1.36</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="P3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q3">
         <v>2.95</v>
@@ -816,7 +816,7 @@
         <v>1.6</v>
       </c>
       <c r="T3">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="U3">
         <v>3.58</v>
@@ -825,7 +825,7 @@
         <v>1.21</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
         <v>1.09</v>
@@ -834,16 +834,16 @@
         <v>1.53</v>
       </c>
       <c r="Z3">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AA3">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="AB3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC3">
-        <v>4.85</v>
+        <v>5.59</v>
       </c>
       <c r="AD3">
         <v>1.11</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="O4">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P4">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -976,19 +976,19 @@
         <v>1.73</v>
       </c>
       <c r="S4">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="U4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="V4">
         <v>1.17</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
         <v>1.12</v>
@@ -1009,13 +1009,13 @@
         <v>5.65</v>
       </c>
       <c r="AD4">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG4">
         <v>1.55</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK4">
         <v>1.4</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O5">
         <v>3.1</v>
@@ -1151,7 +1151,7 @@
         <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,16 +1160,16 @@
         <v>1.32</v>
       </c>
       <c r="Z5">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA5">
         <v>2.14</v>
       </c>
       <c r="AB5">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC5">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="AD5">
         <v>1.18</v>
@@ -1181,7 +1181,7 @@
         <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P13">
         <v>1.61</v>
       </c>
       <c r="Q13">
-        <v>4.5</v>
+        <v>5.26</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S13">
         <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U13">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="V13">
         <v>1.46</v>
@@ -2461,31 +2461,31 @@
         <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA13">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB13">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AC13">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD13">
         <v>1.39</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF13">
         <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>2.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,7 +2594,7 @@
         <v>2.15</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
         <v>2.9</v>
@@ -2606,46 +2606,46 @@
         <v>2.04</v>
       </c>
       <c r="S14">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z14">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA14">
         <v>2</v>
       </c>
       <c r="AB14">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC14">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="AD14">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE14">
         <v>1.04</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG14">
         <v>1.95</v>
@@ -2664,7 +2664,7 @@
         <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.12</v>
+        <v>3.95</v>
       </c>
       <c r="O19">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="Q19">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R19">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S19">
         <v>1.27</v>
       </c>
       <c r="T19">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="V19">
         <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
         <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AA19">
         <v>1.56</v>
       </c>
       <c r="AB19">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="AC19">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AD19">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE19">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF19">
         <v>1.54</v>
       </c>
       <c r="AG19">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AK19">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O20">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q20">
         <v>3.13</v>
@@ -3587,16 +3587,16 @@
         <v>1.18</v>
       </c>
       <c r="T20">
-        <v>3.88</v>
+        <v>4.4</v>
       </c>
       <c r="U20">
         <v>1.93</v>
       </c>
       <c r="V20">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W20">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3608,13 +3608,13 @@
         <v>6.1</v>
       </c>
       <c r="AA20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB20">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AC20">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD20">
         <v>1.85</v>
@@ -3626,7 +3626,7 @@
         <v>1.31</v>
       </c>
       <c r="AG20">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="AK20">
         <v>1.37</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="O23">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="Q23">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R23">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="S23">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="T23">
-        <v>4.8</v>
+        <v>3.82</v>
       </c>
       <c r="U23">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="V23">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="W23">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Z23">
-        <v>6.32</v>
+        <v>6.85</v>
       </c>
       <c r="AA23">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AB23">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="AC23">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AD23">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AE23">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AF23">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG23">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,25 +4221,25 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="O24">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="P24">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="Q24">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="R24">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
         <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U24">
         <v>2.22</v>
@@ -4248,7 +4248,7 @@
         <v>1.58</v>
       </c>
       <c r="W24">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4260,10 +4260,10 @@
         <v>4.7</v>
       </c>
       <c r="AA24">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB24">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AC24">
         <v>2.34</v>
@@ -4278,7 +4278,7 @@
         <v>1.51</v>
       </c>
       <c r="AG24">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O25">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P25">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P27">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.79</v>
+        <v>3.35</v>
       </c>
       <c r="O28">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>4.5</v>
+        <v>1.99</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O29">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,65 +5199,65 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.3</v>
+        <v>1.64</v>
       </c>
       <c r="O30">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
+        <v>4.6</v>
+      </c>
+      <c r="Q30">
+        <v>2.22</v>
+      </c>
+      <c r="R30">
+        <v>2.2</v>
+      </c>
+      <c r="S30">
+        <v>1.33</v>
+      </c>
+      <c r="T30">
+        <v>2.98</v>
+      </c>
+      <c r="U30">
+        <v>2.56</v>
+      </c>
+      <c r="V30">
+        <v>1.44</v>
+      </c>
+      <c r="W30">
+        <v>1.07</v>
+      </c>
+      <c r="X30">
+        <v>1.02</v>
+      </c>
+      <c r="Y30">
+        <v>1.22</v>
+      </c>
+      <c r="Z30">
+        <v>3.5</v>
+      </c>
+      <c r="AA30">
+        <v>1.8</v>
+      </c>
+      <c r="AB30">
+        <v>1.96</v>
+      </c>
+      <c r="AC30">
+        <v>3.04</v>
+      </c>
+      <c r="AD30">
+        <v>1.36</v>
+      </c>
+      <c r="AE30">
+        <v>1.1</v>
+      </c>
+      <c r="AF30">
+        <v>1.75</v>
+      </c>
+      <c r="AG30">
         <v>1.97</v>
       </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>0</v>
-      </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="O31">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>3.55</v>
+        <v>2.04</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="O32">
+        <v>3.45</v>
+      </c>
+      <c r="P32">
+        <v>3.6</v>
+      </c>
+      <c r="Q32">
+        <v>2.4</v>
+      </c>
+      <c r="R32">
+        <v>2.2</v>
+      </c>
+      <c r="S32">
+        <v>1.34</v>
+      </c>
+      <c r="T32">
+        <v>2.95</v>
+      </c>
+      <c r="U32">
+        <v>2.75</v>
+      </c>
+      <c r="V32">
+        <v>1.42</v>
+      </c>
+      <c r="W32">
+        <v>1.07</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>1.26</v>
+      </c>
+      <c r="Z32">
         <v>3.65</v>
       </c>
-      <c r="P32">
-        <v>3.8</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P33">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P34">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="O35">
+        <v>3.55</v>
+      </c>
+      <c r="P35">
+        <v>3</v>
+      </c>
+      <c r="Q35">
+        <v>2.7</v>
+      </c>
+      <c r="R35">
+        <v>2.16</v>
+      </c>
+      <c r="S35">
+        <v>1.33</v>
+      </c>
+      <c r="T35">
+        <v>2.99</v>
+      </c>
+      <c r="U35">
+        <v>2.66</v>
+      </c>
+      <c r="V35">
+        <v>1.41</v>
+      </c>
+      <c r="W35">
+        <v>1.05</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.27</v>
+      </c>
+      <c r="Z35">
         <v>3.5</v>
       </c>
-      <c r="P35">
-        <v>3.25</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="O37">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6506,61 +6506,61 @@
         <v>1.54</v>
       </c>
       <c r="O38">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="P38">
-        <v>6</v>
+        <v>4.45</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q39">
-        <v>2.71</v>
+        <v>2.37</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T39">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="U39">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="V39">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA39">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AB39">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC39">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="AD39">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
+        <v>2.21</v>
+      </c>
+      <c r="O40">
+        <v>3.3</v>
+      </c>
+      <c r="P40">
+        <v>3.22</v>
+      </c>
+      <c r="Q40">
+        <v>3</v>
+      </c>
+      <c r="R40">
+        <v>1.99</v>
+      </c>
+      <c r="S40">
+        <v>1.41</v>
+      </c>
+      <c r="T40">
+        <v>2.69</v>
+      </c>
+      <c r="U40">
+        <v>2.73</v>
+      </c>
+      <c r="V40">
+        <v>1.38</v>
+      </c>
+      <c r="W40">
+        <v>1.04</v>
+      </c>
+      <c r="X40">
+        <v>1.02</v>
+      </c>
+      <c r="Y40">
+        <v>1.3</v>
+      </c>
+      <c r="Z40">
+        <v>3.12</v>
+      </c>
+      <c r="AA40">
+        <v>2.09</v>
+      </c>
+      <c r="AB40">
         <v>1.8</v>
       </c>
-      <c r="O40">
-        <v>3.65</v>
-      </c>
-      <c r="P40">
-        <v>3.95</v>
-      </c>
-      <c r="Q40">
-        <v>2.36</v>
-      </c>
-      <c r="R40">
-        <v>2.18</v>
-      </c>
-      <c r="S40">
-        <v>1.34</v>
-      </c>
-      <c r="T40">
-        <v>2.99</v>
-      </c>
-      <c r="U40">
-        <v>2.59</v>
-      </c>
-      <c r="V40">
-        <v>1.44</v>
-      </c>
-      <c r="W40">
-        <v>1.06</v>
-      </c>
-      <c r="X40">
-        <v>1</v>
-      </c>
-      <c r="Y40">
-        <v>1.21</v>
-      </c>
-      <c r="Z40">
-        <v>3.62</v>
-      </c>
-      <c r="AA40">
-        <v>1.78</v>
-      </c>
-      <c r="AB40">
-        <v>2</v>
-      </c>
       <c r="AC40">
-        <v>2.8</v>
+        <v>3.24</v>
       </c>
       <c r="AD40">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG40">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK40">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="O41">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="P41">
-        <v>2.8</v>
+        <v>3.86</v>
       </c>
       <c r="Q41">
-        <v>3.18</v>
+        <v>2.35</v>
       </c>
       <c r="R41">
-        <v>2.01</v>
+        <v>2.31</v>
       </c>
       <c r="S41">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="U41">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="V41">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W41">
         <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z41">
-        <v>3.12</v>
+        <v>3.72</v>
       </c>
       <c r="AA41">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AB41">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AC41">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="AD41">
+        <v>1.35</v>
+      </c>
+      <c r="AE41">
+        <v>1.12</v>
+      </c>
+      <c r="AF41">
+        <v>1.71</v>
+      </c>
+      <c r="AG41">
+        <v>2.02</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.26</v>
       </c>
-      <c r="AE41">
-        <v>1.06</v>
-      </c>
-      <c r="AF41">
-        <v>1.73</v>
-      </c>
-      <c r="AG41">
-        <v>2</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.33</v>
-      </c>
       <c r="AK41">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="O42">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q42">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="R42">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S42">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T42">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U42">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="V42">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z42">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="AA42">
         <v>1.87</v>
       </c>
       <c r="AB42">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC42">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="AD42">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE42">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF42">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG42">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK42">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="O43">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="P43">
-        <v>5.58</v>
+        <v>4.74</v>
       </c>
       <c r="Q43">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S43">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T43">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="U43">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="V43">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z43">
-        <v>3.76</v>
+        <v>3.35</v>
       </c>
       <c r="AA43">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AB43">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AC43">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AD43">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE43">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF43">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG43">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="O44">
+        <v>3.4</v>
+      </c>
+      <c r="P44">
+        <v>3.04</v>
+      </c>
+      <c r="Q44">
+        <v>2.62</v>
+      </c>
+      <c r="R44">
+        <v>2.25</v>
+      </c>
+      <c r="S44">
+        <v>1.36</v>
+      </c>
+      <c r="T44">
+        <v>3.06</v>
+      </c>
+      <c r="U44">
+        <v>2.8</v>
+      </c>
+      <c r="V44">
+        <v>1.41</v>
+      </c>
+      <c r="W44">
+        <v>1.06</v>
+      </c>
+      <c r="X44">
+        <v>1.03</v>
+      </c>
+      <c r="Y44">
+        <v>1.3</v>
+      </c>
+      <c r="Z44">
         <v>3.45</v>
       </c>
-      <c r="P44">
-        <v>2.56</v>
-      </c>
-      <c r="Q44">
-        <v>3.12</v>
-      </c>
-      <c r="R44">
-        <v>2.15</v>
-      </c>
-      <c r="S44">
-        <v>1.35</v>
-      </c>
-      <c r="T44">
-        <v>2.94</v>
-      </c>
-      <c r="U44">
-        <v>2.73</v>
-      </c>
-      <c r="V44">
-        <v>1.4</v>
-      </c>
-      <c r="W44">
-        <v>1.05</v>
-      </c>
-      <c r="X44">
-        <v>1.01</v>
-      </c>
-      <c r="Y44">
-        <v>1.24</v>
-      </c>
-      <c r="Z44">
-        <v>3.38</v>
-      </c>
       <c r="AA44">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB44">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC44">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD44">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE44">
         <v>1.07</v>
       </c>
       <c r="AF44">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG44">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P51">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="O52">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="Q52">
-        <v>3.28</v>
+        <v>3.66</v>
       </c>
       <c r="R52">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="S52">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T52">
-        <v>2.77</v>
+        <v>3.19</v>
       </c>
       <c r="U52">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V52">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W52">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.18</v>
+        <v>3.54</v>
       </c>
       <c r="AA52">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AB52">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AC52">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="AD52">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE52">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AG52">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="AK52">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,55 +8948,55 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="O53">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="P53">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="Q53">
-        <v>2.87</v>
+        <v>3.03</v>
       </c>
       <c r="R53">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T53">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="U53">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V53">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W53">
         <v>1.06</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z53">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AA53">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB53">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC53">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AD53">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE53">
         <v>1.09</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK53">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL53">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="O6">
-        <v>7.44</v>
+        <v>7.6</v>
       </c>
       <c r="P6">
-        <v>9.02</v>
+        <v>14</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="O12">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="S12">
         <v>1.3</v>
@@ -2286,19 +2286,19 @@
         <v>3.25</v>
       </c>
       <c r="U12">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V12">
         <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z12">
         <v>4.35</v>
@@ -2307,22 +2307,22 @@
         <v>1.65</v>
       </c>
       <c r="AB12">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC12">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AD12">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AE12">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG12">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P18">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="Q18">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="R18">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="S18">
         <v>1.11</v>
       </c>
       <c r="T18">
-        <v>5.5</v>
+        <v>5.05</v>
       </c>
       <c r="U18">
         <v>1.62</v>
@@ -3285,22 +3285,22 @@
         <v>1.2</v>
       </c>
       <c r="AB18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AC18">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AD18">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AE18">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AF18">
         <v>1.19</v>
       </c>
       <c r="AG18">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
         <v>1.39</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,58 +4710,58 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="O27">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="P27">
-        <v>2.55</v>
+        <v>4.45</v>
       </c>
       <c r="Q27">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="R27">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="S27">
+        <v>1.3</v>
+      </c>
+      <c r="T27">
+        <v>3.16</v>
+      </c>
+      <c r="U27">
+        <v>2.44</v>
+      </c>
+      <c r="V27">
+        <v>1.48</v>
+      </c>
+      <c r="W27">
+        <v>1.09</v>
+      </c>
+      <c r="X27">
+        <v>1.02</v>
+      </c>
+      <c r="Y27">
+        <v>1.18</v>
+      </c>
+      <c r="Z27">
+        <v>3.84</v>
+      </c>
+      <c r="AA27">
+        <v>1.71</v>
+      </c>
+      <c r="AB27">
+        <v>2.08</v>
+      </c>
+      <c r="AC27">
+        <v>2.62</v>
+      </c>
+      <c r="AD27">
         <v>1.38</v>
       </c>
-      <c r="T27">
-        <v>2.77</v>
-      </c>
-      <c r="U27">
-        <v>2.85</v>
-      </c>
-      <c r="V27">
-        <v>1.36</v>
-      </c>
-      <c r="W27">
-        <v>1.04</v>
-      </c>
-      <c r="X27">
-        <v>1.01</v>
-      </c>
-      <c r="Y27">
-        <v>1.28</v>
-      </c>
-      <c r="Z27">
-        <v>3.08</v>
-      </c>
-      <c r="AA27">
-        <v>2</v>
-      </c>
-      <c r="AB27">
-        <v>1.77</v>
-      </c>
-      <c r="AC27">
-        <v>3.42</v>
-      </c>
-      <c r="AD27">
-        <v>1.23</v>
-      </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
         <v>1.76</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
-        <v>1.47</v>
+        <v>2.36</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.35</v>
+        <v>1.51</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>1.99</v>
+        <v>4.9</v>
       </c>
       <c r="Q28">
-        <v>4.13</v>
+        <v>2.04</v>
       </c>
       <c r="R28">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U28">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA28">
+        <v>1.92</v>
+      </c>
+      <c r="AB28">
+        <v>1.85</v>
+      </c>
+      <c r="AC28">
+        <v>3.3</v>
+      </c>
+      <c r="AD28">
+        <v>1.32</v>
+      </c>
+      <c r="AE28">
+        <v>1.06</v>
+      </c>
+      <c r="AF28">
         <v>1.98</v>
       </c>
-      <c r="AB28">
-        <v>1.81</v>
-      </c>
-      <c r="AC28">
-        <v>3.45</v>
-      </c>
-      <c r="AD28">
-        <v>1.3</v>
-      </c>
-      <c r="AE28">
-        <v>1.05</v>
-      </c>
-      <c r="AF28">
-        <v>1.77</v>
-      </c>
       <c r="AG28">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.27</v>
+        <v>2.46</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.92</v>
+        <v>3.55</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q29">
-        <v>2.57</v>
+        <v>4.19</v>
       </c>
       <c r="R29">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="U29">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="V29">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="AA29">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB29">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC29">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE29">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AG29">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.26</v>
+        <v>1.76</v>
       </c>
       <c r="AK29">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.64</v>
+        <v>3.35</v>
       </c>
       <c r="O30">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>4.6</v>
+        <v>1.99</v>
       </c>
       <c r="Q30">
-        <v>2.22</v>
+        <v>4.13</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T30">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U30">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z30">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA30">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AB30">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AC30">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="AD30">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE30">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF30">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG30">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK30">
-        <v>2.07</v>
+        <v>1.27</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="Q31">
-        <v>3.62</v>
+        <v>2.57</v>
       </c>
       <c r="R31">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="S31">
+        <v>1.33</v>
+      </c>
+      <c r="T31">
+        <v>2.99</v>
+      </c>
+      <c r="U31">
+        <v>2.69</v>
+      </c>
+      <c r="V31">
+        <v>1.4</v>
+      </c>
+      <c r="W31">
+        <v>1.05</v>
+      </c>
+      <c r="X31">
+        <v>1.01</v>
+      </c>
+      <c r="Y31">
+        <v>1.24</v>
+      </c>
+      <c r="Z31">
+        <v>3.56</v>
+      </c>
+      <c r="AA31">
+        <v>1.88</v>
+      </c>
+      <c r="AB31">
+        <v>1.88</v>
+      </c>
+      <c r="AC31">
+        <v>3.08</v>
+      </c>
+      <c r="AD31">
         <v>1.28</v>
       </c>
-      <c r="T31">
-        <v>3.28</v>
-      </c>
-      <c r="U31">
-        <v>2.36</v>
-      </c>
-      <c r="V31">
-        <v>1.5</v>
-      </c>
-      <c r="W31">
+      <c r="AE31">
         <v>1.07</v>
       </c>
-      <c r="X31">
-        <v>1.03</v>
-      </c>
-      <c r="Y31">
-        <v>1.16</v>
-      </c>
-      <c r="Z31">
-        <v>4.1</v>
-      </c>
-      <c r="AA31">
-        <v>1.68</v>
-      </c>
-      <c r="AB31">
-        <v>2.12</v>
-      </c>
-      <c r="AC31">
-        <v>2.56</v>
-      </c>
-      <c r="AD31">
-        <v>1.38</v>
-      </c>
-      <c r="AE31">
-        <v>1.16</v>
-      </c>
       <c r="AF31">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AG31">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="O32">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="P32">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="Q32">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="R32">
         <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="U32">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
         <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB32">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AC32">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="AD32">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="O33">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
-        <v>2.97</v>
+        <v>2.55</v>
       </c>
       <c r="Q33">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="U33">
         <v>2.85</v>
@@ -5715,22 +5715,22 @@
         <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z33">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA33">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB33">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC33">
         <v>3.42</v>
@@ -5739,7 +5739,7 @@
         <v>1.23</v>
       </c>
       <c r="AE33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
         <v>1.76</v>
@@ -5761,7 +5761,7 @@
         <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.41</v>
+        <v>3.45</v>
       </c>
       <c r="O34">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>2.59</v>
+        <v>2.04</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S34">
+        <v>1.28</v>
+      </c>
+      <c r="T34">
+        <v>3.28</v>
+      </c>
+      <c r="U34">
+        <v>2.36</v>
+      </c>
+      <c r="V34">
+        <v>1.5</v>
+      </c>
+      <c r="W34">
+        <v>1.07</v>
+      </c>
+      <c r="X34">
+        <v>1.03</v>
+      </c>
+      <c r="Y34">
+        <v>1.16</v>
+      </c>
+      <c r="Z34">
+        <v>4.1</v>
+      </c>
+      <c r="AA34">
+        <v>1.68</v>
+      </c>
+      <c r="AB34">
+        <v>2.12</v>
+      </c>
+      <c r="AC34">
+        <v>2.56</v>
+      </c>
+      <c r="AD34">
         <v>1.38</v>
       </c>
-      <c r="T34">
-        <v>2.91</v>
-      </c>
-      <c r="U34">
-        <v>2.93</v>
-      </c>
-      <c r="V34">
-        <v>1.38</v>
-      </c>
-      <c r="W34">
-        <v>1.05</v>
-      </c>
-      <c r="X34">
-        <v>1.02</v>
-      </c>
-      <c r="Y34">
-        <v>1.3</v>
-      </c>
-      <c r="Z34">
-        <v>3.39</v>
-      </c>
-      <c r="AA34">
-        <v>1.96</v>
-      </c>
-      <c r="AB34">
-        <v>1.8</v>
-      </c>
-      <c r="AC34">
-        <v>3.2</v>
-      </c>
-      <c r="AD34">
-        <v>1.26</v>
-      </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="O35">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="Q35">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="R35">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T35">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U35">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V35">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z35">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AA35">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB35">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AC35">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="AD35">
         <v>1.3</v>
       </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG35">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.55</v>
+        <v>2.2</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P36">
-        <v>1.95</v>
+        <v>2.97</v>
       </c>
       <c r="Q36">
-        <v>4.19</v>
+        <v>2.83</v>
       </c>
       <c r="R36">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="S36">
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U36">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="V36">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="AA36">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AB36">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC36">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="AD36">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AE36">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF36">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AG36">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.51</v>
+        <v>2.41</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="P37">
-        <v>4.9</v>
+        <v>2.59</v>
       </c>
       <c r="Q37">
-        <v>2.04</v>
+        <v>3.1</v>
       </c>
       <c r="R37">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="U37">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="V37">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
         <v>1.3</v>
       </c>
       <c r="Z37">
-        <v>3.28</v>
+        <v>3.39</v>
       </c>
       <c r="AA37">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AB37">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC37">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD37">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE37">
         <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AG37">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>2.46</v>
+        <v>1.48</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="O38">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="P38">
-        <v>4.45</v>
+        <v>3</v>
       </c>
       <c r="Q38">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="R38">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="S38">
+        <v>1.33</v>
+      </c>
+      <c r="T38">
+        <v>2.99</v>
+      </c>
+      <c r="U38">
+        <v>2.66</v>
+      </c>
+      <c r="V38">
+        <v>1.41</v>
+      </c>
+      <c r="W38">
+        <v>1.05</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.27</v>
+      </c>
+      <c r="Z38">
+        <v>3.5</v>
+      </c>
+      <c r="AA38">
+        <v>1.81</v>
+      </c>
+      <c r="AB38">
+        <v>1.86</v>
+      </c>
+      <c r="AC38">
+        <v>3.2</v>
+      </c>
+      <c r="AD38">
         <v>1.3</v>
       </c>
-      <c r="T38">
-        <v>3.16</v>
-      </c>
-      <c r="U38">
-        <v>2.44</v>
-      </c>
-      <c r="V38">
-        <v>1.48</v>
-      </c>
-      <c r="W38">
-        <v>1.09</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.18</v>
-      </c>
-      <c r="Z38">
-        <v>3.84</v>
-      </c>
-      <c r="AA38">
-        <v>1.71</v>
-      </c>
-      <c r="AB38">
-        <v>2.08</v>
-      </c>
-      <c r="AC38">
-        <v>2.62</v>
-      </c>
-      <c r="AD38">
-        <v>1.38</v>
-      </c>
       <c r="AE38">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG38">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.51</v>
+        <v>1.74</v>
       </c>
       <c r="O47">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="P47">
-        <v>2.56</v>
+        <v>4.46</v>
       </c>
       <c r="Q47">
-        <v>3.05</v>
+        <v>2.27</v>
       </c>
       <c r="R47">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S47">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T47">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="U47">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="V47">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="AA47">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB47">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AC47">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="AD47">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE47">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF47">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.45</v>
+        <v>2.06</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.74</v>
+        <v>2.51</v>
       </c>
       <c r="O49">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="P49">
-        <v>4.46</v>
+        <v>2.56</v>
       </c>
       <c r="Q49">
-        <v>2.27</v>
+        <v>3.05</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S49">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T49">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="V49">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z49">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="AA49">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AB49">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AC49">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="AD49">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF49">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG49">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK49">
-        <v>2.06</v>
+        <v>1.45</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>3.4</v>
       </c>
       <c r="Q54">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="R54">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S54">
         <v>1.49</v>
@@ -9141,22 +9141,22 @@
         <v>1.02</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y54">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z54">
         <v>2.58</v>
       </c>
       <c r="AA54">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="AB54">
         <v>1.56</v>
       </c>
       <c r="AC54">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD54">
         <v>1.19</v>
@@ -9165,10 +9165,10 @@
         <v>1.01</v>
       </c>
       <c r="AF54">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG54">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.32</v>
       </c>
       <c r="AK54">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9292,34 +9292,34 @@
         <v>1.56</v>
       </c>
       <c r="T55">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="U55">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V55">
         <v>1.25</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X55">
         <v>1.12</v>
       </c>
       <c r="Y55">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="Z55">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="AA55">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AB55">
         <v>1.44</v>
       </c>
       <c r="AC55">
-        <v>4.7</v>
+        <v>5.19</v>
       </c>
       <c r="AD55">
         <v>1.16</v>
@@ -9328,10 +9328,10 @@
         <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG55">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AK55">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9440,10 +9440,10 @@
         <v>1.53</v>
       </c>
       <c r="O56">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P56">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="Q56">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -2274,16 +2274,16 @@
         <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R12">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U12">
         <v>2.4</v>
@@ -2298,16 +2298,16 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AA12">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB12">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC12">
         <v>2.52</v>
@@ -2316,7 +2316,7 @@
         <v>1.41</v>
       </c>
       <c r="AE12">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF12">
         <v>1.52</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
         <v>1.65</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="O27">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P27">
-        <v>4.45</v>
+        <v>5.25</v>
       </c>
       <c r="Q27">
         <v>2.05</v>
       </c>
       <c r="R27">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S27">
         <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V27">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W27">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AA27">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB27">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AC27">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD27">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE27">
         <v>1.12</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.51</v>
+        <v>3.5</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="Q28">
-        <v>2.04</v>
+        <v>4.18</v>
       </c>
       <c r="R28">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="S28">
+        <v>1.4</v>
+      </c>
+      <c r="T28">
+        <v>2.64</v>
+      </c>
+      <c r="U28">
+        <v>2.88</v>
+      </c>
+      <c r="V28">
         <v>1.36</v>
-      </c>
-      <c r="T28">
-        <v>2.85</v>
-      </c>
-      <c r="U28">
-        <v>2.73</v>
-      </c>
-      <c r="V28">
-        <v>1.39</v>
       </c>
       <c r="W28">
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z28">
+        <v>3.14</v>
+      </c>
+      <c r="AA28">
+        <v>2</v>
+      </c>
+      <c r="AB28">
+        <v>1.8</v>
+      </c>
+      <c r="AC28">
         <v>3.28</v>
       </c>
-      <c r="AA28">
-        <v>1.92</v>
-      </c>
-      <c r="AB28">
-        <v>1.85</v>
-      </c>
-      <c r="AC28">
-        <v>3.3</v>
-      </c>
       <c r="AD28">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
         <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AG28">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.55</v>
+        <v>1.93</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="Q29">
-        <v>4.19</v>
+        <v>2.57</v>
       </c>
       <c r="R29">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="U29">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z29">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA29">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB29">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC29">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="AD29">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG29">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.76</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P30">
-        <v>1.99</v>
+        <v>3.85</v>
       </c>
       <c r="Q30">
-        <v>4.13</v>
+        <v>2.3</v>
       </c>
       <c r="R30">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="U30">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>3.14</v>
+        <v>3.65</v>
       </c>
       <c r="AA30">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AB30">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AC30">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AD30">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE30">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG30">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK30">
-        <v>1.27</v>
+        <v>2.02</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="O31">
+        <v>4.1</v>
+      </c>
+      <c r="P31">
+        <v>5.75</v>
+      </c>
+      <c r="Q31">
+        <v>2.04</v>
+      </c>
+      <c r="R31">
+        <v>2.25</v>
+      </c>
+      <c r="S31">
+        <v>1.36</v>
+      </c>
+      <c r="T31">
+        <v>2.85</v>
+      </c>
+      <c r="U31">
+        <v>2.88</v>
+      </c>
+      <c r="V31">
+        <v>1.42</v>
+      </c>
+      <c r="W31">
+        <v>1.06</v>
+      </c>
+      <c r="X31">
+        <v>1.03</v>
+      </c>
+      <c r="Y31">
+        <v>1.3</v>
+      </c>
+      <c r="Z31">
+        <v>3.28</v>
+      </c>
+      <c r="AA31">
+        <v>1.9</v>
+      </c>
+      <c r="AB31">
+        <v>1.87</v>
+      </c>
+      <c r="AC31">
         <v>3.3</v>
       </c>
-      <c r="P31">
-        <v>3.2</v>
-      </c>
-      <c r="Q31">
-        <v>2.57</v>
-      </c>
-      <c r="R31">
-        <v>2.18</v>
-      </c>
-      <c r="S31">
-        <v>1.33</v>
-      </c>
-      <c r="T31">
-        <v>2.99</v>
-      </c>
-      <c r="U31">
-        <v>2.69</v>
-      </c>
-      <c r="V31">
-        <v>1.4</v>
-      </c>
-      <c r="W31">
-        <v>1.05</v>
-      </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
-      <c r="Y31">
-        <v>1.24</v>
-      </c>
-      <c r="Z31">
-        <v>3.56</v>
-      </c>
-      <c r="AA31">
-        <v>1.88</v>
-      </c>
-      <c r="AB31">
-        <v>1.88</v>
-      </c>
-      <c r="AC31">
-        <v>3.08</v>
-      </c>
       <c r="AD31">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="AG31">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>1.72</v>
+        <v>2.46</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,28 +5525,28 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.64</v>
+        <v>3.5</v>
       </c>
       <c r="O32">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>4.6</v>
+        <v>1.98</v>
       </c>
       <c r="Q32">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="R32">
         <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
         <v>1.44</v>
@@ -5555,34 +5555,34 @@
         <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z32">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA32">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB32">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC32">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AD32">
         <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK32">
-        <v>2.07</v>
+        <v>1.25</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P33">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -5718,34 +5718,34 @@
         <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z33">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AA33">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB33">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AC33">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD33">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
         <v>1.76</v>
       </c>
       <c r="AG33">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,58 +5851,58 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.45</v>
+        <v>2.87</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="P34">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="Q34">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="R34">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA34">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB34">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AD34">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE34">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
         <v>1.56</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
         <v>1.33</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="O35">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q35">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U35">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V35">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="AA35">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AB35">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AC35">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AD35">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6183,7 +6183,7 @@
         <v>3.45</v>
       </c>
       <c r="P36">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="Q36">
         <v>2.83</v>
@@ -6192,49 +6192,49 @@
         <v>2.11</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T36">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="U36">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W36">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>3.14</v>
+        <v>2.94</v>
       </c>
       <c r="AA36">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB36">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC36">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD36">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE36">
         <v>1.04</v>
       </c>
       <c r="AF36">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG36">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
         <v>1.59</v>
@@ -6340,58 +6340,58 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.41</v>
+        <v>2.26</v>
       </c>
       <c r="O37">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P37">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="Q37">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="R37">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
         <v>1.38</v>
       </c>
       <c r="T37">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="U37">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
         <v>1.05</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z37">
-        <v>3.39</v>
+        <v>3.14</v>
       </c>
       <c r="AA37">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB37">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC37">
         <v>3.2</v>
       </c>
       <c r="AD37">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
         <v>1.73</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="O38">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="Q38">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T38">
-        <v>2.99</v>
+        <v>2.74</v>
       </c>
       <c r="U38">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V38">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AA38">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AB38">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AC38">
         <v>3.2</v>
       </c>
       <c r="AD38">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG38">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK38">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,65 +6666,65 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="Q39">
-        <v>2.37</v>
+        <v>2.78</v>
       </c>
       <c r="R39">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="T39">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="U39">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="V39">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="AA39">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AB39">
+        <v>1.8</v>
+      </c>
+      <c r="AC39">
+        <v>3.24</v>
+      </c>
+      <c r="AD39">
+        <v>1.26</v>
+      </c>
+      <c r="AE39">
+        <v>1.06</v>
+      </c>
+      <c r="AF39">
+        <v>1.75</v>
+      </c>
+      <c r="AG39">
         <v>2</v>
       </c>
-      <c r="AC39">
-        <v>2.76</v>
-      </c>
-      <c r="AD39">
-        <v>1.38</v>
-      </c>
-      <c r="AE39">
-        <v>1.1</v>
-      </c>
-      <c r="AF39">
-        <v>1.62</v>
-      </c>
-      <c r="AG39">
-        <v>2.15</v>
-      </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK39">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.21</v>
+        <v>1.86</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P40">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="Q40">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="R40">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="S40">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T40">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="U40">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V40">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z40">
-        <v>3.12</v>
+        <v>3.72</v>
       </c>
       <c r="AA40">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="AB40">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AC40">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="AD40">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF40">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG40">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK40">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
+        <v>2.28</v>
+      </c>
+      <c r="O41">
+        <v>3.4</v>
+      </c>
+      <c r="P41">
+        <v>3.04</v>
+      </c>
+      <c r="Q41">
+        <v>2.81</v>
+      </c>
+      <c r="R41">
+        <v>2.15</v>
+      </c>
+      <c r="S41">
+        <v>1.33</v>
+      </c>
+      <c r="T41">
+        <v>3</v>
+      </c>
+      <c r="U41">
+        <v>2.59</v>
+      </c>
+      <c r="V41">
+        <v>1.4</v>
+      </c>
+      <c r="W41">
+        <v>1.05</v>
+      </c>
+      <c r="X41">
+        <v>1.01</v>
+      </c>
+      <c r="Y41">
+        <v>1.24</v>
+      </c>
+      <c r="Z41">
+        <v>3.38</v>
+      </c>
+      <c r="AA41">
+        <v>1.9</v>
+      </c>
+      <c r="AB41">
         <v>1.89</v>
       </c>
-      <c r="O41">
-        <v>3.58</v>
-      </c>
-      <c r="P41">
-        <v>3.86</v>
-      </c>
-      <c r="Q41">
-        <v>2.35</v>
-      </c>
-      <c r="R41">
-        <v>2.31</v>
-      </c>
-      <c r="S41">
-        <v>1.35</v>
-      </c>
-      <c r="T41">
-        <v>2.94</v>
-      </c>
-      <c r="U41">
-        <v>2.69</v>
-      </c>
-      <c r="V41">
-        <v>1.41</v>
-      </c>
-      <c r="W41">
-        <v>1.04</v>
-      </c>
-      <c r="X41">
-        <v>1.03</v>
-      </c>
-      <c r="Y41">
+      <c r="AC41">
+        <v>3.25</v>
+      </c>
+      <c r="AD41">
+        <v>1.28</v>
+      </c>
+      <c r="AE41">
+        <v>1.11</v>
+      </c>
+      <c r="AF41">
+        <v>1.73</v>
+      </c>
+      <c r="AG41">
+        <v>2.05</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.27</v>
       </c>
-      <c r="Z41">
-        <v>3.72</v>
-      </c>
-      <c r="AA41">
-        <v>1.88</v>
-      </c>
-      <c r="AB41">
-        <v>1.96</v>
-      </c>
-      <c r="AC41">
-        <v>2.99</v>
-      </c>
-      <c r="AD41">
-        <v>1.35</v>
-      </c>
-      <c r="AE41">
-        <v>1.12</v>
-      </c>
-      <c r="AF41">
-        <v>1.71</v>
-      </c>
-      <c r="AG41">
-        <v>2.02</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.26</v>
-      </c>
       <c r="AK41">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,61 +7155,61 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="O42">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q42">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="R42">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S42">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U42">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="V42">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
+        <v>1.07</v>
+      </c>
+      <c r="X42">
         <v>1.05</v>
       </c>
-      <c r="X42">
-        <v>1.01</v>
-      </c>
       <c r="Y42">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="AA42">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AB42">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC42">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AD42">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE42">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG42">
         <v>2.1</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.65</v>
+        <v>2.47</v>
       </c>
       <c r="O43">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>4.74</v>
+        <v>2.75</v>
       </c>
       <c r="Q43">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="R43">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="U43">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="V43">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
+        <v>1.06</v>
+      </c>
+      <c r="X43">
+        <v>1.03</v>
+      </c>
+      <c r="Y43">
+        <v>1.29</v>
+      </c>
+      <c r="Z43">
+        <v>3.6</v>
+      </c>
+      <c r="AA43">
+        <v>1.9</v>
+      </c>
+      <c r="AB43">
+        <v>1.9</v>
+      </c>
+      <c r="AC43">
+        <v>3.05</v>
+      </c>
+      <c r="AD43">
+        <v>1.31</v>
+      </c>
+      <c r="AE43">
         <v>1.07</v>
       </c>
-      <c r="X43">
-        <v>1.01</v>
-      </c>
-      <c r="Y43">
-        <v>1.26</v>
-      </c>
-      <c r="Z43">
-        <v>3.35</v>
-      </c>
-      <c r="AA43">
-        <v>1.79</v>
-      </c>
-      <c r="AB43">
-        <v>1.99</v>
-      </c>
-      <c r="AC43">
-        <v>2.8</v>
-      </c>
-      <c r="AD43">
-        <v>1.34</v>
-      </c>
-      <c r="AE43">
-        <v>1.1</v>
-      </c>
       <c r="AF43">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG43">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK43">
-        <v>2.14</v>
+        <v>1.5</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P44">
-        <v>3.04</v>
+        <v>4.85</v>
       </c>
       <c r="Q44">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="R44">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S44">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T44">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="U44">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="V44">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z44">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA44">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AB44">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AC44">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD44">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG44">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK44">
-        <v>1.61</v>
+        <v>2.14</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,80 +7644,80 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O45">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P45">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q45">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="R45">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S45">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U45">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="V45">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W45">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y45">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z45">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AA45">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB45">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC45">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="AD45">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE45">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF45">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG45">
+        <v>1.95</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>1.25</v>
+      </c>
+      <c r="AK45">
         <v>2.04</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.24</v>
-      </c>
-      <c r="AK45">
-        <v>2.05</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,37 +7807,37 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="O46">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q46">
         <v>2.35</v>
       </c>
       <c r="R46">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S46">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T46">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="U46">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="V46">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W46">
         <v>1.06</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
         <v>1.25</v>
@@ -7846,22 +7846,22 @@
         <v>3.3</v>
       </c>
       <c r="AA46">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB46">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AC46">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD46">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE46">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF46">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG46">
         <v>2</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK46">
         <v>1.79</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.74</v>
+        <v>2.51</v>
       </c>
       <c r="O47">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>4.46</v>
+        <v>2.6</v>
       </c>
       <c r="Q47">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="R47">
         <v>2.2</v>
       </c>
       <c r="S47">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="U47">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V47">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z47">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="AA47">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB47">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC47">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AD47">
         <v>1.32</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF47">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AG47">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK47">
-        <v>2.06</v>
+        <v>1.49</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.42</v>
+        <v>1.7</v>
       </c>
       <c r="O48">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P48">
-        <v>2.58</v>
+        <v>3.9</v>
       </c>
       <c r="Q48">
-        <v>3.06</v>
+        <v>2.25</v>
       </c>
       <c r="R48">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
         <v>3.04</v>
       </c>
       <c r="U48">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="V48">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA48">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB48">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AC48">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="AD48">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE48">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="O49">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="R49">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S49">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T49">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="U49">
-        <v>2.82</v>
+        <v>2.54</v>
       </c>
       <c r="V49">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>3.45</v>
+        <v>3.88</v>
       </c>
       <c r="AA49">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AB49">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AC49">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AD49">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE49">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK49">
         <v>1.45</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O50">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q50">
         <v>2.4</v>
@@ -8477,47 +8477,47 @@
         <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U50">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="V50">
         <v>1.5</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA50">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB50">
+        <v>2.17</v>
+      </c>
+      <c r="AC50">
+        <v>2.7</v>
+      </c>
+      <c r="AD50">
+        <v>1.45</v>
+      </c>
+      <c r="AE50">
+        <v>1.17</v>
+      </c>
+      <c r="AF50">
+        <v>1.58</v>
+      </c>
+      <c r="AG50">
         <v>2.2</v>
       </c>
-      <c r="AC50">
-        <v>2.54</v>
-      </c>
-      <c r="AD50">
-        <v>1.41</v>
-      </c>
-      <c r="AE50">
-        <v>1.13</v>
-      </c>
-      <c r="AF50">
-        <v>1.57</v>
-      </c>
-      <c r="AG50">
-        <v>2.38</v>
-      </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK50">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="O51">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="P51">
         <v>2.54</v>
       </c>
       <c r="Q51">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="R51">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T51">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="U51">
         <v>2.85</v>
@@ -8649,31 +8649,31 @@
         <v>1.37</v>
       </c>
       <c r="W51">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA51">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB51">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC51">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="AD51">
         <v>1.3</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
         <v>1.7</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,28 +8785,28 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P52">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="Q52">
-        <v>3.66</v>
+        <v>3.56</v>
       </c>
       <c r="R52">
         <v>2.13</v>
       </c>
       <c r="S52">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>3.19</v>
+        <v>2.82</v>
       </c>
       <c r="U52">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V52">
         <v>1.43</v>
@@ -8815,7 +8815,7 @@
         <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y52">
         <v>1.22</v>
@@ -8824,25 +8824,25 @@
         <v>3.54</v>
       </c>
       <c r="AA52">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC52">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AD52">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
         <v>1.63</v>
       </c>
       <c r="AG52">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
         <v>1.36</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O53">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
         <v>2.85</v>
       </c>
       <c r="Q53">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="R53">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S53">
         <v>1.38</v>
@@ -8969,37 +8969,37 @@
         <v>2.81</v>
       </c>
       <c r="U53">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z53">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AA53">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB53">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC53">
         <v>3.1</v>
       </c>
       <c r="AD53">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE53">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF53">
         <v>1.64</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AK53">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL53">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="O25">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="P25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.55</v>
+        <v>3.5</v>
       </c>
       <c r="O27">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>5.25</v>
+        <v>2</v>
       </c>
       <c r="Q27">
-        <v>2.05</v>
+        <v>4.18</v>
       </c>
       <c r="R27">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="U27">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.85</v>
+        <v>3.14</v>
       </c>
       <c r="AA27">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
-        <v>2.59</v>
+        <v>3.28</v>
       </c>
       <c r="AD27">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG27">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
+        <v>1.93</v>
+      </c>
+      <c r="O28">
+        <v>3.6</v>
+      </c>
+      <c r="P28">
+        <v>3.3</v>
+      </c>
+      <c r="Q28">
+        <v>2.57</v>
+      </c>
+      <c r="R28">
+        <v>2.18</v>
+      </c>
+      <c r="S28">
+        <v>1.33</v>
+      </c>
+      <c r="T28">
+        <v>2.99</v>
+      </c>
+      <c r="U28">
+        <v>2.75</v>
+      </c>
+      <c r="V28">
+        <v>1.4</v>
+      </c>
+      <c r="W28">
+        <v>1.05</v>
+      </c>
+      <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>1.28</v>
+      </c>
+      <c r="Z28">
         <v>3.5</v>
       </c>
-      <c r="O28">
-        <v>3.4</v>
-      </c>
-      <c r="P28">
+      <c r="AA28">
+        <v>1.88</v>
+      </c>
+      <c r="AB28">
+        <v>1.9</v>
+      </c>
+      <c r="AC28">
+        <v>3.08</v>
+      </c>
+      <c r="AD28">
+        <v>1.28</v>
+      </c>
+      <c r="AE28">
+        <v>1.07</v>
+      </c>
+      <c r="AF28">
+        <v>1.7</v>
+      </c>
+      <c r="AG28">
         <v>2</v>
-      </c>
-      <c r="Q28">
-        <v>4.18</v>
-      </c>
-      <c r="R28">
-        <v>2.12</v>
-      </c>
-      <c r="S28">
-        <v>1.4</v>
-      </c>
-      <c r="T28">
-        <v>2.64</v>
-      </c>
-      <c r="U28">
-        <v>2.88</v>
-      </c>
-      <c r="V28">
-        <v>1.36</v>
-      </c>
-      <c r="W28">
-        <v>1.06</v>
-      </c>
-      <c r="X28">
-        <v>1</v>
-      </c>
-      <c r="Y28">
-        <v>1.27</v>
-      </c>
-      <c r="Z28">
-        <v>3.14</v>
-      </c>
-      <c r="AA28">
-        <v>2</v>
-      </c>
-      <c r="AB28">
-        <v>1.8</v>
-      </c>
-      <c r="AC28">
-        <v>3.28</v>
-      </c>
-      <c r="AD28">
-        <v>1.25</v>
-      </c>
-      <c r="AE28">
-        <v>1.06</v>
-      </c>
-      <c r="AF28">
-        <v>1.78</v>
-      </c>
-      <c r="AG28">
-        <v>1.93</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="Q29">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="R29">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V29">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z29">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA29">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB29">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC29">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK29">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="O30">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="R30">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S30">
+        <v>1.38</v>
+      </c>
+      <c r="T30">
+        <v>2.77</v>
+      </c>
+      <c r="U30">
+        <v>2.85</v>
+      </c>
+      <c r="V30">
         <v>1.36</v>
       </c>
-      <c r="T30">
-        <v>2.82</v>
-      </c>
-      <c r="U30">
-        <v>2.5</v>
-      </c>
-      <c r="V30">
-        <v>1.45</v>
-      </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z30">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AA30">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AB30">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AC30">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AD30">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="O31">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>5.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q31">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U31">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="V31">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.28</v>
+        <v>3.63</v>
       </c>
       <c r="AA31">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AB31">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC31">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>2.46</v>
+        <v>1.88</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P32">
-        <v>1.98</v>
+        <v>5.25</v>
       </c>
       <c r="Q32">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="AA32">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AC32">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AD32">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AK32">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="O33">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="P33">
-        <v>2.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>2.04</v>
       </c>
       <c r="R33">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U33">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
+        <v>3.28</v>
+      </c>
+      <c r="AA33">
+        <v>1.9</v>
+      </c>
+      <c r="AB33">
+        <v>1.87</v>
+      </c>
+      <c r="AC33">
         <v>3.3</v>
       </c>
-      <c r="AA33">
-        <v>1.94</v>
-      </c>
-      <c r="AB33">
-        <v>1.74</v>
-      </c>
-      <c r="AC33">
-        <v>3.6</v>
-      </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AG33">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.48</v>
+        <v>2.46</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="O34">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="P34">
-        <v>2.07</v>
+        <v>3.85</v>
       </c>
       <c r="Q34">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U34">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
         <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z34">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="AA34">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AC34">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AD34">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK34">
-        <v>1.33</v>
+        <v>2.02</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.84</v>
+        <v>2.87</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P35">
-        <v>3.85</v>
+        <v>2.07</v>
       </c>
       <c r="Q35">
+        <v>3.6</v>
+      </c>
+      <c r="R35">
         <v>2.3</v>
       </c>
-      <c r="R35">
+      <c r="S35">
+        <v>1.3</v>
+      </c>
+      <c r="T35">
+        <v>3.2</v>
+      </c>
+      <c r="U35">
+        <v>2.55</v>
+      </c>
+      <c r="V35">
+        <v>1.45</v>
+      </c>
+      <c r="W35">
+        <v>1.1</v>
+      </c>
+      <c r="X35">
+        <v>1.04</v>
+      </c>
+      <c r="Y35">
+        <v>1.22</v>
+      </c>
+      <c r="Z35">
+        <v>4.2</v>
+      </c>
+      <c r="AA35">
+        <v>1.67</v>
+      </c>
+      <c r="AB35">
         <v>2.15</v>
       </c>
-      <c r="S35">
+      <c r="AC35">
+        <v>2.62</v>
+      </c>
+      <c r="AD35">
+        <v>1.43</v>
+      </c>
+      <c r="AE35">
+        <v>1.13</v>
+      </c>
+      <c r="AF35">
+        <v>1.56</v>
+      </c>
+      <c r="AG35">
+        <v>2.28</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.29</v>
+      </c>
+      <c r="AK35">
         <v>1.33</v>
-      </c>
-      <c r="T35">
-        <v>3</v>
-      </c>
-      <c r="U35">
-        <v>2.66</v>
-      </c>
-      <c r="V35">
-        <v>1.41</v>
-      </c>
-      <c r="W35">
-        <v>1.05</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.25</v>
-      </c>
-      <c r="Z35">
-        <v>3.63</v>
-      </c>
-      <c r="AA35">
-        <v>1.81</v>
-      </c>
-      <c r="AB35">
-        <v>1.86</v>
-      </c>
-      <c r="AC35">
-        <v>3.14</v>
-      </c>
-      <c r="AD35">
-        <v>1.28</v>
-      </c>
-      <c r="AE35">
-        <v>1.08</v>
-      </c>
-      <c r="AF35">
-        <v>1.7</v>
-      </c>
-      <c r="AG35">
-        <v>1.97</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.25</v>
-      </c>
-      <c r="AK35">
-        <v>1.88</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,28 +7155,28 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P42">
-        <v>3.6</v>
+        <v>4.85</v>
       </c>
       <c r="Q42">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="R42">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T42">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="U42">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V42">
         <v>1.44</v>
@@ -7185,16 +7185,16 @@
         <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z42">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AA42">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB42">
         <v>2</v>
@@ -7203,16 +7203,16 @@
         <v>3</v>
       </c>
       <c r="AD42">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE42">
         <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG42">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK42">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,61 +7318,61 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="O43">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q43">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R43">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S43">
         <v>1.36</v>
       </c>
       <c r="T43">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U43">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="V43">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z43">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AA43">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB43">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC43">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AD43">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE43">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF43">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG43">
         <v>2.1</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.65</v>
+        <v>2.47</v>
       </c>
       <c r="O44">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>4.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q44">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="R44">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S44">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="U44">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="V44">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
+        <v>1.06</v>
+      </c>
+      <c r="X44">
+        <v>1.03</v>
+      </c>
+      <c r="Y44">
+        <v>1.29</v>
+      </c>
+      <c r="Z44">
+        <v>3.6</v>
+      </c>
+      <c r="AA44">
+        <v>1.9</v>
+      </c>
+      <c r="AB44">
+        <v>1.9</v>
+      </c>
+      <c r="AC44">
+        <v>3.05</v>
+      </c>
+      <c r="AD44">
+        <v>1.31</v>
+      </c>
+      <c r="AE44">
         <v>1.07</v>
       </c>
-      <c r="X44">
-        <v>1.02</v>
-      </c>
-      <c r="Y44">
-        <v>1.25</v>
-      </c>
-      <c r="Z44">
-        <v>3.8</v>
-      </c>
-      <c r="AA44">
-        <v>1.79</v>
-      </c>
-      <c r="AB44">
-        <v>2</v>
-      </c>
-      <c r="AC44">
-        <v>3</v>
-      </c>
-      <c r="AD44">
-        <v>1.34</v>
-      </c>
-      <c r="AE44">
-        <v>1.14</v>
-      </c>
       <c r="AF44">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG44">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AK44">
-        <v>2.14</v>
+        <v>1.5</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="O45">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P45">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="Q45">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="R45">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S45">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T45">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="U45">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V45">
         <v>1.42</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z45">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="AA45">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AB45">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC45">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD45">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE45">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG45">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK45">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.94</v>
+        <v>2.51</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q46">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="R46">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T46">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="U46">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="V46">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W46">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z46">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA46">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AB46">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC46">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD46">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE46">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF46">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK46">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.51</v>
+        <v>1.7</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P47">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q47">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T47">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="U47">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="V47">
+        <v>1.44</v>
+      </c>
+      <c r="W47">
+        <v>1.06</v>
+      </c>
+      <c r="X47">
+        <v>1.02</v>
+      </c>
+      <c r="Y47">
+        <v>1.18</v>
+      </c>
+      <c r="Z47">
+        <v>3.5</v>
+      </c>
+      <c r="AA47">
+        <v>1.75</v>
+      </c>
+      <c r="AB47">
+        <v>2.04</v>
+      </c>
+      <c r="AC47">
+        <v>2.67</v>
+      </c>
+      <c r="AD47">
         <v>1.4</v>
       </c>
-      <c r="W47">
-        <v>1.08</v>
-      </c>
-      <c r="X47">
-        <v>1.03</v>
-      </c>
-      <c r="Y47">
-        <v>1.28</v>
-      </c>
-      <c r="Z47">
-        <v>3.6</v>
-      </c>
-      <c r="AA47">
-        <v>1.95</v>
-      </c>
-      <c r="AB47">
-        <v>1.9</v>
-      </c>
-      <c r="AC47">
-        <v>3</v>
-      </c>
-      <c r="AD47">
-        <v>1.32</v>
-      </c>
       <c r="AE47">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AK47">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="O48">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P48">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q48">
-        <v>2.25</v>
+        <v>3.08</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T48">
         <v>3.04</v>
       </c>
       <c r="U48">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="V48">
         <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
         <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="AA48">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB48">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC48">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="AD48">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>1.96</v>
+        <v>1.45</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P49">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q49">
-        <v>3.08</v>
+        <v>2.28</v>
       </c>
       <c r="R49">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="S49">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U49">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W49">
         <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y49">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z49">
-        <v>3.88</v>
+        <v>3.54</v>
       </c>
       <c r="AA49">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AB49">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC49">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD49">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG49">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.45</v>
+        <v>2.04</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -644,16 +644,16 @@
         <v>2.37</v>
       </c>
       <c r="Q2">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="R2">
         <v>2.06</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T2">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
         <v>2.88</v>
@@ -668,28 +668,28 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z2">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA2">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB2">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE2">
         <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG2">
         <v>1.86</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AK2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -804,22 +804,22 @@
         <v>2.8</v>
       </c>
       <c r="P3">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q3">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="R3">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="S3">
         <v>1.6</v>
       </c>
       <c r="T3">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="U3">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="V3">
         <v>1.21</v>
@@ -828,13 +828,13 @@
         <v>1.01</v>
       </c>
       <c r="X3">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y3">
         <v>1.53</v>
       </c>
       <c r="Z3">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AA3">
         <v>2.7</v>
@@ -843,7 +843,7 @@
         <v>1.43</v>
       </c>
       <c r="AC3">
-        <v>5.59</v>
+        <v>4.85</v>
       </c>
       <c r="AD3">
         <v>1.11</v>
@@ -852,7 +852,7 @@
         <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG3">
         <v>1.61</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,61 +961,61 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="O4">
         <v>2.62</v>
       </c>
       <c r="P4">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q4">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="R4">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="S4">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T4">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="U4">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Y4">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z4">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AA4">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AB4">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC4">
-        <v>5.65</v>
+        <v>6</v>
       </c>
       <c r="AD4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AG4">
         <v>1.55</v>
@@ -1034,7 +1034,7 @@
         <v>1.4</v>
       </c>
       <c r="AK4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P5">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q5">
         <v>3.07</v>
@@ -1139,16 +1139,16 @@
         <v>2.04</v>
       </c>
       <c r="S5">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T5">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="U5">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W5">
         <v>1.01</v>
@@ -1181,7 +1181,7 @@
         <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK5">
         <v>1.47</v>
@@ -2283,7 +2283,7 @@
         <v>1.28</v>
       </c>
       <c r="T12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
         <v>2.4</v>
@@ -2295,7 +2295,7 @@
         <v>1.09</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
         <v>1.2</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.7</v>
+        <v>2.17</v>
       </c>
       <c r="O13">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="P13">
-        <v>1.61</v>
+        <v>2.9</v>
       </c>
       <c r="Q13">
-        <v>5.26</v>
+        <v>2.9</v>
       </c>
       <c r="R13">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="U13">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="AA13">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB13">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AC13">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AD13">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AE13">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.15</v>
+        <v>4.5</v>
       </c>
       <c r="O14">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>2.9</v>
+        <v>1.61</v>
       </c>
       <c r="Q14">
-        <v>2.84</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="S14">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z14">
-        <v>3.14</v>
+        <v>4.21</v>
       </c>
       <c r="AA14">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB14">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AC14">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AE14">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK14">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3249,7 +3249,7 @@
         <v>4.05</v>
       </c>
       <c r="P18">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="Q18">
         <v>3.12</v>
@@ -3258,7 +3258,7 @@
         <v>2.65</v>
       </c>
       <c r="S18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T18">
         <v>5.05</v>
@@ -3285,10 +3285,10 @@
         <v>1.2</v>
       </c>
       <c r="AB18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AC18">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AD18">
         <v>2.41</v>
@@ -3297,10 +3297,10 @@
         <v>1.7</v>
       </c>
       <c r="AF18">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AG18">
-        <v>4.22</v>
+        <v>2.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="AK18">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P19">
         <v>1.73</v>
       </c>
       <c r="Q19">
-        <v>4</v>
+        <v>4.57</v>
       </c>
       <c r="R19">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S19">
         <v>1.27</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U19">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W19">
         <v>1.11</v>
@@ -3448,22 +3448,22 @@
         <v>1.56</v>
       </c>
       <c r="AB19">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AC19">
         <v>2.33</v>
       </c>
       <c r="AD19">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG19">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P20">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>3.13</v>
+        <v>3.22</v>
       </c>
       <c r="R20">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="S20">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T20">
-        <v>4.4</v>
+        <v>3.88</v>
       </c>
       <c r="U20">
         <v>1.93</v>
       </c>
       <c r="V20">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3605,7 +3605,7 @@
         <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="AA20">
         <v>1.3</v>
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="O21">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P21">
-        <v>4.05</v>
+        <v>5.4</v>
       </c>
       <c r="Q21">
+        <v>2.04</v>
+      </c>
+      <c r="R21">
+        <v>2.42</v>
+      </c>
+      <c r="S21">
+        <v>1.18</v>
+      </c>
+      <c r="T21">
+        <v>3.88</v>
+      </c>
+      <c r="U21">
+        <v>1.8</v>
+      </c>
+      <c r="V21">
         <v>1.91</v>
       </c>
-      <c r="R21">
-        <v>2.7</v>
-      </c>
-      <c r="S21">
-        <v>1.19</v>
-      </c>
-      <c r="T21">
-        <v>3.82</v>
-      </c>
-      <c r="U21">
-        <v>1.87</v>
-      </c>
-      <c r="V21">
-        <v>1.85</v>
-      </c>
       <c r="W21">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3768,28 +3768,28 @@
         <v>1.04</v>
       </c>
       <c r="Z21">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="AA21">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB21">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="AC21">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AD21">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AE21">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF21">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG21">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.17</v>
       </c>
       <c r="AK21">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="O24">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="P24">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="Q24">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S24">
         <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="U24">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="V24">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W24">
         <v>1.11</v>
@@ -4257,7 +4257,7 @@
         <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA24">
         <v>1.49</v>
@@ -4266,19 +4266,19 @@
         <v>2.3</v>
       </c>
       <c r="AC24">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AD24">
         <v>1.56</v>
       </c>
       <c r="AE24">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF24">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="O25">
         <v>4.35</v>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P27">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q27">
-        <v>4.18</v>
+        <v>3.64</v>
       </c>
       <c r="R27">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
         <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U27">
         <v>2.88</v>
@@ -4740,34 +4740,34 @@
         <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z27">
-        <v>3.14</v>
+        <v>3.39</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB27">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC27">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE27">
         <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P28">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q28">
         <v>2.57</v>
@@ -4897,7 +4897,7 @@
         <v>2.75</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
         <v>1.05</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P29">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="Q29">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S29">
+        <v>1.38</v>
+      </c>
+      <c r="T29">
+        <v>2.77</v>
+      </c>
+      <c r="U29">
+        <v>2.85</v>
+      </c>
+      <c r="V29">
         <v>1.36</v>
       </c>
-      <c r="T29">
-        <v>2.88</v>
-      </c>
-      <c r="U29">
-        <v>2.5</v>
-      </c>
-      <c r="V29">
-        <v>1.44</v>
-      </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="Z29">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="AA29">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AB29">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AC29">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AD29">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AG29">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="O30">
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q30">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="R30">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="AA30">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AB30">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AC30">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="AD30">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG30">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,61 +5362,61 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P31">
+        <v>5.25</v>
+      </c>
+      <c r="Q31">
+        <v>2.03</v>
+      </c>
+      <c r="R31">
+        <v>2.38</v>
+      </c>
+      <c r="S31">
+        <v>1.3</v>
+      </c>
+      <c r="T31">
+        <v>3.2</v>
+      </c>
+      <c r="U31">
+        <v>2.41</v>
+      </c>
+      <c r="V31">
+        <v>1.49</v>
+      </c>
+      <c r="W31">
+        <v>1.08</v>
+      </c>
+      <c r="X31">
+        <v>1.05</v>
+      </c>
+      <c r="Y31">
+        <v>1.22</v>
+      </c>
+      <c r="Z31">
         <v>3.85</v>
       </c>
-      <c r="Q31">
-        <v>2.3</v>
-      </c>
-      <c r="R31">
-        <v>2.15</v>
-      </c>
-      <c r="S31">
-        <v>1.33</v>
-      </c>
-      <c r="T31">
-        <v>3</v>
-      </c>
-      <c r="U31">
-        <v>2.66</v>
-      </c>
-      <c r="V31">
-        <v>1.41</v>
-      </c>
-      <c r="W31">
-        <v>1.05</v>
-      </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
-      <c r="Y31">
-        <v>1.25</v>
-      </c>
-      <c r="Z31">
-        <v>3.63</v>
-      </c>
       <c r="AA31">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AB31">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AC31">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="AD31">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF31">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG31">
         <v>1.97</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK31">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="O32">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P32">
-        <v>5.25</v>
+        <v>3.85</v>
       </c>
       <c r="Q32">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R32">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U32">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z32">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="AA32">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AB32">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="AC32">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="AD32">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG32">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK32">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.53</v>
+        <v>3.5</v>
       </c>
       <c r="O33">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>5.75</v>
+        <v>1.98</v>
       </c>
       <c r="Q33">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="R33">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
         <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
+        <v>2.5</v>
+      </c>
+      <c r="V33">
+        <v>1.44</v>
+      </c>
+      <c r="W33">
+        <v>1.07</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.21</v>
+      </c>
+      <c r="Z33">
+        <v>3.58</v>
+      </c>
+      <c r="AA33">
+        <v>1.87</v>
+      </c>
+      <c r="AB33">
+        <v>1.95</v>
+      </c>
+      <c r="AC33">
         <v>2.88</v>
       </c>
-      <c r="V33">
-        <v>1.42</v>
-      </c>
-      <c r="W33">
-        <v>1.06</v>
-      </c>
-      <c r="X33">
-        <v>1.03</v>
-      </c>
-      <c r="Y33">
-        <v>1.3</v>
-      </c>
-      <c r="Z33">
-        <v>3.28</v>
-      </c>
-      <c r="AA33">
-        <v>1.9</v>
-      </c>
-      <c r="AB33">
-        <v>1.87</v>
-      </c>
-      <c r="AC33">
-        <v>3.3</v>
-      </c>
       <c r="AD33">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK33">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="O34">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P34">
-        <v>3.85</v>
+        <v>6.05</v>
       </c>
       <c r="Q34">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="R34">
         <v>2.25</v>
@@ -5869,47 +5869,47 @@
         <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="AA34">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AC34">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD34">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE34">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
+        <v>1.98</v>
+      </c>
+      <c r="AG34">
         <v>1.73</v>
       </c>
-      <c r="AG34">
-        <v>2</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="O35">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="P35">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q35">
-        <v>3.6</v>
+        <v>3.29</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S35">
         <v>1.3</v>
@@ -6195,7 +6195,7 @@
         <v>1.42</v>
       </c>
       <c r="T36">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U36">
         <v>2.73</v>
@@ -6204,7 +6204,7 @@
         <v>1.38</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
         <v>1.04</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK37">
         <v>1.5</v>
@@ -6512,16 +6512,16 @@
         <v>2.85</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R38">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="S38">
         <v>1.38</v>
       </c>
       <c r="T38">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="U38">
         <v>2.75</v>
@@ -6533,25 +6533,25 @@
         <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AA38">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB38">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC38">
         <v>3.2</v>
       </c>
       <c r="AD38">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE38">
         <v>1.11</v>
@@ -6560,7 +6560,7 @@
         <v>1.65</v>
       </c>
       <c r="AG38">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>2.98</v>
       </c>
       <c r="Q39">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="R39">
         <v>2.1</v>
@@ -6886,7 +6886,7 @@
         <v>1.71</v>
       </c>
       <c r="AG40">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="Q41">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="R41">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
         <v>3</v>
       </c>
       <c r="U41">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
+        <v>1.07</v>
+      </c>
+      <c r="X41">
         <v>1.05</v>
       </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
       <c r="Y41">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="AA41">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB41">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC41">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD41">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG41">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="Q43">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="R43">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
         <v>3</v>
       </c>
       <c r="U43">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V43">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z43">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="AA43">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC43">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AD43">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF43">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7487,7 +7487,7 @@
         <v>3.3</v>
       </c>
       <c r="P44">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -7554,7 +7554,7 @@
         <v>1.4</v>
       </c>
       <c r="AK44">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.94</v>
+        <v>2.51</v>
       </c>
       <c r="O45">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P45">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q45">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="R45">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S45">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="U45">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="V45">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
         <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z45">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA45">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AB45">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC45">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD45">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE45">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF45">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK45">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="O46">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q46">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="R46">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S46">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T46">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="U46">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="V46">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="AA46">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AB46">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AC46">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD46">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AE46">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O47">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P47">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q47">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="R47">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S47">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U47">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="V47">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z47">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AA47">
+        <v>1.83</v>
+      </c>
+      <c r="AB47">
+        <v>1.95</v>
+      </c>
+      <c r="AC47">
+        <v>3.1</v>
+      </c>
+      <c r="AD47">
+        <v>1.35</v>
+      </c>
+      <c r="AE47">
+        <v>1.12</v>
+      </c>
+      <c r="AF47">
         <v>1.75</v>
       </c>
-      <c r="AB47">
-        <v>2.04</v>
-      </c>
-      <c r="AC47">
-        <v>2.67</v>
-      </c>
-      <c r="AD47">
-        <v>1.4</v>
-      </c>
-      <c r="AE47">
-        <v>1.1</v>
-      </c>
-      <c r="AF47">
-        <v>1.69</v>
-      </c>
       <c r="AG47">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="O48">
         <v>3.5</v>
       </c>
       <c r="P48">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q48">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="R48">
         <v>2.16</v>
       </c>
       <c r="S48">
+        <v>1.38</v>
+      </c>
+      <c r="T48">
+        <v>2.73</v>
+      </c>
+      <c r="U48">
+        <v>2.59</v>
+      </c>
+      <c r="V48">
+        <v>1.42</v>
+      </c>
+      <c r="W48">
+        <v>1.06</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.25</v>
+      </c>
+      <c r="Z48">
+        <v>3.3</v>
+      </c>
+      <c r="AA48">
+        <v>1.89</v>
+      </c>
+      <c r="AB48">
+        <v>1.88</v>
+      </c>
+      <c r="AC48">
+        <v>3.25</v>
+      </c>
+      <c r="AD48">
         <v>1.33</v>
       </c>
-      <c r="T48">
-        <v>3.04</v>
-      </c>
-      <c r="U48">
-        <v>2.54</v>
-      </c>
-      <c r="V48">
-        <v>1.44</v>
-      </c>
-      <c r="W48">
-        <v>1.07</v>
-      </c>
-      <c r="X48">
-        <v>1.04</v>
-      </c>
-      <c r="Y48">
-        <v>1.18</v>
-      </c>
-      <c r="Z48">
-        <v>3.88</v>
-      </c>
-      <c r="AA48">
-        <v>1.74</v>
-      </c>
-      <c r="AB48">
-        <v>2.07</v>
-      </c>
-      <c r="AC48">
-        <v>2.8</v>
-      </c>
-      <c r="AD48">
-        <v>1.43</v>
-      </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG48">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK48">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O49">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P49">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q49">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R49">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U49">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="V49">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB49">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AC49">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG49">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK49">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
         <v>1.8</v>
@@ -8788,16 +8788,16 @@
         <v>2.84</v>
       </c>
       <c r="O52">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
         <v>2.27</v>
       </c>
       <c r="Q52">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="R52">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S52">
         <v>1.36</v>
@@ -8809,7 +8809,7 @@
         <v>2.6</v>
       </c>
       <c r="V52">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
         <v>1.07</v>
@@ -8830,19 +8830,19 @@
         <v>1.98</v>
       </c>
       <c r="AC52">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AD52">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE52">
         <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG52">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>3.4</v>
       </c>
       <c r="P53">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="Q53">
         <v>3.06</v>
@@ -9283,34 +9283,34 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="R55">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="S55">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="T55">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="U55">
         <v>3.4</v>
       </c>
       <c r="V55">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X55">
         <v>1.12</v>
       </c>
       <c r="Y55">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z55">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="AA55">
         <v>2.43</v>
@@ -9319,7 +9319,7 @@
         <v>1.44</v>
       </c>
       <c r="AC55">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="AD55">
         <v>1.16</v>
@@ -9328,7 +9328,7 @@
         <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG55">
         <v>1.68</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AK55">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AL55">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -641,10 +641,10 @@
         <v>3.2</v>
       </c>
       <c r="P2">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q2">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="R2">
         <v>2.06</v>
@@ -668,16 +668,16 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AA2">
         <v>2.02</v>
       </c>
       <c r="AB2">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AC2">
         <v>3.34</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O5">
         <v>3.05</v>
@@ -1145,10 +1145,10 @@
         <v>2.56</v>
       </c>
       <c r="U5">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
         <v>1.01</v>
@@ -1160,10 +1160,10 @@
         <v>1.32</v>
       </c>
       <c r="Z5">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AB5">
         <v>1.64</v>
@@ -1181,7 +1181,7 @@
         <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>1.1</v>
       </c>
       <c r="O6">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>14</v>
@@ -2437,7 +2437,7 @@
         <v>2.9</v>
       </c>
       <c r="Q13">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="R13">
         <v>2.04</v>
@@ -2461,10 +2461,10 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA13">
         <v>2</v>
@@ -2618,16 +2618,16 @@
         <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="AA14">
         <v>1.66</v>
@@ -2636,7 +2636,7 @@
         <v>2.09</v>
       </c>
       <c r="AC14">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD14">
         <v>1.39</v>
@@ -2664,7 +2664,7 @@
         <v>1.19</v>
       </c>
       <c r="AK14">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.65</v>
+        <v>1.52</v>
       </c>
       <c r="O20">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="Q20">
-        <v>3.22</v>
+        <v>2.04</v>
       </c>
       <c r="R20">
         <v>2.42</v>
       </c>
       <c r="S20">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T20">
         <v>3.88</v>
       </c>
       <c r="U20">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="V20">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="W20">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z20">
-        <v>6.05</v>
+        <v>6.9</v>
       </c>
       <c r="AA20">
         <v>1.3</v>
       </c>
       <c r="AB20">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AC20">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AD20">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AE20">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AF20">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AG20">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>1.37</v>
+        <v>2.25</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.52</v>
+        <v>2.65</v>
       </c>
       <c r="O21">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="P21">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>2.04</v>
+        <v>3.22</v>
       </c>
       <c r="R21">
         <v>2.42</v>
       </c>
       <c r="S21">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T21">
         <v>3.88</v>
       </c>
       <c r="U21">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="V21">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="W21">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z21">
-        <v>6.9</v>
+        <v>6.05</v>
       </c>
       <c r="AA21">
         <v>1.3</v>
       </c>
       <c r="AB21">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AC21">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AD21">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AE21">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AF21">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AG21">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK21">
-        <v>2.25</v>
+        <v>1.37</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O24">
         <v>4.04</v>
       </c>
       <c r="P24">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="Q24">
         <v>2.17</v>
@@ -4239,7 +4239,7 @@
         <v>1.22</v>
       </c>
       <c r="T24">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U24">
         <v>2.25</v>
@@ -4257,13 +4257,13 @@
         <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="AA24">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB24">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC24">
         <v>2.37</v>
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="N25">
+        <v>4.3</v>
+      </c>
+      <c r="O25">
         <v>4.4</v>
-      </c>
-      <c r="O25">
-        <v>4.35</v>
       </c>
       <c r="P25">
         <v>1.59</v>
@@ -4396,7 +4396,7 @@
         <v>4.49</v>
       </c>
       <c r="R25">
-        <v>2.69</v>
+        <v>2.48</v>
       </c>
       <c r="S25">
         <v>1.15</v>
@@ -4423,10 +4423,10 @@
         <v>6.8</v>
       </c>
       <c r="AA25">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB25">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AC25">
         <v>1.83</v>
@@ -4435,7 +4435,7 @@
         <v>1.94</v>
       </c>
       <c r="AE25">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AF25">
         <v>1.36</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,61 +5199,61 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P30">
+        <v>5.25</v>
+      </c>
+      <c r="Q30">
+        <v>2.03</v>
+      </c>
+      <c r="R30">
+        <v>2.38</v>
+      </c>
+      <c r="S30">
+        <v>1.3</v>
+      </c>
+      <c r="T30">
+        <v>3.2</v>
+      </c>
+      <c r="U30">
+        <v>2.41</v>
+      </c>
+      <c r="V30">
+        <v>1.49</v>
+      </c>
+      <c r="W30">
+        <v>1.08</v>
+      </c>
+      <c r="X30">
+        <v>1.05</v>
+      </c>
+      <c r="Y30">
+        <v>1.22</v>
+      </c>
+      <c r="Z30">
         <v>3.85</v>
       </c>
-      <c r="Q30">
-        <v>2.3</v>
-      </c>
-      <c r="R30">
-        <v>2.15</v>
-      </c>
-      <c r="S30">
-        <v>1.33</v>
-      </c>
-      <c r="T30">
-        <v>3</v>
-      </c>
-      <c r="U30">
-        <v>2.66</v>
-      </c>
-      <c r="V30">
-        <v>1.41</v>
-      </c>
-      <c r="W30">
-        <v>1.05</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.25</v>
-      </c>
-      <c r="Z30">
-        <v>3.63</v>
-      </c>
       <c r="AA30">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AB30">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AC30">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="AD30">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF30">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
         <v>1.97</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK30">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.55</v>
+        <v>3.5</v>
       </c>
       <c r="O31">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>5.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q31">
-        <v>2.03</v>
+        <v>4</v>
       </c>
       <c r="R31">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U31">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z31">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="AA31">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB31">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AC31">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AD31">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE31">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,16 +5525,16 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="O32">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>3.85</v>
+        <v>6.05</v>
       </c>
       <c r="Q32">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="R32">
         <v>2.25</v>
@@ -5543,46 +5543,46 @@
         <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V32">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="AA32">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB32">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AC32">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.5</v>
+        <v>1.84</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P33">
-        <v>1.98</v>
+        <v>3.85</v>
       </c>
       <c r="Q33">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="AA33">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AB33">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC33">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD33">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.48</v>
+        <v>2.26</v>
       </c>
       <c r="O34">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P34">
-        <v>6.05</v>
+        <v>2.76</v>
       </c>
       <c r="Q34">
-        <v>2.04</v>
+        <v>2.93</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="U34">
         <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
+        <v>1.27</v>
+      </c>
+      <c r="Z34">
+        <v>3.14</v>
+      </c>
+      <c r="AA34">
+        <v>1.97</v>
+      </c>
+      <c r="AB34">
+        <v>1.81</v>
+      </c>
+      <c r="AC34">
+        <v>3.2</v>
+      </c>
+      <c r="AD34">
         <v>1.3</v>
       </c>
-      <c r="Z34">
-        <v>3.28</v>
-      </c>
-      <c r="AA34">
-        <v>1.9</v>
-      </c>
-      <c r="AB34">
-        <v>1.87</v>
-      </c>
-      <c r="AC34">
-        <v>3.3</v>
-      </c>
-      <c r="AD34">
-        <v>1.32</v>
-      </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>2.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="O35">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q35">
-        <v>3.29</v>
+        <v>2.83</v>
       </c>
       <c r="R35">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
         <v>1.04</v>
       </c>
       <c r="Y35">
+        <v>1.33</v>
+      </c>
+      <c r="Z35">
+        <v>2.94</v>
+      </c>
+      <c r="AA35">
+        <v>2.05</v>
+      </c>
+      <c r="AB35">
+        <v>1.73</v>
+      </c>
+      <c r="AC35">
+        <v>3.6</v>
+      </c>
+      <c r="AD35">
         <v>1.22</v>
       </c>
-      <c r="Z35">
-        <v>4.2</v>
-      </c>
-      <c r="AA35">
-        <v>1.67</v>
-      </c>
-      <c r="AB35">
-        <v>2.15</v>
-      </c>
-      <c r="AC35">
-        <v>2.62</v>
-      </c>
-      <c r="AD35">
-        <v>1.43</v>
-      </c>
       <c r="AE35">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="AG35">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="O36">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P36">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="Q36">
-        <v>2.83</v>
+        <v>2.15</v>
       </c>
       <c r="R36">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U36">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V36">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
+        <v>1.28</v>
+      </c>
+      <c r="Z36">
+        <v>3.65</v>
+      </c>
+      <c r="AA36">
+        <v>1.83</v>
+      </c>
+      <c r="AB36">
+        <v>1.96</v>
+      </c>
+      <c r="AC36">
+        <v>3</v>
+      </c>
+      <c r="AD36">
         <v>1.33</v>
       </c>
-      <c r="Z36">
-        <v>2.94</v>
-      </c>
-      <c r="AA36">
-        <v>2.05</v>
-      </c>
-      <c r="AB36">
-        <v>1.73</v>
-      </c>
-      <c r="AC36">
-        <v>3.6</v>
-      </c>
-      <c r="AD36">
-        <v>1.22</v>
-      </c>
       <c r="AE36">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AG36">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>1.59</v>
+        <v>2.02</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>2.76</v>
+        <v>2.1</v>
       </c>
       <c r="Q37">
-        <v>2.93</v>
+        <v>3.29</v>
       </c>
       <c r="R37">
+        <v>2.17</v>
+      </c>
+      <c r="S37">
+        <v>1.3</v>
+      </c>
+      <c r="T37">
+        <v>3.2</v>
+      </c>
+      <c r="U37">
+        <v>2.55</v>
+      </c>
+      <c r="V37">
+        <v>1.45</v>
+      </c>
+      <c r="W37">
+        <v>1.1</v>
+      </c>
+      <c r="X37">
+        <v>1.04</v>
+      </c>
+      <c r="Y37">
+        <v>1.22</v>
+      </c>
+      <c r="Z37">
+        <v>4.2</v>
+      </c>
+      <c r="AA37">
+        <v>1.67</v>
+      </c>
+      <c r="AB37">
         <v>2.15</v>
       </c>
-      <c r="S37">
-        <v>1.38</v>
-      </c>
-      <c r="T37">
-        <v>2.77</v>
-      </c>
-      <c r="U37">
-        <v>2.88</v>
-      </c>
-      <c r="V37">
-        <v>1.36</v>
-      </c>
-      <c r="W37">
-        <v>1.05</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.27</v>
-      </c>
-      <c r="Z37">
-        <v>3.14</v>
-      </c>
-      <c r="AA37">
-        <v>1.97</v>
-      </c>
-      <c r="AB37">
-        <v>1.81</v>
-      </c>
       <c r="AC37">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD37">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
+        <v>1.29</v>
+      </c>
+      <c r="AK37">
         <v>1.33</v>
-      </c>
-      <c r="AK37">
-        <v>1.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,61 +6666,61 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.28</v>
+        <v>1.86</v>
       </c>
       <c r="O39">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="P39">
-        <v>2.98</v>
+        <v>3.86</v>
       </c>
       <c r="Q39">
-        <v>2.79</v>
+        <v>2.46</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S39">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="T39">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="U39">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V39">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z39">
-        <v>3.12</v>
+        <v>3.72</v>
       </c>
       <c r="AA39">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB39">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AC39">
-        <v>3.24</v>
+        <v>3.16</v>
       </c>
       <c r="AD39">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF39">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG39">
         <v>2</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.86</v>
+        <v>2.47</v>
       </c>
       <c r="O40">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>3.86</v>
+        <v>2.74</v>
       </c>
       <c r="Q40">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="R40">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.76</v>
+        <v>3.02</v>
       </c>
       <c r="U40">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="V40">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
         <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
         <v>1.29</v>
       </c>
       <c r="Z40">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="AA40">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC40">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="AD40">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE40">
         <v>1.07</v>
       </c>
       <c r="AF40">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK40">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,65 +6992,65 @@
         </is>
       </c>
       <c r="N41">
+        <v>2.28</v>
+      </c>
+      <c r="O41">
+        <v>3.25</v>
+      </c>
+      <c r="P41">
+        <v>2.98</v>
+      </c>
+      <c r="Q41">
+        <v>2.79</v>
+      </c>
+      <c r="R41">
+        <v>2.1</v>
+      </c>
+      <c r="S41">
+        <v>1.42</v>
+      </c>
+      <c r="T41">
+        <v>2.59</v>
+      </c>
+      <c r="U41">
+        <v>2.73</v>
+      </c>
+      <c r="V41">
+        <v>1.38</v>
+      </c>
+      <c r="W41">
+        <v>1.05</v>
+      </c>
+      <c r="X41">
+        <v>1.02</v>
+      </c>
+      <c r="Y41">
+        <v>1.28</v>
+      </c>
+      <c r="Z41">
+        <v>3.12</v>
+      </c>
+      <c r="AA41">
         <v>1.98</v>
       </c>
-      <c r="O41">
-        <v>3.6</v>
-      </c>
-      <c r="P41">
-        <v>3.6</v>
-      </c>
-      <c r="Q41">
-        <v>2.5</v>
-      </c>
-      <c r="R41">
-        <v>2.16</v>
-      </c>
-      <c r="S41">
-        <v>1.36</v>
-      </c>
-      <c r="T41">
-        <v>3</v>
-      </c>
-      <c r="U41">
-        <v>2.6</v>
-      </c>
-      <c r="V41">
-        <v>1.44</v>
-      </c>
-      <c r="W41">
-        <v>1.07</v>
-      </c>
-      <c r="X41">
-        <v>1.05</v>
-      </c>
-      <c r="Y41">
-        <v>1.2</v>
-      </c>
-      <c r="Z41">
-        <v>3.7</v>
-      </c>
-      <c r="AA41">
-        <v>1.78</v>
-      </c>
       <c r="AB41">
+        <v>1.8</v>
+      </c>
+      <c r="AC41">
+        <v>3.24</v>
+      </c>
+      <c r="AD41">
+        <v>1.26</v>
+      </c>
+      <c r="AE41">
+        <v>1.06</v>
+      </c>
+      <c r="AF41">
+        <v>1.75</v>
+      </c>
+      <c r="AG41">
         <v>2</v>
       </c>
-      <c r="AC41">
-        <v>3</v>
-      </c>
-      <c r="AD41">
-        <v>1.38</v>
-      </c>
-      <c r="AE41">
-        <v>1.14</v>
-      </c>
-      <c r="AF41">
-        <v>1.64</v>
-      </c>
-      <c r="AG41">
-        <v>2.1</v>
-      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK41">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="Q43">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="R43">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
         <v>3</v>
       </c>
       <c r="U43">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V43">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
+        <v>1.07</v>
+      </c>
+      <c r="X43">
         <v>1.05</v>
       </c>
-      <c r="X43">
-        <v>1.03</v>
-      </c>
       <c r="Y43">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="AA43">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB43">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC43">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD43">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF43">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG43">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="Q44">
+        <v>2.81</v>
+      </c>
+      <c r="R44">
+        <v>2.15</v>
+      </c>
+      <c r="S44">
+        <v>1.33</v>
+      </c>
+      <c r="T44">
         <v>3</v>
       </c>
-      <c r="R44">
-        <v>2.2</v>
-      </c>
-      <c r="S44">
-        <v>1.36</v>
-      </c>
-      <c r="T44">
-        <v>3.02</v>
-      </c>
       <c r="U44">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="V44">
         <v>1.4</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
         <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z44">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AA44">
         <v>1.9</v>
       </c>
       <c r="AB44">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC44">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD44">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF44">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG44">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK44">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P46">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q46">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="R46">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U46">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
         <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>3.88</v>
+        <v>4.15</v>
       </c>
       <c r="AA46">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AB46">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AC46">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD46">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE46">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF46">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG46">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O47">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P47">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q47">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R47">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T47">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U47">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="V47">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AA47">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB47">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AC47">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="AD47">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK47">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="O48">
         <v>3.5</v>
       </c>
       <c r="P48">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q48">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="R48">
         <v>2.16</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T48">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="U48">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="V48">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="AA48">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AB48">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AC48">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD48">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>1.79</v>
+        <v>1.45</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="O49">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q49">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T49">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="U49">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W49">
         <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA49">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB49">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AC49">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="AD49">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE49">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AG49">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P50">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q50">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U50">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="V50">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z50">
-        <v>4.15</v>
+        <v>3.54</v>
       </c>
       <c r="AA50">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AB50">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AC50">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AD50">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG50">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O54">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P54">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q54">
         <v>2.8</v>
@@ -9132,7 +9132,7 @@
         <v>2.54</v>
       </c>
       <c r="U54">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V54">
         <v>1.3</v>
@@ -9144,22 +9144,22 @@
         <v>1.06</v>
       </c>
       <c r="Y54">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z54">
         <v>2.58</v>
       </c>
       <c r="AA54">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AB54">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC54">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AD54">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE54">
         <v>1.01</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK54">
         <v>1.67</v>
@@ -9301,7 +9301,7 @@
         <v>1.27</v>
       </c>
       <c r="W55">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X55">
         <v>1.12</v>
@@ -9313,10 +9313,10 @@
         <v>2.53</v>
       </c>
       <c r="AA55">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="AB55">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC55">
         <v>5.18</v>
@@ -9328,7 +9328,7 @@
         <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG55">
         <v>1.68</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O56">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P56">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL56">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -3249,16 +3249,16 @@
         <v>4.05</v>
       </c>
       <c r="P18">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="Q18">
         <v>3.12</v>
       </c>
       <c r="R18">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="S18">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T18">
         <v>5.05</v>
@@ -3282,10 +3282,10 @@
         <v>10</v>
       </c>
       <c r="AA18">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AB18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AC18">
         <v>1.4</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.5</v>
+        <v>1.48</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P31">
-        <v>1.98</v>
+        <v>6.05</v>
       </c>
       <c r="Q31">
-        <v>4</v>
+        <v>2.04</v>
       </c>
       <c r="R31">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
         <v>1.36</v>
       </c>
       <c r="T31">
+        <v>2.85</v>
+      </c>
+      <c r="U31">
         <v>2.88</v>
       </c>
-      <c r="U31">
-        <v>2.5</v>
-      </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z31">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA31">
+        <v>1.9</v>
+      </c>
+      <c r="AB31">
         <v>1.87</v>
       </c>
-      <c r="AB31">
-        <v>1.95</v>
-      </c>
       <c r="AC31">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AD31">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AG31">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P32">
-        <v>6.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q32">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T32">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>3.28</v>
+        <v>2.94</v>
       </c>
       <c r="AA32">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB32">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC32">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD32">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AG32">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>2.46</v>
+        <v>1.59</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O33">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P33">
         <v>3.85</v>
       </c>
       <c r="Q33">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="R33">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
+        <v>1.36</v>
+      </c>
+      <c r="T33">
+        <v>2.82</v>
+      </c>
+      <c r="U33">
+        <v>2.5</v>
+      </c>
+      <c r="V33">
+        <v>1.45</v>
+      </c>
+      <c r="W33">
+        <v>1.07</v>
+      </c>
+      <c r="X33">
+        <v>1.02</v>
+      </c>
+      <c r="Y33">
+        <v>1.28</v>
+      </c>
+      <c r="Z33">
+        <v>3.65</v>
+      </c>
+      <c r="AA33">
+        <v>1.83</v>
+      </c>
+      <c r="AB33">
+        <v>1.96</v>
+      </c>
+      <c r="AC33">
+        <v>3</v>
+      </c>
+      <c r="AD33">
         <v>1.33</v>
       </c>
-      <c r="T33">
-        <v>3</v>
-      </c>
-      <c r="U33">
-        <v>2.66</v>
-      </c>
-      <c r="V33">
-        <v>1.41</v>
-      </c>
-      <c r="W33">
-        <v>1.05</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.25</v>
-      </c>
-      <c r="Z33">
-        <v>3.63</v>
-      </c>
-      <c r="AA33">
-        <v>1.81</v>
-      </c>
-      <c r="AB33">
-        <v>1.86</v>
-      </c>
-      <c r="AC33">
-        <v>3.14</v>
-      </c>
-      <c r="AD33">
-        <v>1.28</v>
-      </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG33">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK33">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="O34">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>2.76</v>
+        <v>3.85</v>
       </c>
       <c r="Q34">
-        <v>2.93</v>
+        <v>2.3</v>
       </c>
       <c r="R34">
         <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W34">
         <v>1.05</v>
@@ -5884,32 +5884,32 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
+        <v>3.63</v>
+      </c>
+      <c r="AA34">
+        <v>1.81</v>
+      </c>
+      <c r="AB34">
+        <v>1.86</v>
+      </c>
+      <c r="AC34">
         <v>3.14</v>
       </c>
-      <c r="AA34">
+      <c r="AD34">
+        <v>1.28</v>
+      </c>
+      <c r="AE34">
+        <v>1.08</v>
+      </c>
+      <c r="AF34">
+        <v>1.7</v>
+      </c>
+      <c r="AG34">
         <v>1.97</v>
       </c>
-      <c r="AB34">
-        <v>1.81</v>
-      </c>
-      <c r="AC34">
-        <v>3.2</v>
-      </c>
-      <c r="AD34">
-        <v>1.3</v>
-      </c>
-      <c r="AE34">
-        <v>1.1</v>
-      </c>
-      <c r="AF34">
-        <v>1.73</v>
-      </c>
-      <c r="AG34">
-        <v>2</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
+        <v>3.5</v>
+      </c>
+      <c r="O35">
+        <v>3.5</v>
+      </c>
+      <c r="P35">
+        <v>1.98</v>
+      </c>
+      <c r="Q35">
+        <v>4</v>
+      </c>
+      <c r="R35">
         <v>2.2</v>
       </c>
-      <c r="O35">
-        <v>3.45</v>
-      </c>
-      <c r="P35">
-        <v>2.95</v>
-      </c>
-      <c r="Q35">
-        <v>2.83</v>
-      </c>
-      <c r="R35">
-        <v>2.11</v>
-      </c>
       <c r="S35">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
         <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V35">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W35">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Z35">
-        <v>2.94</v>
+        <v>3.58</v>
       </c>
       <c r="AA35">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AB35">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC35">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AD35">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK35">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,61 +6177,61 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="O36">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P36">
-        <v>3.85</v>
+        <v>2.76</v>
       </c>
       <c r="Q36">
+        <v>2.93</v>
+      </c>
+      <c r="R36">
         <v>2.15</v>
       </c>
-      <c r="R36">
-        <v>2.25</v>
-      </c>
       <c r="S36">
+        <v>1.38</v>
+      </c>
+      <c r="T36">
+        <v>2.77</v>
+      </c>
+      <c r="U36">
+        <v>2.88</v>
+      </c>
+      <c r="V36">
         <v>1.36</v>
       </c>
-      <c r="T36">
-        <v>2.82</v>
-      </c>
-      <c r="U36">
-        <v>2.5</v>
-      </c>
-      <c r="V36">
-        <v>1.45</v>
-      </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>3.65</v>
+        <v>3.14</v>
       </c>
       <c r="AA36">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AB36">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AC36">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE36">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
         <v>2</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="O41">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="Q41">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="R41">
+        <v>2.16</v>
+      </c>
+      <c r="S41">
+        <v>1.36</v>
+      </c>
+      <c r="T41">
+        <v>3</v>
+      </c>
+      <c r="U41">
+        <v>2.6</v>
+      </c>
+      <c r="V41">
+        <v>1.44</v>
+      </c>
+      <c r="W41">
+        <v>1.07</v>
+      </c>
+      <c r="X41">
+        <v>1.05</v>
+      </c>
+      <c r="Y41">
+        <v>1.2</v>
+      </c>
+      <c r="Z41">
+        <v>3.7</v>
+      </c>
+      <c r="AA41">
+        <v>1.78</v>
+      </c>
+      <c r="AB41">
+        <v>2</v>
+      </c>
+      <c r="AC41">
+        <v>3</v>
+      </c>
+      <c r="AD41">
+        <v>1.38</v>
+      </c>
+      <c r="AE41">
+        <v>1.14</v>
+      </c>
+      <c r="AF41">
+        <v>1.64</v>
+      </c>
+      <c r="AG41">
         <v>2.1</v>
       </c>
-      <c r="S41">
-        <v>1.42</v>
-      </c>
-      <c r="T41">
-        <v>2.59</v>
-      </c>
-      <c r="U41">
-        <v>2.73</v>
-      </c>
-      <c r="V41">
-        <v>1.38</v>
-      </c>
-      <c r="W41">
-        <v>1.05</v>
-      </c>
-      <c r="X41">
-        <v>1.02</v>
-      </c>
-      <c r="Y41">
-        <v>1.28</v>
-      </c>
-      <c r="Z41">
-        <v>3.12</v>
-      </c>
-      <c r="AA41">
-        <v>1.98</v>
-      </c>
-      <c r="AB41">
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.25</v>
+      </c>
+      <c r="AK41">
         <v>1.8</v>
-      </c>
-      <c r="AC41">
-        <v>3.24</v>
-      </c>
-      <c r="AD41">
-        <v>1.26</v>
-      </c>
-      <c r="AE41">
-        <v>1.06</v>
-      </c>
-      <c r="AF41">
-        <v>1.75</v>
-      </c>
-      <c r="AG41">
-        <v>2</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.31</v>
-      </c>
-      <c r="AK41">
-        <v>1.57</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,58 +7155,58 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.65</v>
+        <v>2.28</v>
       </c>
       <c r="O42">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P42">
-        <v>4.85</v>
+        <v>2.98</v>
       </c>
       <c r="Q42">
-        <v>2.12</v>
+        <v>2.79</v>
       </c>
       <c r="R42">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T42">
-        <v>2.94</v>
+        <v>2.59</v>
       </c>
       <c r="U42">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z42">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="AA42">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC42">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="AD42">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF42">
         <v>1.75</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AK42">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="Q43">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="R43">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
         <v>3</v>
       </c>
       <c r="U43">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V43">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z43">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="AA43">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC43">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AD43">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF43">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.28</v>
+        <v>1.65</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P44">
-        <v>3.04</v>
+        <v>4.85</v>
       </c>
       <c r="Q44">
-        <v>2.81</v>
+        <v>2.12</v>
       </c>
       <c r="R44">
         <v>2.15</v>
       </c>
       <c r="S44">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T44">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="U44">
         <v>2.59</v>
       </c>
       <c r="V44">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W44">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z44">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="AA44">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB44">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC44">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD44">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE44">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG44">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK44">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="O46">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q46">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T46">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U46">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
         <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>4.15</v>
+        <v>3.88</v>
       </c>
       <c r="AA46">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AB46">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AC46">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD46">
+        <v>1.43</v>
+      </c>
+      <c r="AE46">
+        <v>1.13</v>
+      </c>
+      <c r="AF46">
+        <v>1.57</v>
+      </c>
+      <c r="AG46">
+        <v>2.26</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>1.29</v>
+      </c>
+      <c r="AK46">
         <v>1.45</v>
-      </c>
-      <c r="AE46">
-        <v>1.17</v>
-      </c>
-      <c r="AF46">
-        <v>1.58</v>
-      </c>
-      <c r="AG46">
-        <v>2.2</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.25</v>
-      </c>
-      <c r="AK46">
-        <v>1.8</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="O48">
         <v>3.5</v>
       </c>
       <c r="P48">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q48">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="R48">
         <v>2.16</v>
       </c>
       <c r="S48">
+        <v>1.38</v>
+      </c>
+      <c r="T48">
+        <v>2.73</v>
+      </c>
+      <c r="U48">
+        <v>2.59</v>
+      </c>
+      <c r="V48">
+        <v>1.42</v>
+      </c>
+      <c r="W48">
+        <v>1.06</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.25</v>
+      </c>
+      <c r="Z48">
+        <v>3.3</v>
+      </c>
+      <c r="AA48">
+        <v>1.89</v>
+      </c>
+      <c r="AB48">
+        <v>1.88</v>
+      </c>
+      <c r="AC48">
+        <v>3.25</v>
+      </c>
+      <c r="AD48">
         <v>1.33</v>
       </c>
-      <c r="T48">
-        <v>3.04</v>
-      </c>
-      <c r="U48">
-        <v>2.54</v>
-      </c>
-      <c r="V48">
-        <v>1.44</v>
-      </c>
-      <c r="W48">
-        <v>1.07</v>
-      </c>
-      <c r="X48">
-        <v>1.04</v>
-      </c>
-      <c r="Y48">
-        <v>1.18</v>
-      </c>
-      <c r="Z48">
-        <v>3.88</v>
-      </c>
-      <c r="AA48">
-        <v>1.74</v>
-      </c>
-      <c r="AB48">
-        <v>2.07</v>
-      </c>
-      <c r="AC48">
-        <v>2.8</v>
-      </c>
-      <c r="AD48">
-        <v>1.43</v>
-      </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG48">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK48">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P49">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q49">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="R49">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="V49">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
+        <v>1.2</v>
+      </c>
+      <c r="Z49">
+        <v>4.15</v>
+      </c>
+      <c r="AA49">
+        <v>1.67</v>
+      </c>
+      <c r="AB49">
+        <v>2.17</v>
+      </c>
+      <c r="AC49">
+        <v>2.7</v>
+      </c>
+      <c r="AD49">
+        <v>1.45</v>
+      </c>
+      <c r="AE49">
+        <v>1.17</v>
+      </c>
+      <c r="AF49">
+        <v>1.58</v>
+      </c>
+      <c r="AG49">
+        <v>2.2</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.25</v>
       </c>
-      <c r="Z49">
-        <v>3.3</v>
-      </c>
-      <c r="AA49">
-        <v>1.89</v>
-      </c>
-      <c r="AB49">
-        <v>1.88</v>
-      </c>
-      <c r="AC49">
-        <v>3.25</v>
-      </c>
-      <c r="AD49">
-        <v>1.33</v>
-      </c>
-      <c r="AE49">
-        <v>1.08</v>
-      </c>
-      <c r="AF49">
+      <c r="AK49">
         <v>1.8</v>
-      </c>
-      <c r="AG49">
-        <v>2</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.27</v>
-      </c>
-      <c r="AK49">
-        <v>1.79</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9283,28 +9283,28 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="R55">
         <v>1.98</v>
       </c>
       <c r="S55">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="T55">
         <v>2.27</v>
       </c>
       <c r="U55">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="V55">
         <v>1.27</v>
       </c>
       <c r="W55">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X55">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y55">
         <v>1.5</v>
@@ -9328,7 +9328,7 @@
         <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG55">
         <v>1.68</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK55">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AL55">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.48</v>
+        <v>2.26</v>
       </c>
       <c r="O31">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P31">
-        <v>6.05</v>
+        <v>2.76</v>
       </c>
       <c r="Q31">
-        <v>2.04</v>
+        <v>2.93</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T31">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="U31">
         <v>2.88</v>
       </c>
       <c r="V31">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
+        <v>1.27</v>
+      </c>
+      <c r="Z31">
+        <v>3.14</v>
+      </c>
+      <c r="AA31">
+        <v>1.97</v>
+      </c>
+      <c r="AB31">
+        <v>1.81</v>
+      </c>
+      <c r="AC31">
+        <v>3.2</v>
+      </c>
+      <c r="AD31">
         <v>1.3</v>
       </c>
-      <c r="Z31">
-        <v>3.28</v>
-      </c>
-      <c r="AA31">
-        <v>1.9</v>
-      </c>
-      <c r="AB31">
-        <v>1.87</v>
-      </c>
-      <c r="AC31">
-        <v>3.3</v>
-      </c>
-      <c r="AD31">
-        <v>1.32</v>
-      </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AG31">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK31">
-        <v>2.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,65 +6177,65 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.26</v>
+        <v>1.48</v>
       </c>
       <c r="O36">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P36">
-        <v>2.76</v>
+        <v>6.05</v>
       </c>
       <c r="Q36">
-        <v>2.93</v>
+        <v>2.04</v>
       </c>
       <c r="R36">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U36">
         <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA36">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AB36">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AC36">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD36">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
+        <v>1.98</v>
+      </c>
+      <c r="AG36">
         <v>1.73</v>
       </c>
-      <c r="AG36">
-        <v>2</v>
-      </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.5</v>
+        <v>2.46</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="Q41">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="R41">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
         <v>3</v>
       </c>
       <c r="U41">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z41">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="AA41">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AB41">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC41">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AD41">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AE41">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AG41">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK41">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,58 +7155,58 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.28</v>
+        <v>1.65</v>
       </c>
       <c r="O42">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P42">
-        <v>2.98</v>
+        <v>4.85</v>
       </c>
       <c r="Q42">
-        <v>2.79</v>
+        <v>2.12</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S42">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="T42">
+        <v>2.94</v>
+      </c>
+      <c r="U42">
         <v>2.59</v>
       </c>
-      <c r="U42">
-        <v>2.73</v>
-      </c>
       <c r="V42">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z42">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="AA42">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AB42">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC42">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AD42">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AE42">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
         <v>1.75</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AK42">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="Q43">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="R43">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
         <v>3</v>
       </c>
       <c r="U43">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V43">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W43">
+        <v>1.07</v>
+      </c>
+      <c r="X43">
         <v>1.05</v>
       </c>
-      <c r="X43">
-        <v>1.03</v>
-      </c>
       <c r="Y43">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="AA43">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB43">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC43">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD43">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF43">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG43">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,58 +7481,58 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.65</v>
+        <v>2.28</v>
       </c>
       <c r="O44">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
-        <v>4.85</v>
+        <v>2.98</v>
       </c>
       <c r="Q44">
-        <v>2.12</v>
+        <v>2.79</v>
       </c>
       <c r="R44">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T44">
-        <v>2.94</v>
+        <v>2.59</v>
       </c>
       <c r="U44">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="V44">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z44">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="AA44">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AB44">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC44">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="AD44">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
         <v>1.75</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AK44">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="O46">
         <v>3.5</v>
       </c>
       <c r="P46">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q46">
-        <v>3.08</v>
+        <v>2.35</v>
       </c>
       <c r="R46">
         <v>2.16</v>
       </c>
       <c r="S46">
+        <v>1.38</v>
+      </c>
+      <c r="T46">
+        <v>2.73</v>
+      </c>
+      <c r="U46">
+        <v>2.59</v>
+      </c>
+      <c r="V46">
+        <v>1.42</v>
+      </c>
+      <c r="W46">
+        <v>1.06</v>
+      </c>
+      <c r="X46">
+        <v>1.03</v>
+      </c>
+      <c r="Y46">
+        <v>1.25</v>
+      </c>
+      <c r="Z46">
+        <v>3.3</v>
+      </c>
+      <c r="AA46">
+        <v>1.89</v>
+      </c>
+      <c r="AB46">
+        <v>1.88</v>
+      </c>
+      <c r="AC46">
+        <v>3.25</v>
+      </c>
+      <c r="AD46">
         <v>1.33</v>
       </c>
-      <c r="T46">
-        <v>3.04</v>
-      </c>
-      <c r="U46">
-        <v>2.54</v>
-      </c>
-      <c r="V46">
-        <v>1.44</v>
-      </c>
-      <c r="W46">
-        <v>1.07</v>
-      </c>
-      <c r="X46">
-        <v>1.04</v>
-      </c>
-      <c r="Y46">
-        <v>1.18</v>
-      </c>
-      <c r="Z46">
-        <v>3.88</v>
-      </c>
-      <c r="AA46">
-        <v>1.74</v>
-      </c>
-      <c r="AB46">
-        <v>2.07</v>
-      </c>
-      <c r="AC46">
-        <v>2.8</v>
-      </c>
-      <c r="AD46">
-        <v>1.43</v>
-      </c>
       <c r="AE46">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF46">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG46">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK46">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="O48">
         <v>3.5</v>
       </c>
       <c r="P48">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q48">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="R48">
         <v>2.16</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T48">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="U48">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="V48">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="AA48">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AB48">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AC48">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD48">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK48">
-        <v>1.79</v>
+        <v>1.45</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>2</v>
       </c>
       <c r="S54">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T54">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="U54">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V54">
         <v>1.3</v>
@@ -9141,34 +9141,34 @@
         <v>1.02</v>
       </c>
       <c r="X54">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y54">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z54">
         <v>2.58</v>
       </c>
       <c r="AA54">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB54">
         <v>1.57</v>
       </c>
       <c r="AC54">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD54">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE54">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF54">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG54">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>3.7</v>
       </c>
       <c r="P56">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="Q56">
         <v>2.12</v>
@@ -9476,7 +9476,7 @@
         <v>3.37</v>
       </c>
       <c r="AA56">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AB56">
         <v>1.85</v>
@@ -9488,7 +9488,7 @@
         <v>1.31</v>
       </c>
       <c r="AE56">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF56">
         <v>1.87</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q2">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R2">
         <v>2.06</v>
       </c>
       <c r="S2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="U2">
         <v>2.88</v>
@@ -662,22 +662,22 @@
         <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z2">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA2">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB2">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AC2">
         <v>3.34</v>
@@ -692,7 +692,7 @@
         <v>1.76</v>
       </c>
       <c r="AG2">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -807,28 +807,28 @@
         <v>3.5</v>
       </c>
       <c r="Q3">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="R3">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="S3">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="T3">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="U3">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="V3">
         <v>1.21</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
         <v>1.53</v>
@@ -837,13 +837,13 @@
         <v>2.34</v>
       </c>
       <c r="AA3">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AB3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AC3">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="AD3">
         <v>1.11</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,61 +961,61 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="O4">
         <v>2.62</v>
       </c>
       <c r="P4">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="Q4">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="R4">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="S4">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="T4">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="U4">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Y4">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Z4">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AA4">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AB4">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="AD4">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE4">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF4">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AG4">
         <v>1.55</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
+        <v>1.41</v>
+      </c>
+      <c r="AK4">
         <v>1.4</v>
-      </c>
-      <c r="AK4">
-        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
         <v>2.75</v>
@@ -1139,7 +1139,7 @@
         <v>2.04</v>
       </c>
       <c r="S5">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
         <v>2.56</v>
@@ -1157,7 +1157,7 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
         <v>2.88</v>
@@ -1169,10 +1169,10 @@
         <v>1.64</v>
       </c>
       <c r="AC5">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD5">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
         <v>1.02</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
         <v>1.47</v>
@@ -1293,7 +1293,7 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2271,13 +2271,13 @@
         <v>3.5</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q12">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S12">
         <v>1.28</v>
@@ -2295,13 +2295,13 @@
         <v>1.09</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AA12">
         <v>1.66</v>
@@ -2310,19 +2310,19 @@
         <v>2.17</v>
       </c>
       <c r="AC12">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AD12">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE12">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG12">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>3.35</v>
       </c>
       <c r="P13">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q13">
         <v>2.91</v>
@@ -2446,7 +2446,7 @@
         <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="U13">
         <v>2.88</v>
@@ -2467,13 +2467,13 @@
         <v>3.3</v>
       </c>
       <c r="AA13">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB13">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC13">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="AD13">
         <v>1.23</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
         <v>1.55</v>
@@ -2609,7 +2609,7 @@
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U14">
         <v>2.44</v>
@@ -2618,13 +2618,13 @@
         <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
         <v>4.1</v>
@@ -2636,7 +2636,7 @@
         <v>2.09</v>
       </c>
       <c r="AC14">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AD14">
         <v>1.39</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3243,34 +3243,34 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="O18">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q18">
         <v>3.12</v>
       </c>
       <c r="R18">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="S18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T18">
         <v>5.05</v>
       </c>
       <c r="U18">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V18">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="W18">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X18">
         <v>1</v>
@@ -3285,16 +3285,16 @@
         <v>1.16</v>
       </c>
       <c r="AB18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AC18">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AD18">
         <v>2.41</v>
       </c>
       <c r="AE18">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AF18">
         <v>1.18</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.9</v>
+        <v>4.12</v>
       </c>
       <c r="O19">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="P19">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q19">
-        <v>4.57</v>
+        <v>4.41</v>
       </c>
       <c r="R19">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="S19">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U19">
         <v>2.23</v>
       </c>
       <c r="V19">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AB19">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AC19">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AD19">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF19">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AK19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.52</v>
+        <v>2.67</v>
       </c>
       <c r="O20">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>2.04</v>
+        <v>3.24</v>
       </c>
       <c r="R20">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
         <v>1.18</v>
       </c>
       <c r="T20">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="U20">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="V20">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="W20">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="AA20">
+        <v>1.33</v>
+      </c>
+      <c r="AB20">
+        <v>2.83</v>
+      </c>
+      <c r="AC20">
+        <v>1.86</v>
+      </c>
+      <c r="AD20">
+        <v>1.83</v>
+      </c>
+      <c r="AE20">
+        <v>1.32</v>
+      </c>
+      <c r="AF20">
         <v>1.3</v>
       </c>
-      <c r="AB20">
-        <v>3.14</v>
-      </c>
-      <c r="AC20">
-        <v>1.71</v>
-      </c>
-      <c r="AD20">
-        <v>2.02</v>
-      </c>
-      <c r="AE20">
-        <v>1.42</v>
-      </c>
-      <c r="AF20">
-        <v>1.33</v>
-      </c>
       <c r="AG20">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.65</v>
+        <v>1.57</v>
       </c>
       <c r="O21">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P21">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q21">
-        <v>3.22</v>
+        <v>2.03</v>
       </c>
       <c r="R21">
-        <v>2.42</v>
+        <v>2.94</v>
       </c>
       <c r="S21">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T21">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="U21">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="V21">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="W21">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z21">
-        <v>6.05</v>
+        <v>6.32</v>
       </c>
       <c r="AA21">
         <v>1.3</v>
       </c>
       <c r="AB21">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AC21">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AD21">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AE21">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AF21">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AG21">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
-        <v>1.37</v>
+        <v>2.25</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O24">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>4.13</v>
+        <v>4.25</v>
       </c>
       <c r="Q24">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="R24">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S24">
         <v>1.22</v>
@@ -4242,10 +4242,10 @@
         <v>3.8</v>
       </c>
       <c r="U24">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V24">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W24">
         <v>1.11</v>
@@ -4257,28 +4257,28 @@
         <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="AA24">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB24">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC24">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="AD24">
         <v>1.56</v>
       </c>
       <c r="AE24">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF24">
         <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O25">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P25">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q25">
-        <v>4.49</v>
+        <v>4.2</v>
       </c>
       <c r="R25">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="S25">
         <v>1.15</v>
@@ -4417,10 +4417,10 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z25">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>1.33</v>
@@ -4432,10 +4432,10 @@
         <v>1.83</v>
       </c>
       <c r="AD25">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AE25">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AF25">
         <v>1.36</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="AK25">
         <v>1.17</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="O27">
         <v>3.55</v>
@@ -4725,31 +4725,31 @@
         <v>2.05</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="U27">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
         <v>1.26</v>
       </c>
       <c r="Z27">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="AA27">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB27">
         <v>1.85</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
         <v>1.25</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,61 +4873,61 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q28">
-        <v>2.57</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T28">
-        <v>2.99</v>
+        <v>2.77</v>
       </c>
       <c r="U28">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA28">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC28">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG28">
         <v>2</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK28">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="O29">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P29">
-        <v>2.55</v>
+        <v>5.09</v>
       </c>
       <c r="Q29">
-        <v>3.1</v>
+        <v>2.04</v>
       </c>
       <c r="R29">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
       <c r="S29">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>2.77</v>
+        <v>3.16</v>
       </c>
       <c r="U29">
-        <v>2.85</v>
+        <v>2.41</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Z29">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="AA29">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB29">
+        <v>2.04</v>
+      </c>
+      <c r="AC29">
+        <v>2.59</v>
+      </c>
+      <c r="AD29">
+        <v>1.39</v>
+      </c>
+      <c r="AE29">
+        <v>1.15</v>
+      </c>
+      <c r="AF29">
         <v>1.74</v>
       </c>
-      <c r="AC29">
-        <v>3.6</v>
-      </c>
-      <c r="AD29">
-        <v>1.25</v>
-      </c>
-      <c r="AE29">
-        <v>1.06</v>
-      </c>
-      <c r="AF29">
-        <v>1.76</v>
-      </c>
       <c r="AG29">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.55</v>
+        <v>2.32</v>
       </c>
       <c r="O30">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>5.25</v>
+        <v>2.87</v>
       </c>
       <c r="Q30">
-        <v>2.03</v>
+        <v>2.99</v>
       </c>
       <c r="R30">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="U30">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="V30">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
         <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z30">
-        <v>3.85</v>
+        <v>3.39</v>
       </c>
       <c r="AA30">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AB30">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AC30">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="AD30">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AE30">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
         <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="O31">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="Q31">
-        <v>2.93</v>
+        <v>2.35</v>
       </c>
       <c r="R31">
         <v>2.15</v>
       </c>
       <c r="S31">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U31">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W31">
         <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA31">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AB31">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC31">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD31">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE31">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
+        <v>3.25</v>
+      </c>
+      <c r="O32">
+        <v>3.5</v>
+      </c>
+      <c r="P32">
+        <v>1.92</v>
+      </c>
+      <c r="Q32">
+        <v>4</v>
+      </c>
+      <c r="R32">
         <v>2.2</v>
       </c>
-      <c r="O32">
-        <v>3.45</v>
-      </c>
-      <c r="P32">
-        <v>2.95</v>
-      </c>
-      <c r="Q32">
-        <v>2.83</v>
-      </c>
-      <c r="R32">
-        <v>2.11</v>
-      </c>
       <c r="S32">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
         <v>2.88</v>
       </c>
       <c r="U32">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>2.94</v>
+        <v>3.82</v>
       </c>
       <c r="AA32">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AB32">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC32">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="O33">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q33">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="R33">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T33">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="V33">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z33">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="AA33">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB33">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AC33">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AD33">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="Q34">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="R34">
         <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="U34">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V34">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
         <v>1.05</v>
@@ -5884,31 +5884,31 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="AA34">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC34">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
         <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.5</v>
+        <v>1.52</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P35">
-        <v>1.98</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>4</v>
+        <v>2.05</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
         <v>1.36</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="U35">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="V35">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
+        <v>1.26</v>
+      </c>
+      <c r="Z35">
+        <v>3.3</v>
+      </c>
+      <c r="AA35">
+        <v>1.92</v>
+      </c>
+      <c r="AB35">
+        <v>1.85</v>
+      </c>
+      <c r="AC35">
+        <v>3.3</v>
+      </c>
+      <c r="AD35">
+        <v>1.32</v>
+      </c>
+      <c r="AE35">
+        <v>1.06</v>
+      </c>
+      <c r="AF35">
+        <v>1.99</v>
+      </c>
+      <c r="AG35">
+        <v>1.73</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.21</v>
       </c>
-      <c r="Z35">
-        <v>3.58</v>
-      </c>
-      <c r="AA35">
-        <v>1.87</v>
-      </c>
-      <c r="AB35">
-        <v>1.95</v>
-      </c>
-      <c r="AC35">
-        <v>2.88</v>
-      </c>
-      <c r="AD35">
-        <v>1.36</v>
-      </c>
-      <c r="AE35">
-        <v>1.09</v>
-      </c>
-      <c r="AF35">
-        <v>1.67</v>
-      </c>
-      <c r="AG35">
-        <v>2.08</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.27</v>
-      </c>
       <c r="AK35">
-        <v>1.25</v>
+        <v>2.43</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>6.05</v>
+        <v>4.41</v>
       </c>
       <c r="Q36">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R36">
         <v>2.25</v>
@@ -6195,46 +6195,46 @@
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U36">
+        <v>2.56</v>
+      </c>
+      <c r="V36">
+        <v>1.45</v>
+      </c>
+      <c r="W36">
+        <v>1.07</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>1.22</v>
+      </c>
+      <c r="Z36">
+        <v>3.5</v>
+      </c>
+      <c r="AA36">
+        <v>1.78</v>
+      </c>
+      <c r="AB36">
+        <v>1.96</v>
+      </c>
+      <c r="AC36">
         <v>2.88</v>
-      </c>
-      <c r="V36">
-        <v>1.42</v>
-      </c>
-      <c r="W36">
-        <v>1.06</v>
-      </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>1.3</v>
-      </c>
-      <c r="Z36">
-        <v>3.28</v>
-      </c>
-      <c r="AA36">
-        <v>1.9</v>
-      </c>
-      <c r="AB36">
-        <v>1.87</v>
-      </c>
-      <c r="AC36">
-        <v>3.3</v>
       </c>
       <c r="AD36">
         <v>1.32</v>
       </c>
       <c r="AE36">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AG36">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
+        <v>2.05</v>
+      </c>
+      <c r="Q37">
+        <v>3.62</v>
+      </c>
+      <c r="R37">
+        <v>2.26</v>
+      </c>
+      <c r="S37">
+        <v>1.28</v>
+      </c>
+      <c r="T37">
+        <v>3.28</v>
+      </c>
+      <c r="U37">
+        <v>2.41</v>
+      </c>
+      <c r="V37">
+        <v>1.49</v>
+      </c>
+      <c r="W37">
+        <v>1.07</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
+        <v>1.2</v>
+      </c>
+      <c r="Z37">
+        <v>4.1</v>
+      </c>
+      <c r="AA37">
+        <v>1.68</v>
+      </c>
+      <c r="AB37">
         <v>2.1</v>
       </c>
-      <c r="Q37">
-        <v>3.29</v>
-      </c>
-      <c r="R37">
-        <v>2.17</v>
-      </c>
-      <c r="S37">
-        <v>1.3</v>
-      </c>
-      <c r="T37">
-        <v>3.2</v>
-      </c>
-      <c r="U37">
-        <v>2.55</v>
-      </c>
-      <c r="V37">
-        <v>1.45</v>
-      </c>
-      <c r="W37">
-        <v>1.1</v>
-      </c>
-      <c r="X37">
-        <v>1.04</v>
-      </c>
-      <c r="Y37">
-        <v>1.22</v>
-      </c>
-      <c r="Z37">
-        <v>4.2</v>
-      </c>
-      <c r="AA37">
-        <v>1.67</v>
-      </c>
-      <c r="AB37">
-        <v>2.15</v>
-      </c>
       <c r="AC37">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="AD37">
         <v>1.43</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF37">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG37">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
         <v>3.5</v>
@@ -6512,52 +6512,52 @@
         <v>2.85</v>
       </c>
       <c r="Q38">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="R38">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="S38">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T38">
+        <v>2.95</v>
+      </c>
+      <c r="U38">
         <v>2.73</v>
       </c>
-      <c r="U38">
-        <v>2.75</v>
-      </c>
       <c r="V38">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X38">
         <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
         <v>3.42</v>
       </c>
       <c r="AA38">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AB38">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC38">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD38">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AG38">
         <v>2.05</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK38">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,16 +6669,16 @@
         <v>1.86</v>
       </c>
       <c r="O39">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="P39">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="Q39">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="R39">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="S39">
         <v>1.37</v>
@@ -6687,43 +6687,43 @@
         <v>2.76</v>
       </c>
       <c r="U39">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V39">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>3.72</v>
+        <v>3.54</v>
       </c>
       <c r="AA39">
         <v>1.88</v>
       </c>
       <c r="AB39">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AC39">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="AD39">
         <v>1.35</v>
       </c>
       <c r="AE39">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
         <v>1.71</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,34 +6829,34 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="Q40">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S40">
         <v>1.36</v>
       </c>
       <c r="T40">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="U40">
         <v>2.85</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
         <v>1.03</v>
@@ -6865,7 +6865,7 @@
         <v>1.29</v>
       </c>
       <c r="Z40">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA40">
         <v>1.9</v>
@@ -6874,16 +6874,16 @@
         <v>1.9</v>
       </c>
       <c r="AC40">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD40">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE40">
         <v>1.07</v>
       </c>
       <c r="AF40">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG40">
         <v>2.1</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="Q41">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="R41">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T41">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U41">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
         <v>1.05</v>
@@ -7025,31 +7025,31 @@
         <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z41">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="AA41">
         <v>1.9</v>
       </c>
       <c r="AB41">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AC41">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="AD41">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF41">
         <v>1.73</v>
       </c>
       <c r="AG41">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
         <v>1.57</v>
@@ -7155,25 +7155,25 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O42">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>4.85</v>
+        <v>4.63</v>
       </c>
       <c r="Q42">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="R42">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="S42">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="U42">
         <v>2.59</v>
@@ -7185,34 +7185,34 @@
         <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="AA42">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC42">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD42">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE42">
         <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,52 +7318,52 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P43">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q43">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="R43">
         <v>2.16</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T43">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U43">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V43">
         <v>1.44</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z43">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA43">
         <v>1.78</v>
       </c>
       <c r="AB43">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC43">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AD43">
         <v>1.38</v>
@@ -7372,10 +7372,10 @@
         <v>1.14</v>
       </c>
       <c r="AF43">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
         <v>1.8</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O44">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="Q44">
         <v>2.79</v>
@@ -7502,7 +7502,7 @@
         <v>2.59</v>
       </c>
       <c r="U44">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="V44">
         <v>1.38</v>
@@ -7523,19 +7523,19 @@
         <v>1.98</v>
       </c>
       <c r="AB44">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC44">
         <v>3.24</v>
       </c>
       <c r="AD44">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE44">
         <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
         <v>2</v>
@@ -7554,7 +7554,7 @@
         <v>1.31</v>
       </c>
       <c r="AK44">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.51</v>
+        <v>1.9</v>
       </c>
       <c r="O45">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P45">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q45">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R45">
+        <v>2.3</v>
+      </c>
+      <c r="S45">
+        <v>1.28</v>
+      </c>
+      <c r="T45">
+        <v>3.3</v>
+      </c>
+      <c r="U45">
+        <v>2.41</v>
+      </c>
+      <c r="V45">
+        <v>1.5</v>
+      </c>
+      <c r="W45">
+        <v>1.11</v>
+      </c>
+      <c r="X45">
+        <v>1.04</v>
+      </c>
+      <c r="Y45">
+        <v>1.16</v>
+      </c>
+      <c r="Z45">
+        <v>4.15</v>
+      </c>
+      <c r="AA45">
+        <v>1.68</v>
+      </c>
+      <c r="AB45">
         <v>2.2</v>
       </c>
-      <c r="S45">
-        <v>1.36</v>
-      </c>
-      <c r="T45">
-        <v>3.02</v>
-      </c>
-      <c r="U45">
+      <c r="AC45">
         <v>2.7</v>
       </c>
-      <c r="V45">
-        <v>1.4</v>
-      </c>
-      <c r="W45">
-        <v>1.08</v>
-      </c>
-      <c r="X45">
-        <v>1.03</v>
-      </c>
-      <c r="Y45">
-        <v>1.28</v>
-      </c>
-      <c r="Z45">
-        <v>3.6</v>
-      </c>
-      <c r="AA45">
-        <v>1.95</v>
-      </c>
-      <c r="AB45">
-        <v>1.9</v>
-      </c>
-      <c r="AC45">
-        <v>3</v>
-      </c>
       <c r="AD45">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AE45">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF45">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG45">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK45">
-        <v>1.49</v>
+        <v>1.86</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P46">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="Q46">
         <v>2.35</v>
       </c>
       <c r="R46">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="S46">
         <v>1.38</v>
@@ -7828,7 +7828,7 @@
         <v>2.73</v>
       </c>
       <c r="U46">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="V46">
         <v>1.42</v>
@@ -7837,7 +7837,7 @@
         <v>1.06</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
         <v>1.25</v>
@@ -7849,19 +7849,19 @@
         <v>1.89</v>
       </c>
       <c r="AB46">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC46">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AD46">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE46">
         <v>1.08</v>
       </c>
       <c r="AF46">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG46">
         <v>2</v>
@@ -7970,34 +7970,34 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O47">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="P47">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q47">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R47">
         <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T47">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="U47">
         <v>2.57</v>
       </c>
       <c r="V47">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
         <v>1.02</v>
@@ -8006,16 +8006,16 @@
         <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AA47">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB47">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC47">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="AD47">
         <v>1.4</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK47">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>2.5</v>
+        <v>4.51</v>
       </c>
       <c r="Q48">
-        <v>3.08</v>
+        <v>2.3</v>
       </c>
       <c r="R48">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S48">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T48">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U48">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W48">
         <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z48">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="AA48">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AB48">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC48">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AD48">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.45</v>
+        <v>2.06</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="O49">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P49">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U49">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
         <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA49">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB49">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC49">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD49">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE49">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AK49">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="O50">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q50">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="R50">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="S50">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T50">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="U50">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V50">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
+        <v>1.06</v>
+      </c>
+      <c r="X50">
+        <v>1.01</v>
+      </c>
+      <c r="Y50">
+        <v>1.29</v>
+      </c>
+      <c r="Z50">
+        <v>3.35</v>
+      </c>
+      <c r="AA50">
+        <v>1.95</v>
+      </c>
+      <c r="AB50">
+        <v>1.85</v>
+      </c>
+      <c r="AC50">
+        <v>3.35</v>
+      </c>
+      <c r="AD50">
+        <v>1.32</v>
+      </c>
+      <c r="AE50">
         <v>1.07</v>
       </c>
-      <c r="X50">
-        <v>1.05</v>
-      </c>
-      <c r="Y50">
-        <v>1.28</v>
-      </c>
-      <c r="Z50">
-        <v>3.54</v>
-      </c>
-      <c r="AA50">
-        <v>1.83</v>
-      </c>
-      <c r="AB50">
-        <v>1.95</v>
-      </c>
-      <c r="AC50">
-        <v>3.1</v>
-      </c>
-      <c r="AD50">
-        <v>1.35</v>
-      </c>
-      <c r="AE50">
-        <v>1.12</v>
-      </c>
       <c r="AF50">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>2.06</v>
+        <v>1.49</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="O51">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P51">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="Q51">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S51">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
         <v>2.9</v>
       </c>
       <c r="U51">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V51">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
         <v>1.06</v>
@@ -8679,7 +8679,7 @@
         <v>1.7</v>
       </c>
       <c r="AG51">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,25 +8785,25 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="O52">
         <v>3.4</v>
       </c>
       <c r="P52">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="Q52">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R52">
         <v>2.14</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T52">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
         <v>2.6</v>
@@ -8818,16 +8818,16 @@
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z52">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="AA52">
         <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC52">
         <v>2.8</v>
@@ -8836,7 +8836,7 @@
         <v>1.34</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
         <v>1.61</v>
@@ -8948,40 +8948,40 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="O53">
         <v>3.4</v>
       </c>
       <c r="P53">
-        <v>2.64</v>
+        <v>2.81</v>
       </c>
       <c r="Q53">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="R53">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="S53">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T53">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U53">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V53">
         <v>1.42</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z53">
         <v>3.44</v>
@@ -8990,16 +8990,16 @@
         <v>1.9</v>
       </c>
       <c r="AB53">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC53">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AD53">
         <v>1.37</v>
       </c>
       <c r="AE53">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
         <v>1.64</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AK53">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9126,22 +9126,22 @@
         <v>2</v>
       </c>
       <c r="S54">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T54">
         <v>2.33</v>
       </c>
       <c r="U54">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="V54">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W54">
         <v>1.02</v>
       </c>
       <c r="X54">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y54">
         <v>1.43</v>
@@ -9153,10 +9153,10 @@
         <v>2.37</v>
       </c>
       <c r="AB54">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC54">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD54">
         <v>1.19</v>
@@ -9286,13 +9286,13 @@
         <v>4.2</v>
       </c>
       <c r="R55">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="S55">
         <v>1.56</v>
       </c>
       <c r="T55">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="U55">
         <v>3.52</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AK55">
         <v>1.29</v>
@@ -9443,7 +9443,7 @@
         <v>3.7</v>
       </c>
       <c r="P56">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Q56">
         <v>2.12</v>
@@ -9467,7 +9467,7 @@
         <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
         <v>1.29</v>
@@ -9488,13 +9488,13 @@
         <v>1.31</v>
       </c>
       <c r="AE56">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF56">
         <v>1.87</v>
       </c>
       <c r="AG56">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK56">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL56">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.67</v>
+        <v>1.57</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q20">
-        <v>3.24</v>
+        <v>2.03</v>
       </c>
       <c r="R20">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="S20">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T20">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="U20">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="V20">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W20">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z20">
-        <v>5.9</v>
+        <v>6.32</v>
       </c>
       <c r="AA20">
+        <v>1.3</v>
+      </c>
+      <c r="AB20">
+        <v>3.08</v>
+      </c>
+      <c r="AC20">
+        <v>1.75</v>
+      </c>
+      <c r="AD20">
+        <v>1.96</v>
+      </c>
+      <c r="AE20">
+        <v>1.39</v>
+      </c>
+      <c r="AF20">
         <v>1.33</v>
       </c>
-      <c r="AB20">
-        <v>2.83</v>
-      </c>
-      <c r="AC20">
-        <v>1.86</v>
-      </c>
-      <c r="AD20">
-        <v>1.83</v>
-      </c>
-      <c r="AE20">
-        <v>1.32</v>
-      </c>
-      <c r="AF20">
-        <v>1.3</v>
-      </c>
       <c r="AG20">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.57</v>
+        <v>2.67</v>
       </c>
       <c r="O21">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>2.03</v>
+        <v>3.24</v>
       </c>
       <c r="R21">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="T21">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="U21">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="V21">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="W21">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>6.32</v>
+        <v>5.9</v>
       </c>
       <c r="AA21">
+        <v>1.33</v>
+      </c>
+      <c r="AB21">
+        <v>2.83</v>
+      </c>
+      <c r="AC21">
+        <v>1.86</v>
+      </c>
+      <c r="AD21">
+        <v>1.83</v>
+      </c>
+      <c r="AE21">
+        <v>1.32</v>
+      </c>
+      <c r="AF21">
         <v>1.3</v>
       </c>
-      <c r="AB21">
-        <v>3.08</v>
-      </c>
-      <c r="AC21">
-        <v>1.75</v>
-      </c>
-      <c r="AD21">
-        <v>1.96</v>
-      </c>
-      <c r="AE21">
-        <v>1.39</v>
-      </c>
-      <c r="AF21">
-        <v>1.33</v>
-      </c>
       <c r="AG21">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.33</v>
+        <v>1.53</v>
       </c>
       <c r="O27">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>1.96</v>
+        <v>5.09</v>
       </c>
       <c r="Q27">
-        <v>3.64</v>
+        <v>2.04</v>
       </c>
       <c r="R27">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="U27">
-        <v>2.9</v>
+        <v>2.41</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W27">
+        <v>1.08</v>
+      </c>
+      <c r="X27">
         <v>1.04</v>
       </c>
-      <c r="X27">
-        <v>1.02</v>
-      </c>
       <c r="Y27">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="AA27">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB27">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC27">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AD27">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG27">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="O28">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="P28">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="R28">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="U28">
-        <v>2.98</v>
+        <v>2.73</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z28">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA28">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AB28">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC28">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD28">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AE28">
         <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>1.39</v>
+        <v>2.43</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="O29">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>5.09</v>
+        <v>3.8</v>
       </c>
       <c r="Q29">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="R29">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="U29">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AA29">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB29">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AD29">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
         <v>1.74</v>
       </c>
       <c r="AG29">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="Q30">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="R30">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="U30">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V30">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z30">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="AA30">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AB30">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC30">
         <v>3.2</v>
       </c>
       <c r="AD30">
+        <v>1.27</v>
+      </c>
+      <c r="AE30">
+        <v>1.07</v>
+      </c>
+      <c r="AF30">
+        <v>1.7</v>
+      </c>
+      <c r="AG30">
+        <v>2</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.26</v>
       </c>
-      <c r="AE30">
-        <v>1.06</v>
-      </c>
-      <c r="AF30">
-        <v>1.75</v>
-      </c>
-      <c r="AG30">
-        <v>2.05</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.25</v>
-      </c>
       <c r="AK30">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.76</v>
+        <v>3.25</v>
       </c>
       <c r="O31">
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>3.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q31">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="R31">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U31">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="V31">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
         <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA31">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB31">
         <v>1.95</v>
       </c>
       <c r="AC31">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD31">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE31">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
+        <v>1.19</v>
+      </c>
+      <c r="AK31">
         <v>1.25</v>
-      </c>
-      <c r="AK31">
-        <v>1.91</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>1.92</v>
+        <v>2.87</v>
       </c>
       <c r="Q32">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U32">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>3.82</v>
+        <v>3.39</v>
       </c>
       <c r="AA32">
+        <v>1.97</v>
+      </c>
+      <c r="AB32">
         <v>1.81</v>
       </c>
-      <c r="AB32">
-        <v>1.95</v>
-      </c>
       <c r="AC32">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.2</v>
+        <v>3.33</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P33">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q33">
-        <v>2.88</v>
+        <v>3.64</v>
       </c>
       <c r="R33">
         <v>2.05</v>
       </c>
       <c r="S33">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U33">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="V33">
         <v>1.38</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z33">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="AA33">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AB33">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC33">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG33">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK33">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q34">
+        <v>2.88</v>
+      </c>
+      <c r="R34">
+        <v>2.05</v>
+      </c>
+      <c r="S34">
+        <v>1.42</v>
+      </c>
+      <c r="T34">
+        <v>2.88</v>
+      </c>
+      <c r="U34">
         <v>2.73</v>
       </c>
-      <c r="R34">
-        <v>2.15</v>
-      </c>
-      <c r="S34">
-        <v>1.36</v>
-      </c>
-      <c r="T34">
-        <v>2.98</v>
-      </c>
-      <c r="U34">
-        <v>2.75</v>
-      </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W34">
+        <v>1.03</v>
+      </c>
+      <c r="X34">
         <v>1.05</v>
       </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
       <c r="Y34">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="AA34">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD34">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="O35">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>6</v>
+        <v>4.41</v>
       </c>
       <c r="Q35">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="R35">
         <v>2.25</v>
@@ -6032,46 +6032,46 @@
         <v>1.36</v>
       </c>
       <c r="T35">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="V35">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA35">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC35">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD35">
         <v>1.32</v>
       </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="AG35">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,61 +6177,61 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="O36">
+        <v>3.25</v>
+      </c>
+      <c r="P36">
+        <v>2.6</v>
+      </c>
+      <c r="Q36">
+        <v>3.1</v>
+      </c>
+      <c r="R36">
+        <v>2.09</v>
+      </c>
+      <c r="S36">
+        <v>1.38</v>
+      </c>
+      <c r="T36">
+        <v>2.77</v>
+      </c>
+      <c r="U36">
+        <v>2.98</v>
+      </c>
+      <c r="V36">
+        <v>1.37</v>
+      </c>
+      <c r="W36">
+        <v>1.06</v>
+      </c>
+      <c r="X36">
+        <v>1.03</v>
+      </c>
+      <c r="Y36">
+        <v>1.3</v>
+      </c>
+      <c r="Z36">
+        <v>3.4</v>
+      </c>
+      <c r="AA36">
+        <v>2.02</v>
+      </c>
+      <c r="AB36">
+        <v>1.8</v>
+      </c>
+      <c r="AC36">
         <v>3.6</v>
       </c>
-      <c r="P36">
-        <v>4.41</v>
-      </c>
-      <c r="Q36">
-        <v>2.2</v>
-      </c>
-      <c r="R36">
-        <v>2.25</v>
-      </c>
-      <c r="S36">
-        <v>1.36</v>
-      </c>
-      <c r="T36">
-        <v>3.2</v>
-      </c>
-      <c r="U36">
-        <v>2.56</v>
-      </c>
-      <c r="V36">
-        <v>1.45</v>
-      </c>
-      <c r="W36">
-        <v>1.07</v>
-      </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.22</v>
-      </c>
-      <c r="Z36">
-        <v>3.5</v>
-      </c>
-      <c r="AA36">
-        <v>1.78</v>
-      </c>
-      <c r="AB36">
-        <v>1.96</v>
-      </c>
-      <c r="AC36">
-        <v>2.88</v>
-      </c>
       <c r="AD36">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
         <v>2</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK36">
-        <v>2</v>
+        <v>1.39</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,61 +6829,61 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.55</v>
+        <v>1.67</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P40">
-        <v>2.75</v>
+        <v>4.63</v>
       </c>
       <c r="Q40">
-        <v>3.12</v>
+        <v>2.23</v>
       </c>
       <c r="R40">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>2.73</v>
+        <v>3.05</v>
       </c>
       <c r="U40">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="V40">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
         <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="AA40">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB40">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AC40">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD40">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE40">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
         <v>2.1</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.45</v>
+        <v>2.16</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q41">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="R41">
         <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T41">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U41">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W41">
         <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
         <v>1.28</v>
       </c>
       <c r="Z41">
-        <v>3.67</v>
+        <v>3.12</v>
       </c>
       <c r="AA41">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB41">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC41">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="AD41">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE41">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG41">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK41">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,25 +7155,25 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>4.63</v>
+        <v>3.65</v>
       </c>
       <c r="Q42">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="R42">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="S42">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T42">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="U42">
         <v>2.59</v>
@@ -7182,25 +7182,25 @@
         <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA42">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB42">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC42">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
         <v>1.38</v>
@@ -7209,10 +7209,10 @@
         <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="O43">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>3.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q43">
-        <v>2.37</v>
+        <v>3.12</v>
       </c>
       <c r="R43">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S43">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="U43">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="V43">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="AA43">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AB43">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC43">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="AD43">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF43">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG43">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q44">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="R44">
         <v>2.1</v>
       </c>
       <c r="S44">
+        <v>1.39</v>
+      </c>
+      <c r="T44">
+        <v>2.7</v>
+      </c>
+      <c r="U44">
+        <v>2.8</v>
+      </c>
+      <c r="V44">
         <v>1.42</v>
-      </c>
-      <c r="T44">
-        <v>2.59</v>
-      </c>
-      <c r="U44">
-        <v>2.94</v>
-      </c>
-      <c r="V44">
-        <v>1.38</v>
       </c>
       <c r="W44">
         <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
         <v>1.28</v>
       </c>
       <c r="Z44">
-        <v>3.12</v>
+        <v>3.67</v>
       </c>
       <c r="AA44">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB44">
+        <v>1.87</v>
+      </c>
+      <c r="AC44">
+        <v>3.23</v>
+      </c>
+      <c r="AD44">
+        <v>1.34</v>
+      </c>
+      <c r="AE44">
+        <v>1.07</v>
+      </c>
+      <c r="AF44">
         <v>1.73</v>
       </c>
-      <c r="AC44">
-        <v>3.24</v>
-      </c>
-      <c r="AD44">
+      <c r="AG44">
+        <v>2.1</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
         <v>1.29</v>
       </c>
-      <c r="AE44">
-        <v>1.06</v>
-      </c>
-      <c r="AF44">
-        <v>1.8</v>
-      </c>
-      <c r="AG44">
-        <v>2</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.31</v>
-      </c>
       <c r="AK44">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="O45">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P45">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q45">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="R45">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S45">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="U45">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="V45">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z45">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA45">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB45">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC45">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD45">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE45">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF45">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG45">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="AK45">
-        <v>1.86</v>
+        <v>1.41</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="O46">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="P46">
-        <v>3.61</v>
+        <v>4.51</v>
       </c>
       <c r="Q46">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R46">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S46">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T46">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="U46">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="V46">
         <v>1.42</v>
       </c>
       <c r="W46">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z46">
         <v>3.3</v>
       </c>
       <c r="AA46">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AB46">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC46">
-        <v>3.08</v>
+        <v>2.84</v>
       </c>
       <c r="AD46">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE46">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF46">
         <v>1.75</v>
       </c>
       <c r="AG46">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="O47">
-        <v>3.74</v>
+        <v>3.54</v>
       </c>
       <c r="P47">
-        <v>4.6</v>
+        <v>3.61</v>
       </c>
       <c r="Q47">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="R47">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S47">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T47">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="U47">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="V47">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W47">
+        <v>1.06</v>
+      </c>
+      <c r="X47">
+        <v>1.01</v>
+      </c>
+      <c r="Y47">
+        <v>1.25</v>
+      </c>
+      <c r="Z47">
+        <v>3.3</v>
+      </c>
+      <c r="AA47">
+        <v>1.89</v>
+      </c>
+      <c r="AB47">
+        <v>1.9</v>
+      </c>
+      <c r="AC47">
+        <v>3.08</v>
+      </c>
+      <c r="AD47">
+        <v>1.28</v>
+      </c>
+      <c r="AE47">
         <v>1.08</v>
       </c>
-      <c r="X47">
-        <v>1.02</v>
-      </c>
-      <c r="Y47">
-        <v>1.18</v>
-      </c>
-      <c r="Z47">
-        <v>3.85</v>
-      </c>
-      <c r="AA47">
-        <v>1.72</v>
-      </c>
-      <c r="AB47">
-        <v>2.07</v>
-      </c>
-      <c r="AC47">
-        <v>2.72</v>
-      </c>
-      <c r="AD47">
-        <v>1.4</v>
-      </c>
-      <c r="AE47">
-        <v>1.1</v>
-      </c>
       <c r="AF47">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AK47">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,65 +8133,65 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="P48">
-        <v>4.51</v>
+        <v>4.6</v>
       </c>
       <c r="Q48">
+        <v>2.15</v>
+      </c>
+      <c r="R48">
         <v>2.3</v>
       </c>
-      <c r="R48">
+      <c r="S48">
+        <v>1.33</v>
+      </c>
+      <c r="T48">
+        <v>3.02</v>
+      </c>
+      <c r="U48">
+        <v>2.57</v>
+      </c>
+      <c r="V48">
+        <v>1.47</v>
+      </c>
+      <c r="W48">
+        <v>1.08</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>1.18</v>
+      </c>
+      <c r="Z48">
+        <v>3.85</v>
+      </c>
+      <c r="AA48">
+        <v>1.72</v>
+      </c>
+      <c r="AB48">
+        <v>2.07</v>
+      </c>
+      <c r="AC48">
+        <v>2.72</v>
+      </c>
+      <c r="AD48">
+        <v>1.4</v>
+      </c>
+      <c r="AE48">
+        <v>1.1</v>
+      </c>
+      <c r="AF48">
+        <v>1.61</v>
+      </c>
+      <c r="AG48">
         <v>2.12</v>
       </c>
-      <c r="S48">
-        <v>1.34</v>
-      </c>
-      <c r="T48">
-        <v>3.1</v>
-      </c>
-      <c r="U48">
-        <v>2.6</v>
-      </c>
-      <c r="V48">
-        <v>1.42</v>
-      </c>
-      <c r="W48">
-        <v>1.07</v>
-      </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>1.27</v>
-      </c>
-      <c r="Z48">
-        <v>3.3</v>
-      </c>
-      <c r="AA48">
-        <v>1.81</v>
-      </c>
-      <c r="AB48">
-        <v>1.95</v>
-      </c>
-      <c r="AC48">
-        <v>2.84</v>
-      </c>
-      <c r="AD48">
-        <v>1.32</v>
-      </c>
-      <c r="AE48">
-        <v>1.09</v>
-      </c>
-      <c r="AF48">
-        <v>1.75</v>
-      </c>
-      <c r="AG48">
-        <v>1.94</v>
-      </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK48">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="O49">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P49">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q49">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="R49">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T49">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="V49">
+        <v>1.5</v>
+      </c>
+      <c r="W49">
+        <v>1.11</v>
+      </c>
+      <c r="X49">
+        <v>1.04</v>
+      </c>
+      <c r="Y49">
+        <v>1.16</v>
+      </c>
+      <c r="Z49">
+        <v>4.15</v>
+      </c>
+      <c r="AA49">
+        <v>1.68</v>
+      </c>
+      <c r="AB49">
+        <v>2.2</v>
+      </c>
+      <c r="AC49">
+        <v>2.7</v>
+      </c>
+      <c r="AD49">
         <v>1.45</v>
       </c>
-      <c r="W49">
-        <v>1.07</v>
-      </c>
-      <c r="X49">
-        <v>1.03</v>
-      </c>
-      <c r="Y49">
-        <v>1.2</v>
-      </c>
-      <c r="Z49">
-        <v>4.2</v>
-      </c>
-      <c r="AA49">
-        <v>1.7</v>
-      </c>
-      <c r="AB49">
-        <v>2.1</v>
-      </c>
-      <c r="AC49">
-        <v>2.8</v>
-      </c>
-      <c r="AD49">
-        <v>1.43</v>
-      </c>
       <c r="AE49">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AK49">
-        <v>1.41</v>
+        <v>1.86</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="R2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U2">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
         <v>1.04</v>
@@ -668,31 +668,31 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="AA2">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AB2">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC2">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AD2">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AG2">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="O5">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P5">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q5">
-        <v>3.07</v>
+        <v>3.41</v>
       </c>
       <c r="R5">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="S5">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="T5">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="U5">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z5">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AA5">
-        <v>2.12</v>
+        <v>2.49</v>
       </c>
       <c r="AB5">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AD5">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AE5">
         <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AG5">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK5">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1459,22 +1459,22 @@
         <v>2.1</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1483,31 +1483,31 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,40 +1622,40 @@
         <v>4.42</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W8">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1667,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,22 +1785,22 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -1809,31 +1809,31 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2428,52 +2428,52 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O13">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="R13">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="V13">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA13">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC13">
-        <v>3.45</v>
+        <v>3.61</v>
       </c>
       <c r="AD13">
         <v>1.23</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="P14">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="R14">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T14">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U14">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="V14">
+        <v>1.56</v>
+      </c>
+      <c r="W14">
+        <v>1.11</v>
+      </c>
+      <c r="X14">
+        <v>1.01</v>
+      </c>
+      <c r="Y14">
+        <v>1.17</v>
+      </c>
+      <c r="Z14">
+        <v>4.2</v>
+      </c>
+      <c r="AA14">
+        <v>1.6</v>
+      </c>
+      <c r="AB14">
+        <v>2.25</v>
+      </c>
+      <c r="AC14">
+        <v>2.55</v>
+      </c>
+      <c r="AD14">
         <v>1.46</v>
       </c>
-      <c r="W14">
-        <v>1.07</v>
-      </c>
-      <c r="X14">
-        <v>1.03</v>
-      </c>
-      <c r="Y14">
-        <v>1.16</v>
-      </c>
-      <c r="Z14">
-        <v>4.1</v>
-      </c>
-      <c r="AA14">
-        <v>1.66</v>
-      </c>
-      <c r="AB14">
-        <v>2.09</v>
-      </c>
-      <c r="AC14">
-        <v>2.59</v>
-      </c>
-      <c r="AD14">
-        <v>1.39</v>
-      </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF14">
         <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK14">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P18">
         <v>2.15</v>
@@ -3258,19 +3258,19 @@
         <v>2.65</v>
       </c>
       <c r="S18">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T18">
         <v>5.05</v>
       </c>
       <c r="U18">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V18">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="W18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X18">
         <v>1</v>
@@ -3285,7 +3285,7 @@
         <v>1.16</v>
       </c>
       <c r="AB18">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AC18">
         <v>1.45</v>
@@ -3294,10 +3294,10 @@
         <v>2.41</v>
       </c>
       <c r="AE18">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AF18">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AG18">
         <v>2.8</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.68</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="O19">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q19">
-        <v>4.41</v>
+        <v>4</v>
       </c>
       <c r="R19">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
         <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U19">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
         <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA19">
         <v>1.52</v>
       </c>
       <c r="AB19">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AC19">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AD19">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AE19">
         <v>1.22</v>
       </c>
       <c r="AF19">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG19">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
         <v>1.22</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="O20">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>4.33</v>
+        <v>2.37</v>
       </c>
       <c r="Q20">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="R20">
-        <v>2.94</v>
+        <v>2.27</v>
       </c>
       <c r="S20">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="T20">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U20">
-        <v>1.84</v>
+        <v>2.13</v>
       </c>
       <c r="V20">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="W20">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Z20">
-        <v>6.32</v>
+        <v>5.4</v>
       </c>
       <c r="AA20">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AB20">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="AC20">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD20">
-        <v>1.96</v>
+        <v>1.54</v>
       </c>
       <c r="AE20">
+        <v>1.22</v>
+      </c>
+      <c r="AF20">
         <v>1.39</v>
       </c>
-      <c r="AF20">
-        <v>1.33</v>
-      </c>
       <c r="AG20">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="O21">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q21">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="R21">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="U21">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="V21">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="W21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>5.9</v>
+        <v>6.33</v>
       </c>
       <c r="AA21">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB21">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AC21">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AD21">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE21">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AF21">
         <v>1.3</v>
       </c>
       <c r="AG21">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AK21">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
+        <v>1.57</v>
+      </c>
+      <c r="O22">
         <v>3.9</v>
       </c>
-      <c r="O22">
-        <v>3.7</v>
-      </c>
       <c r="P22">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>4.2</v>
+      </c>
+      <c r="O23">
+        <v>3.9</v>
+      </c>
+      <c r="P23">
+        <v>1.61</v>
+      </c>
+      <c r="Q23">
+        <v>4.3</v>
+      </c>
+      <c r="R23">
         <v>2.45</v>
       </c>
-      <c r="O23">
-        <v>3.6</v>
-      </c>
-      <c r="P23">
-        <v>2.3</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.53</v>
+        <v>2.32</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>5.09</v>
+        <v>2.87</v>
       </c>
       <c r="Q27">
-        <v>2.04</v>
+        <v>2.99</v>
       </c>
       <c r="R27">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>3.16</v>
+        <v>2.66</v>
       </c>
       <c r="U27">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="V27">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
         <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>3.85</v>
+        <v>3.39</v>
       </c>
       <c r="AA27">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AB27">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AC27">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="AD27">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="O28">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>6</v>
+        <v>4.41</v>
       </c>
       <c r="Q28">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="R28">
         <v>2.25</v>
@@ -4891,46 +4891,46 @@
         <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA28">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AB28">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC28">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD28">
         <v>1.32</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,65 +5036,65 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="O29">
         <v>3.5</v>
       </c>
       <c r="P29">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q29">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
+        <v>1.42</v>
+      </c>
+      <c r="T29">
+        <v>2.88</v>
+      </c>
+      <c r="U29">
+        <v>2.73</v>
+      </c>
+      <c r="V29">
+        <v>1.38</v>
+      </c>
+      <c r="W29">
+        <v>1.03</v>
+      </c>
+      <c r="X29">
+        <v>1.05</v>
+      </c>
+      <c r="Y29">
         <v>1.33</v>
       </c>
-      <c r="T29">
-        <v>3</v>
-      </c>
-      <c r="U29">
-        <v>2.75</v>
-      </c>
-      <c r="V29">
-        <v>1.42</v>
-      </c>
-      <c r="W29">
-        <v>1.05</v>
-      </c>
-      <c r="X29">
-        <v>1.04</v>
-      </c>
-      <c r="Y29">
-        <v>1.22</v>
-      </c>
       <c r="Z29">
+        <v>2.94</v>
+      </c>
+      <c r="AA29">
+        <v>2.05</v>
+      </c>
+      <c r="AB29">
+        <v>1.75</v>
+      </c>
+      <c r="AC29">
         <v>3.5</v>
       </c>
-      <c r="AA29">
-        <v>1.85</v>
-      </c>
-      <c r="AB29">
+      <c r="AD29">
+        <v>1.29</v>
+      </c>
+      <c r="AE29">
+        <v>1.08</v>
+      </c>
+      <c r="AF29">
+        <v>1.75</v>
+      </c>
+      <c r="AG29">
         <v>1.95</v>
       </c>
-      <c r="AC29">
-        <v>3.1</v>
-      </c>
-      <c r="AD29">
-        <v>1.36</v>
-      </c>
-      <c r="AE29">
-        <v>1.07</v>
-      </c>
-      <c r="AF29">
-        <v>1.74</v>
-      </c>
-      <c r="AG29">
-        <v>1.94</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q30">
-        <v>2.73</v>
+        <v>2.35</v>
       </c>
       <c r="R30">
         <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="U30">
         <v>2.75</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W30">
         <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA30">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB30">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC30">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD30">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE30">
         <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,49 +5525,49 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.32</v>
+        <v>3.33</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P32">
-        <v>2.87</v>
+        <v>1.96</v>
       </c>
       <c r="Q32">
-        <v>2.99</v>
+        <v>3.64</v>
       </c>
       <c r="R32">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="U32">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="V32">
         <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z32">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="AA32">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AB32">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC32">
         <v>3.2</v>
@@ -5579,10 +5579,10 @@
         <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
+        <v>1.21</v>
+      </c>
+      <c r="AK32">
         <v>1.25</v>
-      </c>
-      <c r="AK32">
-        <v>1.45</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.33</v>
+        <v>1.53</v>
       </c>
       <c r="O33">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P33">
-        <v>1.96</v>
+        <v>5.09</v>
       </c>
       <c r="Q33">
-        <v>3.64</v>
+        <v>2.04</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="U33">
-        <v>2.9</v>
+        <v>2.41</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W33">
+        <v>1.08</v>
+      </c>
+      <c r="X33">
         <v>1.04</v>
       </c>
-      <c r="X33">
-        <v>1.02</v>
-      </c>
       <c r="Y33">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z33">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="AA33">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AD33">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG33">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AK33">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q34">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="R34">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="U34">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V34">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>2.94</v>
+        <v>3.55</v>
       </c>
       <c r="AA34">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC34">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P35">
-        <v>4.41</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="R35">
         <v>2.25</v>
@@ -6032,46 +6032,46 @@
         <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="U35">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z35">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA35">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AB35">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AD35">
         <v>1.32</v>
       </c>
       <c r="AE35">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK35">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6666,46 +6666,46 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="O39">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
         <v>3.9</v>
       </c>
       <c r="Q39">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="R39">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="U39">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V39">
         <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y39">
         <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AA39">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB39">
         <v>1.92</v>
@@ -6714,16 +6714,16 @@
         <v>3.1</v>
       </c>
       <c r="AD39">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF39">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG39">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,77 +6832,77 @@
         <v>1.67</v>
       </c>
       <c r="O40">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
-        <v>4.63</v>
+        <v>4.75</v>
       </c>
       <c r="Q40">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="R40">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="U40">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
         <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>3.54</v>
+        <v>4.1</v>
       </c>
       <c r="AA40">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AB40">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC40">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AD40">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE40">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG40">
+        <v>2</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.18</v>
+      </c>
+      <c r="AK40">
         <v>2.1</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.24</v>
-      </c>
-      <c r="AK40">
-        <v>2.16</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O41">
+        <v>3.4</v>
+      </c>
+      <c r="P41">
+        <v>3</v>
+      </c>
+      <c r="Q41">
+        <v>2.9</v>
+      </c>
+      <c r="R41">
+        <v>2.26</v>
+      </c>
+      <c r="S41">
+        <v>1.35</v>
+      </c>
+      <c r="T41">
+        <v>2.85</v>
+      </c>
+      <c r="U41">
+        <v>2.84</v>
+      </c>
+      <c r="V41">
+        <v>1.41</v>
+      </c>
+      <c r="W41">
+        <v>1.04</v>
+      </c>
+      <c r="X41">
+        <v>1.03</v>
+      </c>
+      <c r="Y41">
+        <v>1.25</v>
+      </c>
+      <c r="Z41">
         <v>3.3</v>
       </c>
-      <c r="P41">
-        <v>3.1</v>
-      </c>
-      <c r="Q41">
-        <v>2.79</v>
-      </c>
-      <c r="R41">
-        <v>2.1</v>
-      </c>
-      <c r="S41">
-        <v>1.42</v>
-      </c>
-      <c r="T41">
-        <v>2.59</v>
-      </c>
-      <c r="U41">
-        <v>2.94</v>
-      </c>
-      <c r="V41">
-        <v>1.38</v>
-      </c>
-      <c r="W41">
-        <v>1.05</v>
-      </c>
-      <c r="X41">
-        <v>1.02</v>
-      </c>
-      <c r="Y41">
-        <v>1.28</v>
-      </c>
-      <c r="Z41">
-        <v>3.12</v>
-      </c>
       <c r="AA41">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB41">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC41">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="AD41">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE41">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AG41">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK41">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.92</v>
+        <v>2.54</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q42">
-        <v>2.37</v>
+        <v>2.95</v>
       </c>
       <c r="R42">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T42">
-        <v>3.22</v>
+        <v>2.77</v>
       </c>
       <c r="U42">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z42">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="AA42">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AB42">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>3.33</v>
       </c>
       <c r="AD42">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF42">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG42">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q43">
-        <v>3.12</v>
+        <v>2.52</v>
       </c>
       <c r="R43">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T43">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
+        <v>3.8</v>
+      </c>
+      <c r="AA43">
+        <v>1.79</v>
+      </c>
+      <c r="AB43">
+        <v>1.94</v>
+      </c>
+      <c r="AC43">
         <v>3.1</v>
       </c>
-      <c r="AA43">
-        <v>1.9</v>
-      </c>
-      <c r="AB43">
-        <v>1.9</v>
-      </c>
-      <c r="AC43">
-        <v>3.3</v>
-      </c>
       <c r="AD43">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE43">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF43">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O44">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P44">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="Q44">
-        <v>2.83</v>
+        <v>2.96</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S44">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T44">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="U44">
         <v>2.8</v>
       </c>
       <c r="V44">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W44">
         <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
+        <v>1.29</v>
+      </c>
+      <c r="Z44">
+        <v>3.35</v>
+      </c>
+      <c r="AA44">
+        <v>2.07</v>
+      </c>
+      <c r="AB44">
+        <v>1.73</v>
+      </c>
+      <c r="AC44">
+        <v>3.3</v>
+      </c>
+      <c r="AD44">
         <v>1.28</v>
       </c>
-      <c r="Z44">
-        <v>3.67</v>
-      </c>
-      <c r="AA44">
-        <v>1.9</v>
-      </c>
-      <c r="AB44">
-        <v>1.87</v>
-      </c>
-      <c r="AC44">
-        <v>3.23</v>
-      </c>
-      <c r="AD44">
-        <v>1.34</v>
-      </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK44">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,25 +7644,25 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O45">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P45">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q45">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="R45">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S45">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T45">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U45">
         <v>2.55</v>
@@ -7671,37 +7671,37 @@
         <v>1.45</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z45">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA45">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB45">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC45">
         <v>2.8</v>
       </c>
       <c r="AD45">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE45">
         <v>1.14</v>
       </c>
       <c r="AF45">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AK45">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="O46">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>4.51</v>
+        <v>2.62</v>
       </c>
       <c r="Q46">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R46">
         <v>2.12</v>
       </c>
       <c r="S46">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T46">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U46">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="V46">
         <v>1.42</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z46">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA46">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AB46">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC46">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="AD46">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE46">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK46">
-        <v>2.06</v>
+        <v>1.44</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="O47">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>3.61</v>
+        <v>3.33</v>
       </c>
       <c r="Q47">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R47">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="S47">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="V47">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA47">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AB47">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AC47">
-        <v>3.08</v>
+        <v>2.54</v>
       </c>
       <c r="AD47">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE47">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="O48">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="P48">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q48">
+        <v>2.4</v>
+      </c>
+      <c r="R48">
         <v>2.15</v>
       </c>
-      <c r="R48">
-        <v>2.3</v>
-      </c>
       <c r="S48">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T48">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="U48">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="V48">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z48">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="AA48">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AB48">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="AC48">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="AD48">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE48">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF48">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AK48">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="O49">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P49">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q49">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S49">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
         <v>3.3</v>
       </c>
       <c r="U49">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z49">
-        <v>4.15</v>
+        <v>4.01</v>
       </c>
       <c r="AA49">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB49">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AC49">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AD49">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE49">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AG49">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O50">
         <v>3.4</v>
       </c>
       <c r="P50">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q50">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R50">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S50">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U50">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z50">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="AA50">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB50">
         <v>1.85</v>
       </c>
       <c r="AC50">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD50">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG50">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK50">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,61 +8622,61 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P51">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="Q51">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="R51">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="U51">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z51">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA51">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB51">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC51">
-        <v>3.24</v>
+        <v>2.82</v>
       </c>
       <c r="AD51">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG51">
         <v>2</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AK51">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P52">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q52">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R52">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U52">
         <v>2.6</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W52">
         <v>1.07</v>
@@ -8818,31 +8818,31 @@
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="AA52">
         <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC52">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AD52">
         <v>1.34</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF52">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG52">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK52">
         <v>1.36</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P53">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="Q53">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="R53">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="S53">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T53">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="U53">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V53">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W53">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y53">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="AA53">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AB53">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC53">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD53">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF53">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG53">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
         <v>1.5</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O54">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P54">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q54">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R54">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S54">
         <v>1.5</v>
       </c>
       <c r="T54">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="U54">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="V54">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W54">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y54">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z54">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="AA54">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AB54">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC54">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AD54">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE54">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF54">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG54">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK54">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,19 +9283,19 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="R55">
         <v>1.82</v>
       </c>
       <c r="S55">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="T55">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="U55">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="V55">
         <v>1.27</v>
@@ -9304,31 +9304,31 @@
         <v>1.01</v>
       </c>
       <c r="X55">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y55">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z55">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="AA55">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="AB55">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC55">
-        <v>5.18</v>
+        <v>4.75</v>
       </c>
       <c r="AD55">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE55">
         <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG55">
         <v>1.68</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK55">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9452,10 +9452,10 @@
         <v>2.12</v>
       </c>
       <c r="S56">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T56">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="U56">
         <v>2.78</v>
@@ -9464,31 +9464,31 @@
         <v>1.36</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
+        <v>1.21</v>
+      </c>
+      <c r="Z56">
+        <v>2.7</v>
+      </c>
+      <c r="AA56">
+        <v>1.95</v>
+      </c>
+      <c r="AB56">
+        <v>1.64</v>
+      </c>
+      <c r="AC56">
+        <v>3.2</v>
+      </c>
+      <c r="AD56">
         <v>1.29</v>
       </c>
-      <c r="Z56">
-        <v>3.37</v>
-      </c>
-      <c r="AA56">
-        <v>1.93</v>
-      </c>
-      <c r="AB56">
-        <v>1.85</v>
-      </c>
-      <c r="AC56">
-        <v>3.3</v>
-      </c>
-      <c r="AD56">
-        <v>1.31</v>
-      </c>
       <c r="AE56">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF56">
         <v>1.87</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P3">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="Q3">
-        <v>2.97</v>
+        <v>3.62</v>
       </c>
       <c r="R3">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="S3">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="T3">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="U3">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Y3">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Z3">
-        <v>2.34</v>
+        <v>2.11</v>
       </c>
       <c r="AA3">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AB3">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC3">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AD3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE3">
         <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG3">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.68</v>
+        <v>2.1</v>
       </c>
       <c r="O4">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P4">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q4">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="R4">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="S4">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T4">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="U4">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="Y4">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="Z4">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="AA4">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AB4">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AC4">
-        <v>6.55</v>
+        <v>5.25</v>
       </c>
       <c r="AD4">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE4">
         <v>1.01</v>
       </c>
       <c r="AF4">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AG4">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O6">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="P6">
-        <v>13.5</v>
+        <v>12.01</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,28 +2268,28 @@
         <v>2.05</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P12">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="Q12">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R12">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="S12">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U12">
         <v>2.4</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W12">
         <v>1.09</v>
@@ -2298,31 +2298,31 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z12">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="AA12">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB12">
         <v>2.17</v>
       </c>
       <c r="AC12">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AD12">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE12">
         <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG12">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.62</v>
+        <v>1.57</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P21">
-        <v>2.17</v>
+        <v>4.4</v>
       </c>
       <c r="Q21">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="R21">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="S21">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T21">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U21">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="V21">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W21">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>6.33</v>
+        <v>5.55</v>
       </c>
       <c r="AA21">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AB21">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AC21">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD21">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE21">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AF21">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AG21">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.57</v>
+        <v>2.62</v>
       </c>
       <c r="O22">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>4.4</v>
+        <v>2.17</v>
       </c>
       <c r="Q22">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="R22">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="S22">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U22">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="V22">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W22">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>5.55</v>
+        <v>6.33</v>
       </c>
       <c r="AA22">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AB22">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AC22">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AD22">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AF22">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AG22">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AK22">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="O24">
         <v>4</v>
       </c>
       <c r="P24">
-        <v>4.25</v>
+        <v>4.49</v>
       </c>
       <c r="Q24">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="R24">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="S24">
         <v>1.22</v>
@@ -4242,13 +4242,13 @@
         <v>3.8</v>
       </c>
       <c r="U24">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="V24">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4257,19 +4257,19 @@
         <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>4.97</v>
+        <v>5.5</v>
       </c>
       <c r="AA24">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB24">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC24">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD24">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE24">
         <v>1.18</v>
@@ -4278,7 +4278,7 @@
         <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK24">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O25">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P25">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q25">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="R25">
         <v>2.52</v>
@@ -4402,13 +4402,13 @@
         <v>1.15</v>
       </c>
       <c r="T25">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="U25">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V25">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="W25">
         <v>1.22</v>
@@ -4417,22 +4417,22 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="AA25">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB25">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC25">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AD25">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AE25">
         <v>1.36</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>2.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
         <v>1.17</v>
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P27">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q27">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="R27">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="U27">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
+        <v>1.29</v>
+      </c>
+      <c r="Z27">
+        <v>3.3</v>
+      </c>
+      <c r="AA27">
+        <v>1.98</v>
+      </c>
+      <c r="AB27">
+        <v>1.78</v>
+      </c>
+      <c r="AC27">
+        <v>3.4</v>
+      </c>
+      <c r="AD27">
         <v>1.3</v>
       </c>
-      <c r="Z27">
-        <v>3.39</v>
-      </c>
-      <c r="AA27">
-        <v>1.97</v>
-      </c>
-      <c r="AB27">
-        <v>1.81</v>
-      </c>
-      <c r="AC27">
-        <v>3.2</v>
-      </c>
-      <c r="AD27">
-        <v>1.26</v>
-      </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG27">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AK27">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>4.41</v>
+        <v>3.78</v>
       </c>
       <c r="Q28">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="U28">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA28">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AC28">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="AD28">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P29">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q29">
+        <v>2.27</v>
+      </c>
+      <c r="R29">
+        <v>2.25</v>
+      </c>
+      <c r="S29">
+        <v>1.34</v>
+      </c>
+      <c r="T29">
+        <v>3.05</v>
+      </c>
+      <c r="U29">
+        <v>2.5</v>
+      </c>
+      <c r="V29">
+        <v>1.44</v>
+      </c>
+      <c r="W29">
+        <v>1.11</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>1.25</v>
+      </c>
+      <c r="Z29">
+        <v>3.7</v>
+      </c>
+      <c r="AA29">
+        <v>1.8</v>
+      </c>
+      <c r="AB29">
+        <v>1.96</v>
+      </c>
+      <c r="AC29">
         <v>2.88</v>
       </c>
-      <c r="R29">
-        <v>2.05</v>
-      </c>
-      <c r="S29">
-        <v>1.42</v>
-      </c>
-      <c r="T29">
-        <v>2.88</v>
-      </c>
-      <c r="U29">
-        <v>2.73</v>
-      </c>
-      <c r="V29">
-        <v>1.38</v>
-      </c>
-      <c r="W29">
-        <v>1.03</v>
-      </c>
-      <c r="X29">
-        <v>1.05</v>
-      </c>
-      <c r="Y29">
-        <v>1.33</v>
-      </c>
-      <c r="Z29">
-        <v>2.94</v>
-      </c>
-      <c r="AA29">
-        <v>2.05</v>
-      </c>
-      <c r="AB29">
-        <v>1.75</v>
-      </c>
-      <c r="AC29">
-        <v>3.5</v>
-      </c>
       <c r="AD29">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE29">
         <v>1.08</v>
       </c>
       <c r="AF29">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG29">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK29">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P30">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q30">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="U30">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V30">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
         <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA30">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB30">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AC30">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD30">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE30">
         <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG30">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,34 +5362,34 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.25</v>
+        <v>1.53</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P31">
-        <v>1.92</v>
+        <v>5.25</v>
       </c>
       <c r="Q31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="U31">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>1.02</v>
@@ -5398,28 +5398,28 @@
         <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="AA31">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AB31">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AC31">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AD31">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG31">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AK31">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="O32">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="Q32">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="R32">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
         <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AA32">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AB32">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC32">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD32">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.53</v>
+        <v>3.6</v>
       </c>
       <c r="O33">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>5.09</v>
+        <v>2</v>
       </c>
       <c r="Q33">
-        <v>2.04</v>
+        <v>3.64</v>
       </c>
       <c r="R33">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T33">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="U33">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="V33">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>3.85</v>
+        <v>3.51</v>
       </c>
       <c r="AA33">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB33">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AC33">
-        <v>2.59</v>
+        <v>3.4</v>
       </c>
       <c r="AD33">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AE33">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF33">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AK33">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,34 +5851,34 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q34">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="R34">
         <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W34">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5887,22 +5887,22 @@
         <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AA34">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB34">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC34">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AD34">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
         <v>1.7</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="O35">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P35">
         <v>6</v>
       </c>
       <c r="Q35">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R35">
         <v>2.25</v>
@@ -6032,46 +6032,46 @@
         <v>1.36</v>
       </c>
       <c r="T35">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V35">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W35">
         <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
         <v>3.3</v>
       </c>
       <c r="AA35">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB35">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC35">
         <v>3.3</v>
       </c>
       <c r="AD35">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE35">
         <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG35">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
+        <v>2.62</v>
+      </c>
+      <c r="O36">
+        <v>3.5</v>
+      </c>
+      <c r="P36">
         <v>2.5</v>
       </c>
-      <c r="O36">
-        <v>3.25</v>
-      </c>
-      <c r="P36">
-        <v>2.6</v>
-      </c>
       <c r="Q36">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="R36">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S36">
         <v>1.38</v>
@@ -6198,28 +6198,28 @@
         <v>2.77</v>
       </c>
       <c r="U36">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="V36">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA36">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AB36">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC36">
         <v>3.6</v>
@@ -6228,13 +6228,13 @@
         <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF36">
         <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
         <v>3.6</v>
@@ -6349,10 +6349,10 @@
         <v>2.05</v>
       </c>
       <c r="Q37">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R37">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="S37">
         <v>1.28</v>
@@ -6361,10 +6361,10 @@
         <v>3.28</v>
       </c>
       <c r="U37">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="V37">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
         <v>1.07</v>
@@ -6373,31 +6373,31 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z37">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA37">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB37">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AD37">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AE37">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF37">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6506,46 +6506,46 @@
         <v>2.2</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
         <v>2.85</v>
       </c>
       <c r="Q38">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="R38">
         <v>2.14</v>
       </c>
       <c r="S38">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="U38">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V38">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W38">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA38">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB38">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC38">
         <v>3.14</v>
@@ -6554,13 +6554,13 @@
         <v>1.27</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
         <v>1.69</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK38">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P42">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="Q42">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S42">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T42">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="U42">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
         <v>1.05</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="AA42">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AB42">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC42">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AD42">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE42">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF42">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK42">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="O44">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="Q44">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="R44">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T44">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="U44">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="V44">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
         <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z44">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AA44">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AB44">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC44">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="AD44">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG44">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G45">
@@ -7647,61 +7647,61 @@
         <v>2.6</v>
       </c>
       <c r="O45">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P45">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q45">
         <v>3</v>
       </c>
       <c r="R45">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="S45">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U45">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="V45">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W45">
         <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AA45">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AB45">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AC45">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AD45">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE45">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF45">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG45">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AK45">
         <v>1.44</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="O46">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P46">
-        <v>2.62</v>
+        <v>3.33</v>
       </c>
       <c r="Q46">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="R46">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="V46">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="AA46">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AB46">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AC46">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="AD46">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AE46">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG46">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
-        <v>3.33</v>
+        <v>2.56</v>
       </c>
       <c r="Q47">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="R47">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S47">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
         <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W47">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="AA47">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB47">
         <v>2.08</v>
       </c>
       <c r="AC47">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="AD47">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF47">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG47">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AK47">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="O54">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P54">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q54">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R54">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S54">
         <v>1.5</v>
       </c>
       <c r="T54">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="U54">
         <v>2.7</v>
       </c>
       <c r="V54">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="W54">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X54">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z54">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AA54">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AB54">
         <v>1.57</v>
       </c>
       <c r="AC54">
-        <v>4.5</v>
+        <v>4.34</v>
       </c>
       <c r="AD54">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF54">
         <v>1.8</v>
       </c>
       <c r="AG54">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK54">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q55">
         <v>4.26</v>
@@ -9295,43 +9295,43 @@
         <v>2.27</v>
       </c>
       <c r="U55">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="V55">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W55">
         <v>1.01</v>
       </c>
       <c r="X55">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y55">
         <v>1.53</v>
       </c>
       <c r="Z55">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="AA55">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="AB55">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC55">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AD55">
         <v>1.13</v>
       </c>
       <c r="AE55">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF55">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AG55">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK55">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9443,7 +9443,7 @@
         <v>3.7</v>
       </c>
       <c r="P56">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="Q56">
         <v>2.12</v>
@@ -9452,10 +9452,10 @@
         <v>2.12</v>
       </c>
       <c r="S56">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="T56">
-        <v>2.98</v>
+        <v>2.27</v>
       </c>
       <c r="U56">
         <v>2.78</v>
@@ -9470,16 +9470,16 @@
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z56">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA56">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB56">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AC56">
         <v>3.2</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P22">
-        <v>2.17</v>
+        <v>1.61</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="R22">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="S22">
         <v>1.2</v>
       </c>
       <c r="T22">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U22">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V22">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W22">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>6.33</v>
+        <v>5.5</v>
       </c>
       <c r="AA22">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="AC22">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD22">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE22">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AF22">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AG22">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AK22">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="O23">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>1.61</v>
+        <v>2.17</v>
       </c>
       <c r="Q23">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="R23">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="S23">
         <v>1.2</v>
       </c>
       <c r="T23">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U23">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V23">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W23">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>5.5</v>
+        <v>6.33</v>
       </c>
       <c r="AA23">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AB23">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AC23">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD23">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE23">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AF23">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AG23">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AK23">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="O27">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q27">
+        <v>2.66</v>
+      </c>
+      <c r="R27">
+        <v>2.15</v>
+      </c>
+      <c r="S27">
+        <v>1.33</v>
+      </c>
+      <c r="T27">
         <v>3</v>
       </c>
-      <c r="R27">
-        <v>2.1</v>
-      </c>
-      <c r="S27">
+      <c r="U27">
+        <v>2.59</v>
+      </c>
+      <c r="V27">
         <v>1.38</v>
       </c>
-      <c r="T27">
-        <v>2.77</v>
-      </c>
-      <c r="U27">
-        <v>2.88</v>
-      </c>
-      <c r="V27">
-        <v>1.39</v>
-      </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
+        <v>1.24</v>
+      </c>
+      <c r="Z27">
+        <v>3.34</v>
+      </c>
+      <c r="AA27">
+        <v>1.88</v>
+      </c>
+      <c r="AB27">
+        <v>1.87</v>
+      </c>
+      <c r="AC27">
+        <v>3.08</v>
+      </c>
+      <c r="AD27">
+        <v>1.28</v>
+      </c>
+      <c r="AE27">
+        <v>1.11</v>
+      </c>
+      <c r="AF27">
+        <v>1.7</v>
+      </c>
+      <c r="AG27">
+        <v>2</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.29</v>
       </c>
-      <c r="Z27">
-        <v>3.3</v>
-      </c>
-      <c r="AA27">
-        <v>1.98</v>
-      </c>
-      <c r="AB27">
-        <v>1.78</v>
-      </c>
-      <c r="AC27">
-        <v>3.4</v>
-      </c>
-      <c r="AD27">
-        <v>1.3</v>
-      </c>
-      <c r="AE27">
-        <v>1.07</v>
-      </c>
-      <c r="AF27">
-        <v>1.73</v>
-      </c>
-      <c r="AG27">
-        <v>1.98</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.41</v>
-      </c>
       <c r="AK27">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P28">
-        <v>3.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q28">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="R28">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T28">
         <v>2.77</v>
       </c>
       <c r="U28">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
         <v>1.05</v>
@@ -4906,31 +4906,31 @@
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z28">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA28">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AC28">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="AD28">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
         <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AK28">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="O30">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q30">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R30">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U30">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
+        <v>1.22</v>
+      </c>
+      <c r="Z30">
+        <v>3.65</v>
+      </c>
+      <c r="AA30">
+        <v>1.81</v>
+      </c>
+      <c r="AB30">
+        <v>1.95</v>
+      </c>
+      <c r="AC30">
+        <v>3.1</v>
+      </c>
+      <c r="AD30">
+        <v>1.32</v>
+      </c>
+      <c r="AE30">
+        <v>1.09</v>
+      </c>
+      <c r="AF30">
+        <v>1.67</v>
+      </c>
+      <c r="AG30">
+        <v>2.1</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.29</v>
+      </c>
+      <c r="AK30">
         <v>1.28</v>
-      </c>
-      <c r="Z30">
-        <v>3.3</v>
-      </c>
-      <c r="AA30">
-        <v>2</v>
-      </c>
-      <c r="AB30">
-        <v>1.79</v>
-      </c>
-      <c r="AC30">
-        <v>3.4</v>
-      </c>
-      <c r="AD30">
-        <v>1.26</v>
-      </c>
-      <c r="AE30">
-        <v>1.07</v>
-      </c>
-      <c r="AF30">
-        <v>1.72</v>
-      </c>
-      <c r="AG30">
-        <v>1.93</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.25</v>
-      </c>
-      <c r="AK30">
-        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,61 +5362,61 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="O31">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>5.25</v>
+        <v>3.78</v>
       </c>
       <c r="Q31">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="R31">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>3.22</v>
+        <v>2.77</v>
       </c>
       <c r="U31">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AA31">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AB31">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="AC31">
-        <v>2.65</v>
+        <v>3.13</v>
       </c>
       <c r="AD31">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE31">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG31">
         <v>1.94</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>1.89</v>
+        <v>5.25</v>
       </c>
       <c r="Q32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
         <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="AA32">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AB32">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AC32">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="AD32">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG32">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AK32">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q33">
-        <v>3.64</v>
+        <v>3.28</v>
       </c>
       <c r="R33">
         <v>2.05</v>
       </c>
       <c r="S33">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U33">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="V33">
         <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33">
+        <v>1.33</v>
+      </c>
+      <c r="Z33">
+        <v>3.25</v>
+      </c>
+      <c r="AA33">
+        <v>1.94</v>
+      </c>
+      <c r="AB33">
+        <v>1.74</v>
+      </c>
+      <c r="AC33">
+        <v>3.6</v>
+      </c>
+      <c r="AD33">
         <v>1.25</v>
       </c>
-      <c r="Z33">
-        <v>3.51</v>
-      </c>
-      <c r="AA33">
-        <v>1.95</v>
-      </c>
-      <c r="AB33">
-        <v>1.85</v>
-      </c>
-      <c r="AC33">
-        <v>3.4</v>
-      </c>
-      <c r="AD33">
-        <v>1.27</v>
-      </c>
       <c r="AE33">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.08</v>
+        <v>3.6</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q34">
-        <v>2.66</v>
+        <v>3.64</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U34">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V34">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.34</v>
+        <v>3.51</v>
       </c>
       <c r="AA34">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK34">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="O35">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S35">
+        <v>1.42</v>
+      </c>
+      <c r="T35">
+        <v>2.81</v>
+      </c>
+      <c r="U35">
+        <v>2.73</v>
+      </c>
+      <c r="V35">
         <v>1.36</v>
-      </c>
-      <c r="T35">
-        <v>2.88</v>
-      </c>
-      <c r="U35">
-        <v>2.7</v>
-      </c>
-      <c r="V35">
-        <v>1.42</v>
       </c>
       <c r="W35">
         <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
         <v>3.3</v>
       </c>
       <c r="AA35">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AB35">
         <v>1.79</v>
       </c>
       <c r="AC35">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AG35">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.62</v>
+        <v>1.53</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P36">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="Q36">
-        <v>3.28</v>
+        <v>2</v>
       </c>
       <c r="R36">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U36">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W36">
         <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA36">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AB36">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AC36">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD36">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE36">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG36">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK36">
-        <v>1.43</v>
+        <v>2.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,61 +6666,61 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P39">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="Q39">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S39">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="U39">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="V39">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W39">
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA39">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB39">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC39">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AD39">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG39">
         <v>2</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,34 +6829,34 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="O40">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="Q40">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T40">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U40">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="V40">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
         <v>1.03</v>
@@ -6865,28 +6865,28 @@
         <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA40">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AB40">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC40">
-        <v>2.89</v>
+        <v>3.28</v>
       </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AK40">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="Q41">
-        <v>2.9</v>
+        <v>2.52</v>
       </c>
       <c r="R41">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T41">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="U41">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="V41">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AA41">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB41">
+        <v>1.92</v>
+      </c>
+      <c r="AC41">
+        <v>3.1</v>
+      </c>
+      <c r="AD41">
+        <v>1.3</v>
+      </c>
+      <c r="AE41">
+        <v>1.07</v>
+      </c>
+      <c r="AF41">
+        <v>1.73</v>
+      </c>
+      <c r="AG41">
+        <v>2</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.26</v>
+      </c>
+      <c r="AK41">
         <v>1.85</v>
-      </c>
-      <c r="AC41">
-        <v>3.28</v>
-      </c>
-      <c r="AD41">
-        <v>1.34</v>
-      </c>
-      <c r="AE41">
-        <v>1.11</v>
-      </c>
-      <c r="AF41">
-        <v>1.69</v>
-      </c>
-      <c r="AG41">
-        <v>2.06</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.35</v>
-      </c>
-      <c r="AK41">
-        <v>1.6</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O42">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>3.26</v>
+        <v>3.55</v>
       </c>
       <c r="Q42">
-        <v>2.96</v>
+        <v>2.52</v>
       </c>
       <c r="R42">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="S42">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="U42">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="V42">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z42">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AA42">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AB42">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AC42">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD42">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE42">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q43">
-        <v>2.52</v>
+        <v>2.95</v>
       </c>
       <c r="R43">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T43">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="U43">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="V43">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
         <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="AA43">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB43">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AC43">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="AD43">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF43">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG43">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P44">
-        <v>2.7</v>
+        <v>3.26</v>
       </c>
       <c r="Q44">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S44">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T44">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="U44">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W44">
         <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z44">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="AA44">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AB44">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC44">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AD44">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK44">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O45">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P45">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q45">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R45">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T45">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U45">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="V45">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z45">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AA45">
         <v>1.89</v>
       </c>
       <c r="AB45">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC45">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD45">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE45">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF45">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG45">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK45">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="O46">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P46">
-        <v>3.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q46">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
         <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z46">
-        <v>4.25</v>
+        <v>4.01</v>
       </c>
       <c r="AA46">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB46">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AC46">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="AD46">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE46">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF46">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AG46">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="O47">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>2.56</v>
+        <v>3.33</v>
       </c>
       <c r="Q47">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="R47">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
         <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V47">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="AA47">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB47">
         <v>2.08</v>
       </c>
       <c r="AC47">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="AD47">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE47">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,61 +8133,61 @@
         </is>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O48">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q48">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="R48">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S48">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T48">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U48">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
+        <v>1.23</v>
+      </c>
+      <c r="Z48">
+        <v>3.44</v>
+      </c>
+      <c r="AA48">
+        <v>1.96</v>
+      </c>
+      <c r="AB48">
+        <v>1.85</v>
+      </c>
+      <c r="AC48">
+        <v>3.3</v>
+      </c>
+      <c r="AD48">
         <v>1.25</v>
       </c>
-      <c r="Z48">
-        <v>3.3</v>
-      </c>
-      <c r="AA48">
-        <v>1.89</v>
-      </c>
-      <c r="AB48">
-        <v>1.89</v>
-      </c>
-      <c r="AC48">
-        <v>3.25</v>
-      </c>
-      <c r="AD48">
-        <v>1.34</v>
-      </c>
       <c r="AE48">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF48">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG48">
         <v>2</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AK48">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,61 +8296,61 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O49">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P49">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q49">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R49">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
+        <v>2.94</v>
+      </c>
+      <c r="U49">
+        <v>2.75</v>
+      </c>
+      <c r="V49">
+        <v>1.42</v>
+      </c>
+      <c r="W49">
+        <v>1.07</v>
+      </c>
+      <c r="X49">
+        <v>1.05</v>
+      </c>
+      <c r="Y49">
+        <v>1.27</v>
+      </c>
+      <c r="Z49">
         <v>3.3</v>
       </c>
-      <c r="U49">
-        <v>2.57</v>
-      </c>
-      <c r="V49">
-        <v>1.44</v>
-      </c>
-      <c r="W49">
-        <v>1.06</v>
-      </c>
-      <c r="X49">
-        <v>1.02</v>
-      </c>
-      <c r="Y49">
-        <v>1.24</v>
-      </c>
-      <c r="Z49">
-        <v>4.01</v>
-      </c>
       <c r="AA49">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AB49">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AC49">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="AD49">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE49">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AG49">
         <v>2</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK49">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G50">
@@ -8462,61 +8462,61 @@
         <v>2.6</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Q50">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R50">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S50">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V50">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
         <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y50">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="AA50">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AB50">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AC50">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD50">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
+        <v>1.45</v>
+      </c>
+      <c r="AK50">
         <v>1.44</v>
-      </c>
-      <c r="AK50">
-        <v>1.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="O51">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>4.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q51">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R51">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V51">
         <v>1.42</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA51">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AB51">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC51">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="AD51">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AK51">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -638,52 +638,52 @@
         <v>2.42</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q2">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
-        <v>2.76</v>
+        <v>3.17</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="AA2">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB2">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AC2">
-        <v>3.45</v>
+        <v>3.81</v>
       </c>
       <c r="AD2">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,49 +798,49 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="O3">
         <v>2.62</v>
       </c>
       <c r="P3">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="Q3">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="R3">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="S3">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="T3">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="U3">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="V3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W3">
         <v>1.01</v>
       </c>
       <c r="X3">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Y3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Z3">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AA3">
         <v>3</v>
       </c>
       <c r="AB3">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AC3">
         <v>6.5</v>
@@ -849,13 +849,13 @@
         <v>1.08</v>
       </c>
       <c r="AE3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AG3">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O4">
         <v>2.75</v>
       </c>
       <c r="P4">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="Q4">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="R4">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S4">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T4">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="U4">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
         <v>1.02</v>
@@ -994,19 +994,19 @@
         <v>1.09</v>
       </c>
       <c r="Y4">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Z4">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AA4">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AB4">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC4">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="AD4">
         <v>1.11</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK4">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,52 +1124,52 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="O5">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="P5">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q5">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="R5">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="S5">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T5">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="U5">
         <v>3.6</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W5">
         <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="Z5">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AA5">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AB5">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AC5">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AD5">
         <v>1.11</v>
@@ -1178,10 +1178,10 @@
         <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG5">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O8">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="P8">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="Q8">
         <v>2.7</v>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="R9">
         <v>2</v>
@@ -1797,28 +1797,28 @@
         <v>2.38</v>
       </c>
       <c r="U9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
         <v>0</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y9">
+        <v>1.5</v>
+      </c>
+      <c r="Z9">
+        <v>2.45</v>
+      </c>
+      <c r="AA9">
+        <v>2.6</v>
+      </c>
+      <c r="AB9">
         <v>1.45</v>
-      </c>
-      <c r="Z9">
-        <v>2.55</v>
-      </c>
-      <c r="AA9">
-        <v>2.45</v>
-      </c>
-      <c r="AB9">
-        <v>1.5</v>
       </c>
       <c r="AC9">
         <v>4.5</v>
@@ -1830,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AG9">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,16 +1948,16 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="R10">
         <v>1.96</v>
       </c>
       <c r="S10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T10">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="U10">
         <v>3.15</v>
@@ -1972,7 +1972,7 @@
         <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z10">
         <v>2.69</v>
@@ -1990,7 +1990,7 @@
         <v>1.18</v>
       </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
         <v>1.98</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O11">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P11">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="Q11">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R11">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="S11">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T11">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U11">
         <v>3.34</v>
@@ -2129,25 +2129,25 @@
         <v>1.24</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1.1</v>
       </c>
       <c r="Y11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z11">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="AA11">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="AB11">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AC11">
-        <v>4.64</v>
+        <v>4.66</v>
       </c>
       <c r="AD11">
         <v>1.18</v>
@@ -2156,10 +2156,10 @@
         <v>1.02</v>
       </c>
       <c r="AF11">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG11">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK11">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.19</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="Q13">
-        <v>3.02</v>
+        <v>5.62</v>
       </c>
       <c r="R13">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
-        <v>3.06</v>
+        <v>2.26</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="AA13">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC13">
-        <v>3.61</v>
+        <v>2.38</v>
       </c>
       <c r="AD13">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AE13">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AF13">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="O14">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="Q14">
-        <v>5.75</v>
+        <v>2.8</v>
       </c>
       <c r="R14">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="T14">
+        <v>2.88</v>
+      </c>
+      <c r="U14">
+        <v>2.7</v>
+      </c>
+      <c r="V14">
+        <v>1.39</v>
+      </c>
+      <c r="W14">
+        <v>1.03</v>
+      </c>
+      <c r="X14">
+        <v>1.02</v>
+      </c>
+      <c r="Y14">
+        <v>1.31</v>
+      </c>
+      <c r="Z14">
+        <v>3.35</v>
+      </c>
+      <c r="AA14">
+        <v>1.91</v>
+      </c>
+      <c r="AB14">
+        <v>1.76</v>
+      </c>
+      <c r="AC14">
         <v>3.5</v>
       </c>
-      <c r="U14">
-        <v>2.31</v>
-      </c>
-      <c r="V14">
-        <v>1.56</v>
-      </c>
-      <c r="W14">
-        <v>1.11</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.17</v>
-      </c>
-      <c r="Z14">
-        <v>4.2</v>
-      </c>
-      <c r="AA14">
-        <v>1.6</v>
-      </c>
-      <c r="AB14">
-        <v>2.25</v>
-      </c>
-      <c r="AC14">
-        <v>2.55</v>
-      </c>
       <c r="AD14">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="AE14">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.08</v>
+        <v>1.55</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,10 +2793,10 @@
         <v>3.9</v>
       </c>
       <c r="AA15">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB15">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC15">
         <v>2.7</v>
@@ -2811,7 +2811,7 @@
         <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="O16">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="P16">
-        <v>2.65</v>
+        <v>1.33</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P19">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q19">
         <v>4</v>
       </c>
       <c r="R19">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S19">
         <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="V19">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W19">
         <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
         <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
       <c r="AA19">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AB19">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="AC19">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AD19">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE19">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF19">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG19">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
+        <v>2.04</v>
+      </c>
+      <c r="AK19">
         <v>1.2</v>
-      </c>
-      <c r="AK19">
-        <v>1.22</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O20">
         <v>3.5</v>
       </c>
       <c r="P20">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q20">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R20">
         <v>2.27</v>
@@ -3602,13 +3602,13 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z20">
-        <v>5.4</v>
+        <v>5.58</v>
       </c>
       <c r="AA20">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB20">
         <v>2.5</v>
@@ -3620,7 +3620,7 @@
         <v>1.54</v>
       </c>
       <c r="AE20">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF20">
         <v>1.39</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O21">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P21">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q21">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="R21">
         <v>2.29</v>
       </c>
       <c r="S21">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T21">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="U21">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V21">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W21">
         <v>1.15</v>
@@ -3768,28 +3768,28 @@
         <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC21">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD21">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AE21">
         <v>1.28</v>
       </c>
       <c r="AF21">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3901,13 +3901,13 @@
         <v>3.9</v>
       </c>
       <c r="P22">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q22">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="R22">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S22">
         <v>1.2</v>
@@ -3928,25 +3928,25 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z22">
         <v>5.5</v>
       </c>
       <c r="AA22">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB22">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC22">
         <v>2</v>
       </c>
       <c r="AD22">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF22">
         <v>1.43</v>
@@ -3968,7 +3968,7 @@
         <v>1.16</v>
       </c>
       <c r="AK22">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4061,61 +4061,61 @@
         <v>2.62</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P23">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="Q23">
         <v>3</v>
       </c>
       <c r="R23">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="S23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U23">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="V23">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W23">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
         <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>6.33</v>
+        <v>5.75</v>
       </c>
       <c r="AA23">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AB23">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="AC23">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="AD23">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AE23">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AF23">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AG23">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,46 +4221,46 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="P24">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="Q24">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="R24">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T24">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U24">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="V24">
         <v>1.6</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
         <v>5.5</v>
       </c>
       <c r="AA24">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB24">
         <v>2.4</v>
@@ -4272,7 +4272,7 @@
         <v>1.58</v>
       </c>
       <c r="AE24">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF24">
         <v>1.53</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
         <v>2.1</v>
@@ -4556,28 +4556,28 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.22</v>
@@ -4586,41 +4586,41 @@
         <v>4.1</v>
       </c>
       <c r="AA26">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC26">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE26">
+        <v>1.1</v>
+      </c>
+      <c r="AF26">
+        <v>2.09</v>
+      </c>
+      <c r="AG26">
+        <v>1.65</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.13</v>
       </c>
-      <c r="AF26">
-        <v>2.1</v>
-      </c>
-      <c r="AG26">
-        <v>1.67</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.14</v>
-      </c>
       <c r="AK26">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="Q27">
-        <v>2.66</v>
+        <v>4.34</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S27">
         <v>1.33</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="U27">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="AA27">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB27">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC27">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD27">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE27">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK27">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O28">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q28">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U28">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA28">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB28">
         <v>1.78</v>
       </c>
       <c r="AC28">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,61 +5036,61 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P29">
         <v>4.2</v>
       </c>
       <c r="Q29">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="R29">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S29">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="U29">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AA29">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB29">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD29">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE29">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF29">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG29">
         <v>2</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,34 +5199,34 @@
         </is>
       </c>
       <c r="N30">
+        <v>1.68</v>
+      </c>
+      <c r="O30">
         <v>3.6</v>
       </c>
-      <c r="O30">
-        <v>3.5</v>
-      </c>
       <c r="P30">
-        <v>1.89</v>
+        <v>4.41</v>
       </c>
       <c r="Q30">
-        <v>4</v>
+        <v>2.27</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T30">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U30">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -5235,28 +5235,28 @@
         <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AA30">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB30">
         <v>1.95</v>
       </c>
       <c r="AC30">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AD30">
         <v>1.32</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG30">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK30">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.82</v>
+        <v>3.6</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>3.78</v>
+        <v>2.05</v>
       </c>
       <c r="Q31">
-        <v>2.38</v>
+        <v>4.13</v>
       </c>
       <c r="R31">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="S31">
         <v>1.33</v>
       </c>
       <c r="T31">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="U31">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z31">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA31">
+        <v>1.95</v>
+      </c>
+      <c r="AB31">
         <v>1.85</v>
       </c>
-      <c r="AB31">
-        <v>1.92</v>
-      </c>
       <c r="AC31">
-        <v>3.13</v>
+        <v>3.21</v>
       </c>
       <c r="AD31">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG31">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK31">
-        <v>1.86</v>
+        <v>1.19</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.53</v>
+        <v>1.97</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q32">
-        <v>2</v>
+        <v>2.73</v>
       </c>
       <c r="R32">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="U32">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z32">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AA32">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AB32">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="AC32">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="AD32">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE32">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF32">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AK32">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P33">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q33">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S33">
         <v>1.38</v>
@@ -5709,43 +5709,43 @@
         <v>2.77</v>
       </c>
       <c r="U33">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W33">
         <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AA33">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AB33">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AC33">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG33">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK33">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="P34">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="Q34">
-        <v>3.64</v>
+        <v>2.01</v>
       </c>
       <c r="R34">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="S34">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>3.51</v>
+        <v>4.32</v>
       </c>
       <c r="AA34">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="AD34">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK34">
-        <v>1.25</v>
+        <v>2.43</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O35">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="P35">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q35">
         <v>2.8</v>
       </c>
       <c r="R35">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
         <v>1.42</v>
       </c>
       <c r="T35">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="U35">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W35">
         <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z35">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA35">
         <v>2</v>
       </c>
       <c r="AB35">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC35">
         <v>3.4</v>
       </c>
       <c r="AD35">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AG35">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O36">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P36">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q36">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R36">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U36">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V36">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA36">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB36">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD36">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE36">
         <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG36">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,58 +6340,58 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="Q37">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="R37">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
         <v>1.16</v>
       </c>
       <c r="Z37">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB37">
         <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="AD37">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE37">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF37">
         <v>1.57</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="O38">
         <v>3.4</v>
       </c>
       <c r="P38">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q38">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="R38">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T38">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="U38">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V38">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA38">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB38">
         <v>1.9</v>
       </c>
       <c r="AC38">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AD38">
         <v>1.27</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
         <v>1.69</v>
       </c>
       <c r="AG38">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK38">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="O39">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="P39">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="Q39">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R39">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T39">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="U39">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="V39">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W39">
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z39">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA39">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB39">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC39">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="AD39">
         <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,37 +6829,37 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P40">
         <v>3</v>
       </c>
       <c r="Q40">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="R40">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T40">
         <v>2.85</v>
       </c>
       <c r="U40">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="V40">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
         <v>1.25</v>
@@ -6868,25 +6868,25 @@
         <v>3.3</v>
       </c>
       <c r="AA40">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC40">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AD40">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF40">
         <v>1.69</v>
       </c>
       <c r="AG40">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.9</v>
+        <v>2.59</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q41">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="R41">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T41">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="V41">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W41">
         <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z41">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="AA41">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB41">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC41">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="AD41">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG41">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK41">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7161,52 +7161,52 @@
         <v>3.6</v>
       </c>
       <c r="P42">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="Q42">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="R42">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T42">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U42">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="V42">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z42">
-        <v>3.8</v>
+        <v>4.14</v>
       </c>
       <c r="AA42">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AB42">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC42">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AD42">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE42">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
         <v>1.62</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q43">
-        <v>2.95</v>
+        <v>2.47</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S43">
+        <v>1.36</v>
+      </c>
+      <c r="T43">
+        <v>2.89</v>
+      </c>
+      <c r="U43">
+        <v>2.77</v>
+      </c>
+      <c r="V43">
         <v>1.39</v>
       </c>
-      <c r="T43">
-        <v>2.77</v>
-      </c>
-      <c r="U43">
-        <v>2.85</v>
-      </c>
-      <c r="V43">
-        <v>1.36</v>
-      </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z43">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="AA43">
+        <v>1.9</v>
+      </c>
+      <c r="AB43">
+        <v>1.9</v>
+      </c>
+      <c r="AC43">
+        <v>3.1</v>
+      </c>
+      <c r="AD43">
+        <v>1.28</v>
+      </c>
+      <c r="AE43">
+        <v>1.06</v>
+      </c>
+      <c r="AF43">
+        <v>1.73</v>
+      </c>
+      <c r="AG43">
+        <v>2</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>1.27</v>
+      </c>
+      <c r="AK43">
         <v>1.88</v>
-      </c>
-      <c r="AB43">
-        <v>1.87</v>
-      </c>
-      <c r="AC43">
-        <v>3.33</v>
-      </c>
-      <c r="AD43">
-        <v>1.33</v>
-      </c>
-      <c r="AE43">
-        <v>1.07</v>
-      </c>
-      <c r="AF43">
-        <v>1.68</v>
-      </c>
-      <c r="AG43">
-        <v>2.09</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.3</v>
-      </c>
-      <c r="AK43">
-        <v>1.47</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O44">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="Q44">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="R44">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S44">
         <v>1.42</v>
       </c>
       <c r="T44">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="U44">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="V44">
+        <v>1.38</v>
+      </c>
+      <c r="W44">
+        <v>1.04</v>
+      </c>
+      <c r="X44">
+        <v>1.03</v>
+      </c>
+      <c r="Y44">
         <v>1.33</v>
       </c>
-      <c r="W44">
-        <v>1.05</v>
-      </c>
-      <c r="X44">
-        <v>1.02</v>
-      </c>
-      <c r="Y44">
+      <c r="Z44">
+        <v>2.95</v>
+      </c>
+      <c r="AA44">
+        <v>2</v>
+      </c>
+      <c r="AB44">
+        <v>1.8</v>
+      </c>
+      <c r="AC44">
+        <v>3.67</v>
+      </c>
+      <c r="AD44">
         <v>1.29</v>
       </c>
-      <c r="Z44">
-        <v>3.35</v>
-      </c>
-      <c r="AA44">
-        <v>2.07</v>
-      </c>
-      <c r="AB44">
-        <v>1.73</v>
-      </c>
-      <c r="AC44">
-        <v>3.3</v>
-      </c>
-      <c r="AD44">
-        <v>1.28</v>
-      </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG44">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="O45">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="P45">
-        <v>3.25</v>
+        <v>4.46</v>
       </c>
       <c r="Q45">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R45">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S45">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="U45">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X45">
         <v>1.04</v>
@@ -7680,28 +7680,28 @@
         <v>1.25</v>
       </c>
       <c r="Z45">
-        <v>3.3</v>
+        <v>4.03</v>
       </c>
       <c r="AA45">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AB45">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AC45">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="AD45">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE45">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="O46">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q46">
-        <v>2.28</v>
+        <v>3.22</v>
       </c>
       <c r="R46">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T46">
         <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
+        <v>1.47</v>
+      </c>
+      <c r="W46">
+        <v>1.07</v>
+      </c>
+      <c r="X46">
+        <v>1.05</v>
+      </c>
+      <c r="Y46">
+        <v>1.22</v>
+      </c>
+      <c r="Z46">
+        <v>3.92</v>
+      </c>
+      <c r="AA46">
+        <v>1.72</v>
+      </c>
+      <c r="AB46">
+        <v>2.08</v>
+      </c>
+      <c r="AC46">
+        <v>2.64</v>
+      </c>
+      <c r="AD46">
         <v>1.44</v>
       </c>
-      <c r="W46">
-        <v>1.06</v>
-      </c>
-      <c r="X46">
-        <v>1.02</v>
-      </c>
-      <c r="Y46">
-        <v>1.24</v>
-      </c>
-      <c r="Z46">
-        <v>4.01</v>
-      </c>
-      <c r="AA46">
-        <v>1.67</v>
-      </c>
-      <c r="AB46">
-        <v>2.04</v>
-      </c>
-      <c r="AC46">
-        <v>2.76</v>
-      </c>
-      <c r="AD46">
-        <v>1.38</v>
-      </c>
       <c r="AE46">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AG46">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AK46">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>3.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q47">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="R47">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S47">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>2.91</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="Z47">
-        <v>4.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA47">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AB47">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AC47">
-        <v>2.54</v>
+        <v>3.18</v>
       </c>
       <c r="AD47">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AG47">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK47">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O48">
         <v>3.4</v>
       </c>
       <c r="P48">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q48">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="R48">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S48">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T48">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U48">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="V48">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W48">
+        <v>1.06</v>
+      </c>
+      <c r="X48">
+        <v>1.04</v>
+      </c>
+      <c r="Y48">
+        <v>1.28</v>
+      </c>
+      <c r="Z48">
+        <v>3.7</v>
+      </c>
+      <c r="AA48">
+        <v>1.9</v>
+      </c>
+      <c r="AB48">
+        <v>1.9</v>
+      </c>
+      <c r="AC48">
+        <v>3.05</v>
+      </c>
+      <c r="AD48">
+        <v>1.35</v>
+      </c>
+      <c r="AE48">
         <v>1.08</v>
       </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>1.23</v>
-      </c>
-      <c r="Z48">
-        <v>3.44</v>
-      </c>
-      <c r="AA48">
-        <v>1.96</v>
-      </c>
-      <c r="AB48">
-        <v>1.85</v>
-      </c>
-      <c r="AC48">
-        <v>3.3</v>
-      </c>
-      <c r="AD48">
-        <v>1.25</v>
-      </c>
-      <c r="AE48">
-        <v>1.11</v>
-      </c>
       <c r="AF48">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG48">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="O49">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q49">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="R49">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T49">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V49">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z49">
         <v>3.3</v>
       </c>
       <c r="AA49">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB49">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC49">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="AD49">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE49">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG49">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.6</v>
+        <v>1.94</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
-        <v>2.56</v>
+        <v>3.33</v>
       </c>
       <c r="Q50">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="R50">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T50">
         <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="V50">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W50">
         <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA50">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AC50">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="AD50">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE50">
         <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,16 +8622,16 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="P51">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="Q51">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="R51">
         <v>2.12</v>
@@ -8640,46 +8640,46 @@
         <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U51">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="V51">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
+        <v>1.23</v>
+      </c>
+      <c r="Z51">
+        <v>3.44</v>
+      </c>
+      <c r="AA51">
+        <v>1.85</v>
+      </c>
+      <c r="AB51">
+        <v>1.9</v>
+      </c>
+      <c r="AC51">
+        <v>2.86</v>
+      </c>
+      <c r="AD51">
         <v>1.3</v>
       </c>
-      <c r="Z51">
-        <v>3.45</v>
-      </c>
-      <c r="AA51">
-        <v>1.89</v>
-      </c>
-      <c r="AB51">
-        <v>1.88</v>
-      </c>
-      <c r="AC51">
-        <v>3.05</v>
-      </c>
-      <c r="AD51">
-        <v>1.29</v>
-      </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AG51">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O52">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
         <v>2.25</v>
       </c>
       <c r="Q52">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S52">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="U52">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V52">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
         <v>1.07</v>
@@ -8827,10 +8827,10 @@
         <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC52">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD52">
         <v>1.34</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK52">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,34 +8951,34 @@
         <v>2.5</v>
       </c>
       <c r="O53">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q53">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="R53">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="S53">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="U53">
         <v>2.62</v>
       </c>
       <c r="V53">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W53">
         <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
         <v>1.22</v>
@@ -8987,25 +8987,25 @@
         <v>3.54</v>
       </c>
       <c r="AA53">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB53">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC53">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AD53">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE53">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF53">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9277,13 +9277,13 @@
         <v>3.1</v>
       </c>
       <c r="O55">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="P55">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="Q55">
-        <v>4.26</v>
+        <v>4.08</v>
       </c>
       <c r="R55">
         <v>1.82</v>
@@ -9295,10 +9295,10 @@
         <v>2.27</v>
       </c>
       <c r="U55">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="V55">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W55">
         <v>1.01</v>
@@ -9310,28 +9310,28 @@
         <v>1.53</v>
       </c>
       <c r="Z55">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="AA55">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB55">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC55">
         <v>5</v>
       </c>
       <c r="AD55">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE55">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AG55">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.38</v>
       </c>
       <c r="AK55">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL55">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -1293,7 +1293,7 @@
         <v>7.5</v>
       </c>
       <c r="P6">
-        <v>12.01</v>
+        <v>12</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O12">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
         <v>2.97</v>
@@ -2277,22 +2277,22 @@
         <v>2.5</v>
       </c>
       <c r="R12">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
         <v>2.4</v>
       </c>
       <c r="V12">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2304,25 +2304,25 @@
         <v>4.05</v>
       </c>
       <c r="AA12">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB12">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AC12">
         <v>2.49</v>
       </c>
       <c r="AD12">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AE12">
         <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG12">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>5.62</v>
+        <v>2.8</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
+        <v>1.37</v>
+      </c>
+      <c r="T13">
+        <v>2.88</v>
+      </c>
+      <c r="U13">
+        <v>2.7</v>
+      </c>
+      <c r="V13">
+        <v>1.39</v>
+      </c>
+      <c r="W13">
+        <v>1.03</v>
+      </c>
+      <c r="X13">
+        <v>1.02</v>
+      </c>
+      <c r="Y13">
+        <v>1.31</v>
+      </c>
+      <c r="Z13">
+        <v>3.35</v>
+      </c>
+      <c r="AA13">
+        <v>1.91</v>
+      </c>
+      <c r="AB13">
+        <v>1.76</v>
+      </c>
+      <c r="AC13">
+        <v>3.5</v>
+      </c>
+      <c r="AD13">
+        <v>1.23</v>
+      </c>
+      <c r="AE13">
+        <v>1.04</v>
+      </c>
+      <c r="AF13">
+        <v>1.75</v>
+      </c>
+      <c r="AG13">
+        <v>2.04</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
         <v>1.25</v>
       </c>
-      <c r="T13">
-        <v>3.5</v>
-      </c>
-      <c r="U13">
-        <v>2.26</v>
-      </c>
-      <c r="V13">
-        <v>1.54</v>
-      </c>
-      <c r="W13">
-        <v>1.09</v>
-      </c>
-      <c r="X13">
-        <v>1.01</v>
-      </c>
-      <c r="Y13">
-        <v>1.13</v>
-      </c>
-      <c r="Z13">
-        <v>4.5</v>
-      </c>
-      <c r="AA13">
-        <v>1.57</v>
-      </c>
-      <c r="AB13">
-        <v>2.25</v>
-      </c>
-      <c r="AC13">
-        <v>2.38</v>
-      </c>
-      <c r="AD13">
-        <v>1.56</v>
-      </c>
-      <c r="AE13">
-        <v>1.21</v>
-      </c>
-      <c r="AF13">
-        <v>1.67</v>
-      </c>
-      <c r="AG13">
-        <v>2.15</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.22</v>
-      </c>
       <c r="AK13">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="Q14">
-        <v>2.8</v>
+        <v>5.62</v>
       </c>
       <c r="R14">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U14">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="V14">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA14">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AB14">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="AC14">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD14">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AE14">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.55</v>
+        <v>1.09</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2766,22 +2766,22 @@
         <v>3.3</v>
       </c>
       <c r="R15">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,10 +2793,10 @@
         <v>3.9</v>
       </c>
       <c r="AA15">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB15">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC15">
         <v>2.7</v>
@@ -2805,13 +2805,13 @@
         <v>1.41</v>
       </c>
       <c r="AE15">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
         <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AK15">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="O18">
         <v>4.1</v>
       </c>
       <c r="P18">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q18">
         <v>3.12</v>
       </c>
       <c r="R18">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="S18">
         <v>1.11</v>
       </c>
       <c r="T18">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="U18">
         <v>1.62</v>
@@ -3270,7 +3270,7 @@
         <v>2.2</v>
       </c>
       <c r="W18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X18">
         <v>1</v>
@@ -3279,25 +3279,25 @@
         <v>1.01</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA18">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AB18">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="AC18">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AD18">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="AE18">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="AF18">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AG18">
         <v>2.8</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK18">
         <v>1.39</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="O22">
+        <v>3.75</v>
+      </c>
+      <c r="P22">
+        <v>2.28</v>
+      </c>
+      <c r="Q22">
+        <v>3</v>
+      </c>
+      <c r="R22">
+        <v>2.55</v>
+      </c>
+      <c r="S22">
+        <v>1.22</v>
+      </c>
+      <c r="T22">
         <v>3.9</v>
       </c>
-      <c r="P22">
-        <v>1.6</v>
-      </c>
-      <c r="Q22">
-        <v>4.4</v>
-      </c>
-      <c r="R22">
-        <v>2.6</v>
-      </c>
-      <c r="S22">
-        <v>1.2</v>
-      </c>
-      <c r="T22">
-        <v>4.1</v>
-      </c>
       <c r="U22">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="V22">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W22">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -3931,28 +3931,28 @@
         <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA22">
+        <v>1.43</v>
+      </c>
+      <c r="AB22">
+        <v>2.46</v>
+      </c>
+      <c r="AC22">
+        <v>2.12</v>
+      </c>
+      <c r="AD22">
+        <v>1.64</v>
+      </c>
+      <c r="AE22">
+        <v>1.24</v>
+      </c>
+      <c r="AF22">
         <v>1.4</v>
       </c>
-      <c r="AB22">
-        <v>2.75</v>
-      </c>
-      <c r="AC22">
-        <v>2</v>
-      </c>
-      <c r="AD22">
-        <v>1.73</v>
-      </c>
-      <c r="AE22">
-        <v>1.32</v>
-      </c>
-      <c r="AF22">
-        <v>1.43</v>
-      </c>
       <c r="AG22">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,34 +4058,34 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="O23">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P23">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="R23">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U23">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="V23">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4094,28 +4094,28 @@
         <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA23">
+        <v>1.4</v>
+      </c>
+      <c r="AB23">
+        <v>2.75</v>
+      </c>
+      <c r="AC23">
+        <v>2</v>
+      </c>
+      <c r="AD23">
+        <v>1.73</v>
+      </c>
+      <c r="AE23">
+        <v>1.32</v>
+      </c>
+      <c r="AF23">
         <v>1.43</v>
       </c>
-      <c r="AB23">
-        <v>2.46</v>
-      </c>
-      <c r="AC23">
-        <v>2.12</v>
-      </c>
-      <c r="AD23">
-        <v>1.64</v>
-      </c>
-      <c r="AE23">
-        <v>1.24</v>
-      </c>
-      <c r="AF23">
-        <v>1.4</v>
-      </c>
       <c r="AG23">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4387,16 +4387,16 @@
         <v>4.5</v>
       </c>
       <c r="O25">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P25">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q25">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R25">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="S25">
         <v>1.15</v>
@@ -4405,10 +4405,10 @@
         <v>4.45</v>
       </c>
       <c r="U25">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V25">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W25">
         <v>1.22</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z25">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA25">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AB25">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AC25">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AD25">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AE25">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AF25">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG25">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK25">
         <v>1.17</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="P27">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="Q27">
-        <v>4.34</v>
+        <v>2.8</v>
       </c>
       <c r="R27">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T27">
-        <v>3.24</v>
+        <v>2.59</v>
       </c>
       <c r="U27">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="V27">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.65</v>
+        <v>3.14</v>
       </c>
       <c r="AA27">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AD27">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE27">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AG27">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,65 +4873,65 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="O28">
+        <v>4.2</v>
+      </c>
+      <c r="P28">
+        <v>5.75</v>
+      </c>
+      <c r="Q28">
+        <v>2.12</v>
+      </c>
+      <c r="R28">
+        <v>2.16</v>
+      </c>
+      <c r="S28">
+        <v>1.38</v>
+      </c>
+      <c r="T28">
+        <v>2.77</v>
+      </c>
+      <c r="U28">
+        <v>2.77</v>
+      </c>
+      <c r="V28">
+        <v>1.38</v>
+      </c>
+      <c r="W28">
+        <v>1.04</v>
+      </c>
+      <c r="X28">
+        <v>1.03</v>
+      </c>
+      <c r="Y28">
+        <v>1.27</v>
+      </c>
+      <c r="Z28">
+        <v>3.14</v>
+      </c>
+      <c r="AA28">
+        <v>1.89</v>
+      </c>
+      <c r="AB28">
+        <v>1.85</v>
+      </c>
+      <c r="AC28">
         <v>3.4</v>
       </c>
-      <c r="P28">
-        <v>2.5</v>
-      </c>
-      <c r="Q28">
-        <v>3.02</v>
-      </c>
-      <c r="R28">
-        <v>2.09</v>
-      </c>
-      <c r="S28">
-        <v>1.37</v>
-      </c>
-      <c r="T28">
-        <v>2.81</v>
-      </c>
-      <c r="U28">
-        <v>2.84</v>
-      </c>
-      <c r="V28">
-        <v>1.36</v>
-      </c>
-      <c r="W28">
-        <v>1.05</v>
-      </c>
-      <c r="X28">
-        <v>1</v>
-      </c>
-      <c r="Y28">
-        <v>1.3</v>
-      </c>
-      <c r="Z28">
-        <v>3.08</v>
-      </c>
-      <c r="AA28">
+      <c r="AD28">
+        <v>1.29</v>
+      </c>
+      <c r="AE28">
+        <v>1.06</v>
+      </c>
+      <c r="AF28">
         <v>1.95</v>
       </c>
-      <c r="AB28">
-        <v>1.78</v>
-      </c>
-      <c r="AC28">
-        <v>3.34</v>
-      </c>
-      <c r="AD28">
-        <v>1.24</v>
-      </c>
-      <c r="AE28">
-        <v>1.05</v>
-      </c>
-      <c r="AF28">
+      <c r="AG28">
         <v>1.75</v>
       </c>
-      <c r="AG28">
-        <v>1.97</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.43</v>
+        <v>2.28</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.83</v>
+        <v>3.7</v>
       </c>
       <c r="O29">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>4.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q29">
-        <v>2.33</v>
+        <v>4.34</v>
       </c>
       <c r="R29">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S29">
         <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="U29">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V29">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z29">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="AA29">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB29">
         <v>1.95</v>
       </c>
       <c r="AC29">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AD29">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE29">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.94</v>
+        <v>1.18</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.68</v>
+        <v>3.6</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>4.41</v>
+        <v>2.05</v>
       </c>
       <c r="Q30">
-        <v>2.27</v>
+        <v>4.13</v>
       </c>
       <c r="R30">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S30">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="U30">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="V30">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z30">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA30">
+        <v>1.95</v>
+      </c>
+      <c r="AB30">
         <v>1.85</v>
       </c>
-      <c r="AB30">
-        <v>1.95</v>
-      </c>
       <c r="AC30">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="AD30">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>2.02</v>
+        <v>1.19</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="Q31">
-        <v>4.13</v>
+        <v>2.73</v>
       </c>
       <c r="R31">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="S31">
         <v>1.33</v>
       </c>
       <c r="T31">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="U31">
         <v>2.69</v>
@@ -5389,7 +5389,7 @@
         <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5398,16 +5398,16 @@
         <v>1.24</v>
       </c>
       <c r="Z31">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AA31">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB31">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC31">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="AD31">
         <v>1.28</v>
@@ -5416,10 +5416,10 @@
         <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK31">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
-        <v>2.73</v>
+        <v>2.33</v>
       </c>
       <c r="R32">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="S32">
         <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="U32">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
+        <v>1.22</v>
+      </c>
+      <c r="Z32">
+        <v>3.72</v>
+      </c>
+      <c r="AA32">
+        <v>1.83</v>
+      </c>
+      <c r="AB32">
+        <v>1.95</v>
+      </c>
+      <c r="AC32">
+        <v>3.14</v>
+      </c>
+      <c r="AD32">
+        <v>1.35</v>
+      </c>
+      <c r="AE32">
+        <v>1.13</v>
+      </c>
+      <c r="AF32">
+        <v>1.73</v>
+      </c>
+      <c r="AG32">
+        <v>2</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.24</v>
       </c>
-      <c r="Z32">
-        <v>3.58</v>
-      </c>
-      <c r="AA32">
-        <v>1.88</v>
-      </c>
-      <c r="AB32">
-        <v>1.87</v>
-      </c>
-      <c r="AC32">
-        <v>3.08</v>
-      </c>
-      <c r="AD32">
-        <v>1.28</v>
-      </c>
-      <c r="AE32">
-        <v>1.07</v>
-      </c>
-      <c r="AF32">
-        <v>1.7</v>
-      </c>
-      <c r="AG32">
-        <v>2.04</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.28</v>
-      </c>
       <c r="AK32">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,65 +6014,65 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="O35">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3.1</v>
+        <v>4.41</v>
       </c>
       <c r="Q35">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T35">
-        <v>2.59</v>
+        <v>3.05</v>
       </c>
       <c r="U35">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="V35">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA35">
+        <v>1.85</v>
+      </c>
+      <c r="AB35">
+        <v>1.95</v>
+      </c>
+      <c r="AC35">
+        <v>2.95</v>
+      </c>
+      <c r="AD35">
+        <v>1.32</v>
+      </c>
+      <c r="AE35">
+        <v>1.08</v>
+      </c>
+      <c r="AF35">
+        <v>1.8</v>
+      </c>
+      <c r="AG35">
         <v>2</v>
       </c>
-      <c r="AB35">
-        <v>1.8</v>
-      </c>
-      <c r="AC35">
-        <v>3.4</v>
-      </c>
-      <c r="AD35">
-        <v>1.22</v>
-      </c>
-      <c r="AE35">
-        <v>1.04</v>
-      </c>
-      <c r="AF35">
-        <v>1.77</v>
-      </c>
-      <c r="AG35">
-        <v>1.94</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>1.52</v>
+        <v>2.02</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="O36">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>5.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q36">
-        <v>2.12</v>
+        <v>3.02</v>
       </c>
       <c r="R36">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="S36">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T36">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U36">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="V36">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA36">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AB36">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC36">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD36">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF36">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
-        <v>2.28</v>
+        <v>1.43</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O39">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="P39">
         <v>4.74</v>
@@ -6678,52 +6678,52 @@
         <v>2.22</v>
       </c>
       <c r="R39">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S39">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="U39">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V39">
         <v>1.43</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA39">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AB39">
         <v>1.9</v>
       </c>
       <c r="AC39">
-        <v>2.94</v>
+        <v>2.71</v>
       </c>
       <c r="AD39">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG39">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,25 +6832,25 @@
         <v>2.25</v>
       </c>
       <c r="O40">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q40">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="R40">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S40">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
         <v>2.85</v>
       </c>
       <c r="U40">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V40">
         <v>1.39</v>
@@ -6859,19 +6859,19 @@
         <v>1.05</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
         <v>3.3</v>
       </c>
       <c r="AA40">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB40">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC40">
         <v>3.3</v>
@@ -6880,13 +6880,13 @@
         <v>1.28</v>
       </c>
       <c r="AE40">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK40">
         <v>1.62</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="O41">
         <v>3.4</v>
       </c>
       <c r="P41">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q41">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S41">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
         <v>3</v>
       </c>
       <c r="U41">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="V41">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
         <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z41">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AA41">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB41">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC41">
         <v>3.21</v>
       </c>
       <c r="AD41">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
         <v>1.66</v>
       </c>
       <c r="AG41">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK41">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G42">
@@ -7158,61 +7158,61 @@
         <v>2</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q42">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="R42">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
+        <v>1.4</v>
+      </c>
+      <c r="T42">
+        <v>2.69</v>
+      </c>
+      <c r="U42">
+        <v>2.89</v>
+      </c>
+      <c r="V42">
         <v>1.33</v>
       </c>
-      <c r="T42">
-        <v>3.02</v>
-      </c>
-      <c r="U42">
-        <v>2.57</v>
-      </c>
-      <c r="V42">
-        <v>1.44</v>
-      </c>
       <c r="W42">
+        <v>1.04</v>
+      </c>
+      <c r="X42">
         <v>1.06</v>
       </c>
-      <c r="X42">
-        <v>1</v>
-      </c>
       <c r="Y42">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z42">
-        <v>4.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA42">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC42">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="AD42">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P43">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q43">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="R43">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T43">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="U43">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="V43">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="W43">
+        <v>1.07</v>
+      </c>
+      <c r="X43">
         <v>1.04</v>
       </c>
-      <c r="X43">
-        <v>1.01</v>
-      </c>
       <c r="Y43">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z43">
-        <v>3.44</v>
+        <v>4.33</v>
       </c>
       <c r="AA43">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB43">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AC43">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AD43">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AE43">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF43">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,65 +7481,65 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>3.1</v>
+        <v>4.03</v>
       </c>
       <c r="Q44">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R44">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="S44">
+        <v>1.3</v>
+      </c>
+      <c r="T44">
+        <v>3.2</v>
+      </c>
+      <c r="U44">
+        <v>2.65</v>
+      </c>
+      <c r="V44">
         <v>1.42</v>
       </c>
-      <c r="T44">
-        <v>2.65</v>
-      </c>
-      <c r="U44">
-        <v>2.89</v>
-      </c>
-      <c r="V44">
-        <v>1.38</v>
-      </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
         <v>1.03</v>
       </c>
       <c r="Y44">
+        <v>1.23</v>
+      </c>
+      <c r="Z44">
+        <v>3.55</v>
+      </c>
+      <c r="AA44">
+        <v>1.9</v>
+      </c>
+      <c r="AB44">
+        <v>1.9</v>
+      </c>
+      <c r="AC44">
+        <v>3.1</v>
+      </c>
+      <c r="AD44">
         <v>1.33</v>
       </c>
-      <c r="Z44">
-        <v>2.95</v>
-      </c>
-      <c r="AA44">
+      <c r="AE44">
+        <v>1.07</v>
+      </c>
+      <c r="AF44">
+        <v>1.67</v>
+      </c>
+      <c r="AG44">
         <v>2</v>
       </c>
-      <c r="AB44">
-        <v>1.8</v>
-      </c>
-      <c r="AC44">
-        <v>3.67</v>
-      </c>
-      <c r="AD44">
-        <v>1.29</v>
-      </c>
-      <c r="AE44">
-        <v>1.1</v>
-      </c>
-      <c r="AF44">
-        <v>1.77</v>
-      </c>
-      <c r="AG44">
-        <v>1.94</v>
-      </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,34 +7644,34 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="O45">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
-        <v>4.46</v>
+        <v>3.5</v>
       </c>
       <c r="Q45">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="R45">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="S45">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T45">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="U45">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="V45">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
         <v>1.04</v>
@@ -7680,28 +7680,28 @@
         <v>1.25</v>
       </c>
       <c r="Z45">
-        <v>4.03</v>
+        <v>3.3</v>
       </c>
       <c r="AA45">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB45">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AC45">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="AD45">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AE45">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK45">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.7</v>
+        <v>1.74</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="P46">
-        <v>2.45</v>
+        <v>4.46</v>
       </c>
       <c r="Q46">
-        <v>3.22</v>
+        <v>2.3</v>
       </c>
       <c r="R46">
         <v>2.17</v>
       </c>
       <c r="S46">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V46">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
         <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z46">
-        <v>3.92</v>
+        <v>4.03</v>
       </c>
       <c r="AA46">
         <v>1.72</v>
       </c>
       <c r="AB46">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC46">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AD46">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE46">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.44</v>
+        <v>2.04</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.6</v>
+        <v>1.94</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>2.7</v>
+        <v>3.33</v>
       </c>
       <c r="Q47">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="R47">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="S47">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T47">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.91</v>
+        <v>2.41</v>
       </c>
       <c r="V47">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="AA47">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AB47">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC47">
-        <v>3.18</v>
+        <v>2.54</v>
       </c>
       <c r="AD47">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF47">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AG47">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O48">
         <v>3.4</v>
@@ -8142,55 +8142,55 @@
         <v>2.7</v>
       </c>
       <c r="Q48">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="R48">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="S48">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="U48">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="V48">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z48">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="AA48">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB48">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC48">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="AD48">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF48">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG48">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="P49">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q49">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="R49">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S49">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="U49">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="V49">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W49">
         <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z49">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA49">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB49">
         <v>1.9</v>
       </c>
       <c r="AC49">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="AD49">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>3.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q50">
-        <v>2.45</v>
+        <v>3.22</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S50">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
         <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V50">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z50">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB50">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AC50">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="AD50">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AK50">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="O51">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
-        <v>2.32</v>
+        <v>2.89</v>
       </c>
       <c r="R51">
         <v>2.12</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T51">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U51">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V51">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
         <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z51">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="AA51">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB51">
         <v>1.9</v>
       </c>
       <c r="AC51">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="AD51">
+        <v>1.35</v>
+      </c>
+      <c r="AE51">
+        <v>1.08</v>
+      </c>
+      <c r="AF51">
+        <v>1.68</v>
+      </c>
+      <c r="AG51">
+        <v>2.06</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.3</v>
       </c>
-      <c r="AE51">
-        <v>1.12</v>
-      </c>
-      <c r="AF51">
-        <v>1.76</v>
-      </c>
-      <c r="AG51">
-        <v>1.96</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.26</v>
-      </c>
       <c r="AK51">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.94</v>
+        <v>3.24</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P52">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q52">
         <v>3.74</v>
@@ -8800,7 +8800,7 @@
         <v>2.14</v>
       </c>
       <c r="S52">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T52">
         <v>2.94</v>
@@ -8809,40 +8809,40 @@
         <v>2.59</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W52">
         <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z52">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AA52">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AB52">
         <v>2</v>
       </c>
       <c r="AC52">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD52">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AE52">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG52">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8954,58 +8954,58 @@
         <v>3.3</v>
       </c>
       <c r="P53">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="Q53">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="R53">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>3.19</v>
+        <v>2.8</v>
       </c>
       <c r="U53">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V53">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W53">
         <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y53">
         <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AA53">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB53">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC53">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AD53">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE53">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF53">
         <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,28 +9114,28 @@
         <v>1.94</v>
       </c>
       <c r="O54">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P54">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="Q54">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="R54">
         <v>1.89</v>
       </c>
       <c r="S54">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T54">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="U54">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="V54">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W54">
         <v>1.02</v>
@@ -9153,22 +9153,22 @@
         <v>2.36</v>
       </c>
       <c r="AB54">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC54">
-        <v>4.34</v>
+        <v>4.51</v>
       </c>
       <c r="AD54">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF54">
         <v>1.8</v>
       </c>
       <c r="AG54">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
         <v>1.7</v>
@@ -9440,10 +9440,10 @@
         <v>1.55</v>
       </c>
       <c r="O56">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P56">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="Q56">
         <v>2.12</v>
@@ -9452,10 +9452,10 @@
         <v>2.12</v>
       </c>
       <c r="S56">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T56">
-        <v>2.27</v>
+        <v>2.88</v>
       </c>
       <c r="U56">
         <v>2.78</v>
@@ -9464,22 +9464,22 @@
         <v>1.36</v>
       </c>
       <c r="W56">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z56">
         <v>2.63</v>
       </c>
       <c r="AA56">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AB56">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC56">
         <v>3.2</v>
@@ -9488,13 +9488,13 @@
         <v>1.29</v>
       </c>
       <c r="AE56">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF56">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG56">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AK56">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AL56">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="Q13">
-        <v>2.8</v>
+        <v>5.62</v>
       </c>
       <c r="R13">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="V13">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA13">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="AC13">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD13">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AE13">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AF13">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.55</v>
+        <v>1.09</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="Q14">
-        <v>5.62</v>
+        <v>2.8</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
+        <v>1.37</v>
+      </c>
+      <c r="T14">
+        <v>2.88</v>
+      </c>
+      <c r="U14">
+        <v>2.7</v>
+      </c>
+      <c r="V14">
+        <v>1.39</v>
+      </c>
+      <c r="W14">
+        <v>1.03</v>
+      </c>
+      <c r="X14">
+        <v>1.02</v>
+      </c>
+      <c r="Y14">
+        <v>1.31</v>
+      </c>
+      <c r="Z14">
+        <v>3.35</v>
+      </c>
+      <c r="AA14">
+        <v>1.91</v>
+      </c>
+      <c r="AB14">
+        <v>1.76</v>
+      </c>
+      <c r="AC14">
+        <v>3.5</v>
+      </c>
+      <c r="AD14">
+        <v>1.23</v>
+      </c>
+      <c r="AE14">
+        <v>1.04</v>
+      </c>
+      <c r="AF14">
+        <v>1.75</v>
+      </c>
+      <c r="AG14">
+        <v>2.04</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.25</v>
       </c>
-      <c r="T14">
-        <v>3.5</v>
-      </c>
-      <c r="U14">
-        <v>2.26</v>
-      </c>
-      <c r="V14">
-        <v>1.54</v>
-      </c>
-      <c r="W14">
-        <v>1.09</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.13</v>
-      </c>
-      <c r="Z14">
-        <v>4.5</v>
-      </c>
-      <c r="AA14">
-        <v>1.57</v>
-      </c>
-      <c r="AB14">
-        <v>2.25</v>
-      </c>
-      <c r="AC14">
-        <v>2.38</v>
-      </c>
-      <c r="AD14">
-        <v>1.56</v>
-      </c>
-      <c r="AE14">
-        <v>1.21</v>
-      </c>
-      <c r="AF14">
-        <v>1.67</v>
-      </c>
-      <c r="AG14">
-        <v>2.15</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.22</v>
-      </c>
       <c r="AK14">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="O16">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="P16">
-        <v>1.33</v>
+        <v>2.71</v>
       </c>
       <c r="Q16">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="R16">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="S16">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="T16">
-        <v>2.56</v>
+        <v>2.13</v>
       </c>
       <c r="U16">
-        <v>2.91</v>
+        <v>3.88</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y16">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="Z16">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="AA16">
-        <v>2.09</v>
+        <v>2.75</v>
       </c>
       <c r="AB16">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AC16">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="AD16">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="AG16">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>2.84</v>
+        <v>1.4</v>
       </c>
       <c r="AK16">
-        <v>1.07</v>
+        <v>1.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="O17">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="P17">
-        <v>2.71</v>
+        <v>1.33</v>
       </c>
       <c r="Q17">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="S17">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.13</v>
+        <v>2.56</v>
       </c>
       <c r="U17">
-        <v>3.88</v>
+        <v>2.91</v>
       </c>
       <c r="V17">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="AA17">
-        <v>2.75</v>
+        <v>2.09</v>
       </c>
       <c r="AB17">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AC17">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD17">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF17">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="AG17">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.4</v>
+        <v>2.84</v>
       </c>
       <c r="AK17">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,37 +4710,37 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="O27">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="P27">
-        <v>3.1</v>
+        <v>5.75</v>
       </c>
       <c r="Q27">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S27">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="U27">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V27">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
         <v>1.27</v>
@@ -4749,41 +4749,41 @@
         <v>3.14</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB27">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC27">
         <v>3.4</v>
       </c>
       <c r="AD27">
+        <v>1.29</v>
+      </c>
+      <c r="AE27">
+        <v>1.06</v>
+      </c>
+      <c r="AF27">
+        <v>1.95</v>
+      </c>
+      <c r="AG27">
+        <v>1.75</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.22</v>
       </c>
-      <c r="AE27">
-        <v>1.04</v>
-      </c>
-      <c r="AF27">
-        <v>1.77</v>
-      </c>
-      <c r="AG27">
-        <v>1.94</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.28</v>
-      </c>
       <c r="AK27">
-        <v>1.52</v>
+        <v>2.28</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="O28">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q28">
-        <v>2.12</v>
+        <v>2.73</v>
       </c>
       <c r="R28">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U28">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="V28">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AA28">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB28">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC28">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD28">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG28">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>2.28</v>
+        <v>1.64</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="O30">
+        <v>4.33</v>
+      </c>
+      <c r="P30">
+        <v>5.5</v>
+      </c>
+      <c r="Q30">
+        <v>2.01</v>
+      </c>
+      <c r="R30">
+        <v>2.34</v>
+      </c>
+      <c r="S30">
+        <v>1.29</v>
+      </c>
+      <c r="T30">
         <v>3.3</v>
       </c>
-      <c r="P30">
-        <v>2.05</v>
-      </c>
-      <c r="Q30">
-        <v>4.13</v>
-      </c>
-      <c r="R30">
-        <v>2.17</v>
-      </c>
-      <c r="S30">
-        <v>1.33</v>
-      </c>
-      <c r="T30">
-        <v>3.07</v>
-      </c>
       <c r="U30">
-        <v>2.69</v>
+        <v>2.52</v>
       </c>
       <c r="V30">
+        <v>1.52</v>
+      </c>
+      <c r="W30">
+        <v>1.1</v>
+      </c>
+      <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
+        <v>1.21</v>
+      </c>
+      <c r="Z30">
+        <v>4.32</v>
+      </c>
+      <c r="AA30">
+        <v>1.66</v>
+      </c>
+      <c r="AB30">
+        <v>2.15</v>
+      </c>
+      <c r="AC30">
+        <v>2.65</v>
+      </c>
+      <c r="AD30">
         <v>1.4</v>
       </c>
-      <c r="W30">
-        <v>1.06</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.24</v>
-      </c>
-      <c r="Z30">
-        <v>3.34</v>
-      </c>
-      <c r="AA30">
-        <v>1.95</v>
-      </c>
-      <c r="AB30">
-        <v>1.85</v>
-      </c>
-      <c r="AC30">
-        <v>3.21</v>
-      </c>
-      <c r="AD30">
-        <v>1.28</v>
-      </c>
       <c r="AE30">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF30">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG30">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK30">
-        <v>1.19</v>
+        <v>2.43</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q31">
-        <v>2.73</v>
+        <v>4.13</v>
       </c>
       <c r="R31">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="S31">
         <v>1.33</v>
       </c>
       <c r="T31">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="U31">
         <v>2.69</v>
@@ -5389,7 +5389,7 @@
         <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5398,16 +5398,16 @@
         <v>1.24</v>
       </c>
       <c r="Z31">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AA31">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB31">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC31">
-        <v>3.08</v>
+        <v>3.21</v>
       </c>
       <c r="AD31">
         <v>1.28</v>
@@ -5416,10 +5416,10 @@
         <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG31">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK31">
-        <v>1.64</v>
+        <v>1.19</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q32">
-        <v>2.33</v>
+        <v>3.02</v>
       </c>
       <c r="R32">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T32">
-        <v>3.14</v>
+        <v>2.81</v>
       </c>
       <c r="U32">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="V32">
+        <v>1.36</v>
+      </c>
+      <c r="W32">
+        <v>1.05</v>
+      </c>
+      <c r="X32">
+        <v>1</v>
+      </c>
+      <c r="Y32">
+        <v>1.3</v>
+      </c>
+      <c r="Z32">
+        <v>3.08</v>
+      </c>
+      <c r="AA32">
+        <v>1.95</v>
+      </c>
+      <c r="AB32">
+        <v>1.78</v>
+      </c>
+      <c r="AC32">
+        <v>3.34</v>
+      </c>
+      <c r="AD32">
+        <v>1.24</v>
+      </c>
+      <c r="AE32">
+        <v>1.05</v>
+      </c>
+      <c r="AF32">
+        <v>1.75</v>
+      </c>
+      <c r="AG32">
+        <v>1.97</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.28</v>
+      </c>
+      <c r="AK32">
         <v>1.43</v>
-      </c>
-      <c r="W32">
-        <v>1.07</v>
-      </c>
-      <c r="X32">
-        <v>1.04</v>
-      </c>
-      <c r="Y32">
-        <v>1.22</v>
-      </c>
-      <c r="Z32">
-        <v>3.72</v>
-      </c>
-      <c r="AA32">
-        <v>1.83</v>
-      </c>
-      <c r="AB32">
-        <v>1.95</v>
-      </c>
-      <c r="AC32">
-        <v>3.14</v>
-      </c>
-      <c r="AD32">
-        <v>1.35</v>
-      </c>
-      <c r="AE32">
-        <v>1.13</v>
-      </c>
-      <c r="AF32">
-        <v>1.73</v>
-      </c>
-      <c r="AG32">
-        <v>2</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.24</v>
-      </c>
-      <c r="AK32">
-        <v>1.94</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="O33">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q33">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="R33">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>2.77</v>
+        <v>3.14</v>
       </c>
       <c r="U33">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="V33">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.45</v>
+        <v>3.72</v>
       </c>
       <c r="AA33">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AB33">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD33">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="O34">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q34">
+        <v>2.8</v>
+      </c>
+      <c r="R34">
+        <v>2.08</v>
+      </c>
+      <c r="S34">
+        <v>1.38</v>
+      </c>
+      <c r="T34">
+        <v>2.77</v>
+      </c>
+      <c r="U34">
+        <v>2.93</v>
+      </c>
+      <c r="V34">
+        <v>1.39</v>
+      </c>
+      <c r="W34">
+        <v>1.05</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.3</v>
+      </c>
+      <c r="Z34">
+        <v>3.45</v>
+      </c>
+      <c r="AA34">
+        <v>1.99</v>
+      </c>
+      <c r="AB34">
+        <v>1.85</v>
+      </c>
+      <c r="AC34">
+        <v>3.2</v>
+      </c>
+      <c r="AD34">
+        <v>1.26</v>
+      </c>
+      <c r="AE34">
+        <v>1.06</v>
+      </c>
+      <c r="AF34">
+        <v>1.72</v>
+      </c>
+      <c r="AG34">
         <v>2.01</v>
       </c>
-      <c r="R34">
-        <v>2.34</v>
-      </c>
-      <c r="S34">
-        <v>1.29</v>
-      </c>
-      <c r="T34">
-        <v>3.3</v>
-      </c>
-      <c r="U34">
-        <v>2.52</v>
-      </c>
-      <c r="V34">
-        <v>1.52</v>
-      </c>
-      <c r="W34">
-        <v>1.1</v>
-      </c>
-      <c r="X34">
-        <v>1.03</v>
-      </c>
-      <c r="Y34">
-        <v>1.21</v>
-      </c>
-      <c r="Z34">
-        <v>4.32</v>
-      </c>
-      <c r="AA34">
-        <v>1.66</v>
-      </c>
-      <c r="AB34">
-        <v>2.15</v>
-      </c>
-      <c r="AC34">
-        <v>2.65</v>
-      </c>
-      <c r="AD34">
-        <v>1.4</v>
-      </c>
-      <c r="AE34">
-        <v>1.13</v>
-      </c>
-      <c r="AF34">
-        <v>1.8</v>
-      </c>
-      <c r="AG34">
-        <v>1.94</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AK34">
-        <v>2.43</v>
+        <v>1.47</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="P35">
-        <v>4.41</v>
+        <v>3.1</v>
       </c>
       <c r="Q35">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
-        <v>3.05</v>
+        <v>2.59</v>
       </c>
       <c r="U35">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
+        <v>1.27</v>
+      </c>
+      <c r="Z35">
+        <v>3.14</v>
+      </c>
+      <c r="AA35">
+        <v>2</v>
+      </c>
+      <c r="AB35">
+        <v>1.8</v>
+      </c>
+      <c r="AC35">
+        <v>3.4</v>
+      </c>
+      <c r="AD35">
         <v>1.22</v>
       </c>
-      <c r="Z35">
-        <v>3.5</v>
-      </c>
-      <c r="AA35">
-        <v>1.85</v>
-      </c>
-      <c r="AB35">
-        <v>1.95</v>
-      </c>
-      <c r="AC35">
-        <v>2.95</v>
-      </c>
-      <c r="AD35">
-        <v>1.32</v>
-      </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.75</v>
+        <v>1.68</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>2.5</v>
+        <v>4.41</v>
       </c>
       <c r="Q36">
-        <v>3.02</v>
+        <v>2.27</v>
       </c>
       <c r="R36">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="T36">
-        <v>2.81</v>
+        <v>3.05</v>
       </c>
       <c r="U36">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA36">
+        <v>1.85</v>
+      </c>
+      <c r="AB36">
         <v>1.95</v>
       </c>
-      <c r="AB36">
-        <v>1.78</v>
-      </c>
       <c r="AC36">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="AD36">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE36">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG36">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.57</v>
+        <v>2</v>
       </c>
       <c r="O41">
         <v>3.4</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q41">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="R41">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
+        <v>1.4</v>
+      </c>
+      <c r="T41">
+        <v>2.69</v>
+      </c>
+      <c r="U41">
+        <v>2.89</v>
+      </c>
+      <c r="V41">
         <v>1.33</v>
       </c>
-      <c r="T41">
-        <v>3</v>
-      </c>
-      <c r="U41">
-        <v>2.59</v>
-      </c>
-      <c r="V41">
-        <v>1.42</v>
-      </c>
       <c r="W41">
+        <v>1.04</v>
+      </c>
+      <c r="X41">
         <v>1.06</v>
       </c>
-      <c r="X41">
-        <v>1.04</v>
-      </c>
       <c r="Y41">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
+        <v>3.4</v>
+      </c>
+      <c r="AA41">
+        <v>2</v>
+      </c>
+      <c r="AB41">
+        <v>1.8</v>
+      </c>
+      <c r="AC41">
         <v>3.3</v>
       </c>
-      <c r="AA41">
-        <v>1.91</v>
-      </c>
-      <c r="AB41">
-        <v>1.96</v>
-      </c>
-      <c r="AC41">
-        <v>3.21</v>
-      </c>
       <c r="AD41">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE41">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AG41">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="O42">
         <v>3.4</v>
       </c>
       <c r="P42">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q42">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S42">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T42">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U42">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="V42">
+        <v>1.42</v>
+      </c>
+      <c r="W42">
+        <v>1.06</v>
+      </c>
+      <c r="X42">
+        <v>1.04</v>
+      </c>
+      <c r="Y42">
+        <v>1.24</v>
+      </c>
+      <c r="Z42">
+        <v>3.3</v>
+      </c>
+      <c r="AA42">
+        <v>1.91</v>
+      </c>
+      <c r="AB42">
+        <v>1.96</v>
+      </c>
+      <c r="AC42">
+        <v>3.21</v>
+      </c>
+      <c r="AD42">
+        <v>1.36</v>
+      </c>
+      <c r="AE42">
+        <v>1.14</v>
+      </c>
+      <c r="AF42">
+        <v>1.66</v>
+      </c>
+      <c r="AG42">
+        <v>2.06</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.33</v>
       </c>
-      <c r="W42">
-        <v>1.04</v>
-      </c>
-      <c r="X42">
-        <v>1.06</v>
-      </c>
-      <c r="Y42">
-        <v>1.3</v>
-      </c>
-      <c r="Z42">
-        <v>3.4</v>
-      </c>
-      <c r="AA42">
-        <v>2</v>
-      </c>
-      <c r="AB42">
-        <v>1.8</v>
-      </c>
-      <c r="AC42">
-        <v>3.3</v>
-      </c>
-      <c r="AD42">
-        <v>1.25</v>
-      </c>
-      <c r="AE42">
-        <v>1.09</v>
-      </c>
-      <c r="AF42">
-        <v>1.8</v>
-      </c>
-      <c r="AG42">
-        <v>1.93</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.3</v>
-      </c>
       <c r="AK42">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="O43">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>3.3</v>
+        <v>4.03</v>
       </c>
       <c r="Q43">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R43">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S43">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T43">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="V43">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W43">
+        <v>1.08</v>
+      </c>
+      <c r="X43">
+        <v>1.03</v>
+      </c>
+      <c r="Y43">
+        <v>1.23</v>
+      </c>
+      <c r="Z43">
+        <v>3.55</v>
+      </c>
+      <c r="AA43">
+        <v>1.9</v>
+      </c>
+      <c r="AB43">
+        <v>1.9</v>
+      </c>
+      <c r="AC43">
+        <v>3.1</v>
+      </c>
+      <c r="AD43">
+        <v>1.33</v>
+      </c>
+      <c r="AE43">
         <v>1.07</v>
       </c>
-      <c r="X43">
-        <v>1.04</v>
-      </c>
-      <c r="Y43">
-        <v>1.18</v>
-      </c>
-      <c r="Z43">
-        <v>4.33</v>
-      </c>
-      <c r="AA43">
+      <c r="AF43">
         <v>1.67</v>
       </c>
-      <c r="AB43">
-        <v>2.14</v>
-      </c>
-      <c r="AC43">
-        <v>2.82</v>
-      </c>
-      <c r="AD43">
-        <v>1.45</v>
-      </c>
-      <c r="AE43">
-        <v>1.17</v>
-      </c>
-      <c r="AF43">
-        <v>1.62</v>
-      </c>
       <c r="AG43">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="O44">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P44">
-        <v>4.03</v>
+        <v>3.3</v>
       </c>
       <c r="Q44">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R44">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S44">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T44">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U44">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V44">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z44">
-        <v>3.55</v>
+        <v>4.33</v>
       </c>
       <c r="AA44">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB44">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AC44">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AD44">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG44">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="O45">
+        <v>3.8</v>
+      </c>
+      <c r="P45">
+        <v>3.33</v>
+      </c>
+      <c r="Q45">
+        <v>2.45</v>
+      </c>
+      <c r="R45">
+        <v>2.25</v>
+      </c>
+      <c r="S45">
+        <v>1.28</v>
+      </c>
+      <c r="T45">
         <v>3.3</v>
       </c>
-      <c r="P45">
-        <v>3.5</v>
-      </c>
-      <c r="Q45">
-        <v>2.44</v>
-      </c>
-      <c r="R45">
-        <v>2.14</v>
-      </c>
-      <c r="S45">
-        <v>1.37</v>
-      </c>
-      <c r="T45">
-        <v>2.85</v>
-      </c>
       <c r="U45">
-        <v>2.73</v>
+        <v>2.41</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z45">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA45">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AB45">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AC45">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="AD45">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE45">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF45">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG45">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK45">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.74</v>
+        <v>2.7</v>
       </c>
       <c r="O46">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>4.46</v>
+        <v>2.45</v>
       </c>
       <c r="Q46">
-        <v>2.3</v>
+        <v>3.22</v>
       </c>
       <c r="R46">
         <v>2.17</v>
       </c>
       <c r="S46">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T46">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W46">
         <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>4.03</v>
+        <v>3.92</v>
       </c>
       <c r="AA46">
         <v>1.72</v>
       </c>
       <c r="AB46">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC46">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AD46">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AG46">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AK46">
-        <v>2.04</v>
+        <v>1.44</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="P47">
-        <v>3.33</v>
+        <v>4.46</v>
       </c>
       <c r="Q47">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R47">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S47">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U47">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>4.5</v>
+        <v>4.03</v>
       </c>
       <c r="AA47">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB47">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AC47">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="AD47">
         <v>1.41</v>
       </c>
       <c r="AE47">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AG47">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="P48">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q48">
-        <v>3.14</v>
+        <v>2.32</v>
       </c>
       <c r="R48">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T48">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="U48">
-        <v>2.91</v>
+        <v>2.69</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W48">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z48">
-        <v>3.05</v>
+        <v>3.44</v>
       </c>
       <c r="AA48">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB48">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC48">
-        <v>3.18</v>
+        <v>2.86</v>
       </c>
       <c r="AD48">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE48">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG48">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK48">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="O49">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q49">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="R49">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T49">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U49">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V49">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W49">
         <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA49">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB49">
         <v>1.9</v>
       </c>
       <c r="AC49">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="AD49">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG49">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
+        <v>2.6</v>
+      </c>
+      <c r="O50">
+        <v>3.4</v>
+      </c>
+      <c r="P50">
         <v>2.7</v>
       </c>
-      <c r="O50">
-        <v>3.6</v>
-      </c>
-      <c r="P50">
-        <v>2.45</v>
-      </c>
       <c r="Q50">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="R50">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="S50">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="U50">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="V50">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X50">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z50">
-        <v>3.92</v>
+        <v>3.05</v>
       </c>
       <c r="AA50">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB50">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AC50">
-        <v>2.64</v>
+        <v>3.18</v>
       </c>
       <c r="AD50">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE50">
         <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AL50">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -615,13 +615,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -641,52 +641,52 @@
         <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q2">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="R2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T2">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="U2">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
         <v>2.92</v>
       </c>
       <c r="AA2">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AB2">
         <v>1.69</v>
       </c>
       <c r="AC2">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
         <v>1.79</v>
@@ -701,41 +701,41 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5"]</t>
         </is>
       </c>
       <c r="AJ2">
+        <v>1.28</v>
+      </c>
+      <c r="AK2">
+        <v>1.42</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>4</v>
+      </c>
+      <c r="AN2">
+        <v>3</v>
+      </c>
+      <c r="AO2">
+        <v>10</v>
+      </c>
+      <c r="AP2">
+        <v>7</v>
+      </c>
+      <c r="AQ2">
         <v>1.27</v>
       </c>
-      <c r="AK2">
-        <v>1.4</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>-1</v>
-      </c>
-      <c r="AN2">
-        <v>-1</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>-1</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O3">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="P3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q3">
         <v>3.68</v>
       </c>
       <c r="R3">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="S3">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="T3">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U3">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="V3">
         <v>1.17</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
         <v>1.17</v>
       </c>
       <c r="Y3">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="Z3">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AA3">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AB3">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AC3">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF3">
-        <v>2.28</v>
+        <v>2.64</v>
       </c>
       <c r="AG3">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.14</v>
+        <v>2.75</v>
       </c>
       <c r="O4">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P4">
-        <v>3.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
-        <v>2.94</v>
+        <v>3.66</v>
       </c>
       <c r="R4">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="S4">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="T4">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="U4">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="W4">
+        <v>1.03</v>
+      </c>
+      <c r="X4">
+        <v>1.13</v>
+      </c>
+      <c r="Y4">
+        <v>1.71</v>
+      </c>
+      <c r="Z4">
+        <v>2.02</v>
+      </c>
+      <c r="AA4">
+        <v>3.08</v>
+      </c>
+      <c r="AB4">
+        <v>1.28</v>
+      </c>
+      <c r="AC4">
+        <v>6.25</v>
+      </c>
+      <c r="AD4">
+        <v>1.06</v>
+      </c>
+      <c r="AE4">
         <v>1.02</v>
       </c>
-      <c r="X4">
-        <v>1.09</v>
-      </c>
-      <c r="Y4">
-        <v>1.56</v>
-      </c>
-      <c r="Z4">
-        <v>2.3</v>
-      </c>
-      <c r="AA4">
-        <v>2.56</v>
-      </c>
-      <c r="AB4">
+      <c r="AF4">
+        <v>2.2</v>
+      </c>
+      <c r="AG4">
+        <v>1.48</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.4</v>
       </c>
-      <c r="AC4">
-        <v>4.9</v>
-      </c>
-      <c r="AD4">
-        <v>1.11</v>
-      </c>
-      <c r="AE4">
-        <v>1.01</v>
-      </c>
-      <c r="AF4">
-        <v>2.15</v>
-      </c>
-      <c r="AG4">
-        <v>1.6</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.35</v>
-      </c>
       <c r="AK4">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1104,13 +1104,13 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -1120,68 +1120,68 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O5">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q5">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="S5">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="T5">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="U5">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="V5">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="Z5">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="AA5">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="AB5">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AC5">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD5">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE5">
         <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG5">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1190,41 +1190,41 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK5">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O6">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O7">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="P7">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="Q7">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R7">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S7">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="T7">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="U7">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="V7">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="Z7">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AA7">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AB7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD7">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
         <v>2</v>
       </c>
       <c r="AG7">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK7">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,61 +1616,61 @@
         <v>1.95</v>
       </c>
       <c r="O8">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P8">
+        <v>3.9</v>
+      </c>
+      <c r="Q8">
+        <v>2.86</v>
+      </c>
+      <c r="R8">
+        <v>1.77</v>
+      </c>
+      <c r="S8">
+        <v>1.64</v>
+      </c>
+      <c r="T8">
+        <v>2.11</v>
+      </c>
+      <c r="U8">
         <v>4.2</v>
       </c>
-      <c r="Q8">
-        <v>2.7</v>
-      </c>
-      <c r="R8">
-        <v>1.85</v>
-      </c>
-      <c r="S8">
-        <v>1.57</v>
-      </c>
-      <c r="T8">
-        <v>2.2</v>
-      </c>
-      <c r="U8">
-        <v>3.75</v>
-      </c>
       <c r="V8">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y8">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Z8">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AA8">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AB8">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AG8">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q9">
-        <v>6.25</v>
+        <v>8.6</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S9">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T9">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="U9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z9">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AA9">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AB9">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AC9">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD9">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AG9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="O11">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P11">
-        <v>3.65</v>
+        <v>3.07</v>
       </c>
       <c r="Q11">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="R11">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="S11">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="T11">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="U11">
-        <v>3.34</v>
+        <v>3.92</v>
       </c>
       <c r="V11">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="W11">
+        <v>1.01</v>
+      </c>
+      <c r="X11">
+        <v>1.11</v>
+      </c>
+      <c r="Y11">
+        <v>1.68</v>
+      </c>
+      <c r="Z11">
+        <v>2.16</v>
+      </c>
+      <c r="AA11">
+        <v>2.81</v>
+      </c>
+      <c r="AB11">
+        <v>1.33</v>
+      </c>
+      <c r="AC11">
+        <v>5.55</v>
+      </c>
+      <c r="AD11">
+        <v>1.08</v>
+      </c>
+      <c r="AE11">
         <v>1.03</v>
       </c>
-      <c r="X11">
-        <v>1.1</v>
-      </c>
-      <c r="Y11">
-        <v>1.47</v>
-      </c>
-      <c r="Z11">
-        <v>2.64</v>
-      </c>
-      <c r="AA11">
-        <v>2.48</v>
-      </c>
-      <c r="AB11">
+      <c r="AF11">
+        <v>2.3</v>
+      </c>
+      <c r="AG11">
+        <v>1.54</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.36</v>
+      </c>
+      <c r="AK11">
         <v>1.52</v>
-      </c>
-      <c r="AC11">
-        <v>4.66</v>
-      </c>
-      <c r="AD11">
-        <v>1.18</v>
-      </c>
-      <c r="AE11">
-        <v>1.02</v>
-      </c>
-      <c r="AF11">
-        <v>2.05</v>
-      </c>
-      <c r="AG11">
-        <v>1.7</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.32</v>
-      </c>
-      <c r="AK11">
-        <v>1.58</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P13">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="Q13">
-        <v>5.62</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="T13">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="U13">
-        <v>2.26</v>
+        <v>3.08</v>
       </c>
       <c r="V13">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="W13">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="Z13">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA13">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="AB13">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>2.38</v>
+        <v>3.84</v>
       </c>
       <c r="AD13">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AE13">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK13">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.2</v>
+        <v>5.25</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q14">
-        <v>2.8</v>
+        <v>5.52</v>
       </c>
       <c r="R14">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="S14">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U14">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="V14">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="Z14">
-        <v>3.35</v>
+        <v>4.75</v>
       </c>
       <c r="AA14">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AB14">
-        <v>1.76</v>
+        <v>2.34</v>
       </c>
       <c r="AC14">
-        <v>3.5</v>
+        <v>2.28</v>
       </c>
       <c r="AD14">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AE14">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG14">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK14">
-        <v>1.55</v>
+        <v>1.08</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>2.87</v>
       </c>
       <c r="O15">
         <v>3.25</v>
       </c>
       <c r="P15">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
+        <v>2.73</v>
+      </c>
+      <c r="U15">
+        <v>2.79</v>
+      </c>
+      <c r="V15">
+        <v>1.35</v>
+      </c>
+      <c r="W15">
+        <v>1.06</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>1.25</v>
+      </c>
+      <c r="Z15">
+        <v>3.28</v>
+      </c>
+      <c r="AA15">
+        <v>2</v>
+      </c>
+      <c r="AB15">
+        <v>1.8</v>
+      </c>
+      <c r="AC15">
         <v>3.2</v>
       </c>
-      <c r="U15">
-        <v>2.55</v>
-      </c>
-      <c r="V15">
-        <v>1.45</v>
-      </c>
-      <c r="W15">
-        <v>1.08</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
-        <v>1.2</v>
-      </c>
-      <c r="Z15">
-        <v>3.9</v>
-      </c>
-      <c r="AA15">
-        <v>1.72</v>
-      </c>
-      <c r="AB15">
-        <v>2.07</v>
-      </c>
-      <c r="AC15">
-        <v>2.7</v>
-      </c>
       <c r="AD15">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="O22">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P22">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="R22">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S22">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U22">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="V22">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W22">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -3931,28 +3931,28 @@
         <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA22">
+        <v>1.4</v>
+      </c>
+      <c r="AB22">
+        <v>2.75</v>
+      </c>
+      <c r="AC22">
+        <v>2</v>
+      </c>
+      <c r="AD22">
+        <v>1.73</v>
+      </c>
+      <c r="AE22">
+        <v>1.32</v>
+      </c>
+      <c r="AF22">
         <v>1.43</v>
       </c>
-      <c r="AB22">
-        <v>2.46</v>
-      </c>
-      <c r="AC22">
-        <v>2.12</v>
-      </c>
-      <c r="AD22">
-        <v>1.64</v>
-      </c>
-      <c r="AE22">
-        <v>1.24</v>
-      </c>
-      <c r="AF22">
-        <v>1.4</v>
-      </c>
       <c r="AG22">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK22">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,34 +4058,34 @@
         </is>
       </c>
       <c r="N23">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="O23">
+        <v>3.75</v>
+      </c>
+      <c r="P23">
+        <v>2.28</v>
+      </c>
+      <c r="Q23">
+        <v>3</v>
+      </c>
+      <c r="R23">
+        <v>2.55</v>
+      </c>
+      <c r="S23">
+        <v>1.22</v>
+      </c>
+      <c r="T23">
         <v>3.9</v>
       </c>
-      <c r="P23">
-        <v>1.6</v>
-      </c>
-      <c r="Q23">
-        <v>4.4</v>
-      </c>
-      <c r="R23">
-        <v>2.6</v>
-      </c>
-      <c r="S23">
-        <v>1.2</v>
-      </c>
-      <c r="T23">
-        <v>4.1</v>
-      </c>
       <c r="U23">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="V23">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W23">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4094,28 +4094,28 @@
         <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA23">
+        <v>1.43</v>
+      </c>
+      <c r="AB23">
+        <v>2.46</v>
+      </c>
+      <c r="AC23">
+        <v>2.12</v>
+      </c>
+      <c r="AD23">
+        <v>1.64</v>
+      </c>
+      <c r="AE23">
+        <v>1.24</v>
+      </c>
+      <c r="AF23">
         <v>1.4</v>
       </c>
-      <c r="AB23">
-        <v>2.75</v>
-      </c>
-      <c r="AC23">
-        <v>2</v>
-      </c>
-      <c r="AD23">
-        <v>1.73</v>
-      </c>
-      <c r="AE23">
-        <v>1.32</v>
-      </c>
-      <c r="AF23">
-        <v>1.43</v>
-      </c>
       <c r="AG23">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="O27">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q27">
-        <v>2.12</v>
+        <v>2.73</v>
       </c>
       <c r="R27">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S27">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U27">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AA27">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB27">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC27">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD27">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>2.28</v>
+        <v>1.64</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q28">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="R28">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U28">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28">
+        <v>1.3</v>
+      </c>
+      <c r="Z28">
+        <v>3.08</v>
+      </c>
+      <c r="AA28">
+        <v>1.95</v>
+      </c>
+      <c r="AB28">
+        <v>1.78</v>
+      </c>
+      <c r="AC28">
+        <v>3.34</v>
+      </c>
+      <c r="AD28">
         <v>1.24</v>
       </c>
-      <c r="Z28">
-        <v>3.58</v>
-      </c>
-      <c r="AA28">
-        <v>1.88</v>
-      </c>
-      <c r="AB28">
-        <v>1.87</v>
-      </c>
-      <c r="AC28">
-        <v>3.08</v>
-      </c>
-      <c r="AD28">
-        <v>1.28</v>
-      </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="Q29">
-        <v>4.34</v>
+        <v>2.8</v>
       </c>
       <c r="R29">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T29">
-        <v>3.24</v>
+        <v>2.77</v>
       </c>
       <c r="U29">
-        <v>2.65</v>
+        <v>2.93</v>
       </c>
       <c r="V29">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="AA29">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AB29">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC29">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AD29">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AG29">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK29">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,61 +5199,61 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>4.33</v>
+        <v>3.15</v>
       </c>
       <c r="P30">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q30">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="R30">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="T30">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="U30">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z30">
-        <v>4.32</v>
+        <v>3.14</v>
       </c>
       <c r="AA30">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB30">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC30">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG30">
         <v>1.94</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>2.43</v>
+        <v>1.52</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
+        <v>1.68</v>
+      </c>
+      <c r="O31">
         <v>3.6</v>
       </c>
-      <c r="O31">
-        <v>3.3</v>
-      </c>
       <c r="P31">
-        <v>2.05</v>
+        <v>4.41</v>
       </c>
       <c r="Q31">
-        <v>4.13</v>
+        <v>2.27</v>
       </c>
       <c r="R31">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T31">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="U31">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA31">
+        <v>1.85</v>
+      </c>
+      <c r="AB31">
         <v>1.95</v>
       </c>
-      <c r="AB31">
-        <v>1.85</v>
-      </c>
       <c r="AC31">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="AD31">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG31">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK31">
-        <v>1.19</v>
+        <v>2.02</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
+        <v>1.83</v>
+      </c>
+      <c r="O32">
+        <v>3.7</v>
+      </c>
+      <c r="P32">
+        <v>4.2</v>
+      </c>
+      <c r="Q32">
+        <v>2.33</v>
+      </c>
+      <c r="R32">
+        <v>2.18</v>
+      </c>
+      <c r="S32">
+        <v>1.33</v>
+      </c>
+      <c r="T32">
+        <v>3.14</v>
+      </c>
+      <c r="U32">
         <v>2.75</v>
       </c>
-      <c r="O32">
-        <v>3.4</v>
-      </c>
-      <c r="P32">
-        <v>2.5</v>
-      </c>
-      <c r="Q32">
-        <v>3.02</v>
-      </c>
-      <c r="R32">
-        <v>2.09</v>
-      </c>
-      <c r="S32">
-        <v>1.37</v>
-      </c>
-      <c r="T32">
-        <v>2.81</v>
-      </c>
-      <c r="U32">
-        <v>2.84</v>
-      </c>
       <c r="V32">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.08</v>
+        <v>3.72</v>
       </c>
       <c r="AA32">
+        <v>1.83</v>
+      </c>
+      <c r="AB32">
         <v>1.95</v>
       </c>
-      <c r="AB32">
-        <v>1.78</v>
-      </c>
       <c r="AC32">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AD32">
+        <v>1.35</v>
+      </c>
+      <c r="AE32">
+        <v>1.13</v>
+      </c>
+      <c r="AF32">
+        <v>1.73</v>
+      </c>
+      <c r="AG32">
+        <v>2</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.24</v>
       </c>
-      <c r="AE32">
-        <v>1.05</v>
-      </c>
-      <c r="AF32">
-        <v>1.75</v>
-      </c>
-      <c r="AG32">
-        <v>1.97</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.28</v>
-      </c>
       <c r="AK32">
-        <v>1.43</v>
+        <v>1.94</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.83</v>
+        <v>3.7</v>
       </c>
       <c r="O33">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>4.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q33">
-        <v>2.33</v>
+        <v>4.34</v>
       </c>
       <c r="R33">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S33">
         <v>1.33</v>
       </c>
       <c r="T33">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="U33">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V33">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z33">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="AA33">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB33">
         <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AD33">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE33">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.94</v>
+        <v>1.18</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,58 +5851,58 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>4.13</v>
       </c>
       <c r="R34">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="S34">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="U34">
-        <v>2.93</v>
+        <v>2.69</v>
       </c>
       <c r="V34">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="AA34">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB34">
         <v>1.85</v>
       </c>
       <c r="AC34">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="AD34">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
         <v>1.72</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK34">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,61 +6014,61 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="O35">
-        <v>3.15</v>
+        <v>4.33</v>
       </c>
       <c r="P35">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q35">
-        <v>2.8</v>
+        <v>2.01</v>
       </c>
       <c r="R35">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="S35">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.9</v>
+        <v>2.52</v>
       </c>
       <c r="V35">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z35">
-        <v>3.14</v>
+        <v>4.32</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB35">
+        <v>2.15</v>
+      </c>
+      <c r="AC35">
+        <v>2.65</v>
+      </c>
+      <c r="AD35">
+        <v>1.4</v>
+      </c>
+      <c r="AE35">
+        <v>1.13</v>
+      </c>
+      <c r="AF35">
         <v>1.8</v>
-      </c>
-      <c r="AC35">
-        <v>3.4</v>
-      </c>
-      <c r="AD35">
-        <v>1.22</v>
-      </c>
-      <c r="AE35">
-        <v>1.04</v>
-      </c>
-      <c r="AF35">
-        <v>1.77</v>
       </c>
       <c r="AG35">
         <v>1.94</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK35">
-        <v>1.52</v>
+        <v>2.43</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P36">
-        <v>4.41</v>
+        <v>5.75</v>
       </c>
       <c r="Q36">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="R36">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S36">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="U36">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="V36">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
+        <v>1.27</v>
+      </c>
+      <c r="Z36">
+        <v>3.14</v>
+      </c>
+      <c r="AA36">
+        <v>1.89</v>
+      </c>
+      <c r="AB36">
+        <v>1.85</v>
+      </c>
+      <c r="AC36">
+        <v>3.4</v>
+      </c>
+      <c r="AD36">
+        <v>1.29</v>
+      </c>
+      <c r="AE36">
+        <v>1.06</v>
+      </c>
+      <c r="AF36">
+        <v>1.95</v>
+      </c>
+      <c r="AG36">
+        <v>1.75</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.22</v>
       </c>
-      <c r="Z36">
-        <v>3.5</v>
-      </c>
-      <c r="AA36">
-        <v>1.85</v>
-      </c>
-      <c r="AB36">
-        <v>1.95</v>
-      </c>
-      <c r="AC36">
-        <v>2.95</v>
-      </c>
-      <c r="AD36">
-        <v>1.32</v>
-      </c>
-      <c r="AE36">
-        <v>1.08</v>
-      </c>
-      <c r="AF36">
-        <v>1.8</v>
-      </c>
-      <c r="AG36">
-        <v>2</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.23</v>
-      </c>
       <c r="AK36">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
+        <v>1.93</v>
+      </c>
+      <c r="O41">
+        <v>3.5</v>
+      </c>
+      <c r="P41">
+        <v>4.03</v>
+      </c>
+      <c r="Q41">
+        <v>2.4</v>
+      </c>
+      <c r="R41">
+        <v>2.13</v>
+      </c>
+      <c r="S41">
+        <v>1.3</v>
+      </c>
+      <c r="T41">
+        <v>3.2</v>
+      </c>
+      <c r="U41">
+        <v>2.65</v>
+      </c>
+      <c r="V41">
+        <v>1.42</v>
+      </c>
+      <c r="W41">
+        <v>1.08</v>
+      </c>
+      <c r="X41">
+        <v>1.03</v>
+      </c>
+      <c r="Y41">
+        <v>1.23</v>
+      </c>
+      <c r="Z41">
+        <v>3.55</v>
+      </c>
+      <c r="AA41">
+        <v>1.9</v>
+      </c>
+      <c r="AB41">
+        <v>1.9</v>
+      </c>
+      <c r="AC41">
+        <v>3.1</v>
+      </c>
+      <c r="AD41">
+        <v>1.33</v>
+      </c>
+      <c r="AE41">
+        <v>1.07</v>
+      </c>
+      <c r="AF41">
+        <v>1.67</v>
+      </c>
+      <c r="AG41">
         <v>2</v>
       </c>
-      <c r="O41">
-        <v>3.4</v>
-      </c>
-      <c r="P41">
-        <v>3.7</v>
-      </c>
-      <c r="Q41">
-        <v>2.69</v>
-      </c>
-      <c r="R41">
-        <v>2.1</v>
-      </c>
-      <c r="S41">
-        <v>1.4</v>
-      </c>
-      <c r="T41">
-        <v>2.69</v>
-      </c>
-      <c r="U41">
-        <v>2.89</v>
-      </c>
-      <c r="V41">
-        <v>1.33</v>
-      </c>
-      <c r="W41">
-        <v>1.04</v>
-      </c>
-      <c r="X41">
-        <v>1.06</v>
-      </c>
-      <c r="Y41">
-        <v>1.3</v>
-      </c>
-      <c r="Z41">
-        <v>3.4</v>
-      </c>
-      <c r="AA41">
-        <v>2</v>
-      </c>
-      <c r="AB41">
-        <v>1.8</v>
-      </c>
-      <c r="AC41">
-        <v>3.3</v>
-      </c>
-      <c r="AD41">
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.25</v>
       </c>
-      <c r="AE41">
-        <v>1.09</v>
-      </c>
-      <c r="AF41">
-        <v>1.8</v>
-      </c>
-      <c r="AG41">
-        <v>1.93</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.3</v>
-      </c>
       <c r="AK41">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.57</v>
+        <v>2.03</v>
       </c>
       <c r="O42">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P42">
+        <v>3.3</v>
+      </c>
+      <c r="Q42">
         <v>2.5</v>
       </c>
-      <c r="Q42">
-        <v>3.2</v>
-      </c>
       <c r="R42">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="S42">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U42">
         <v>2.59</v>
       </c>
       <c r="V42">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
         <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA42">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AB42">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="AC42">
-        <v>3.21</v>
+        <v>2.82</v>
       </c>
       <c r="AD42">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.93</v>
+        <v>2.57</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
-        <v>4.03</v>
+        <v>2.5</v>
       </c>
       <c r="Q43">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="R43">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U43">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="V43">
         <v>1.42</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z43">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AA43">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB43">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC43">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="AD43">
+        <v>1.36</v>
+      </c>
+      <c r="AE43">
+        <v>1.14</v>
+      </c>
+      <c r="AF43">
+        <v>1.66</v>
+      </c>
+      <c r="AG43">
+        <v>2.06</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.33</v>
       </c>
-      <c r="AE43">
-        <v>1.07</v>
-      </c>
-      <c r="AF43">
-        <v>1.67</v>
-      </c>
-      <c r="AG43">
-        <v>2</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.25</v>
-      </c>
       <c r="AK43">
-        <v>1.86</v>
+        <v>1.46</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O44">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
+        <v>3.7</v>
+      </c>
+      <c r="Q44">
+        <v>2.69</v>
+      </c>
+      <c r="R44">
+        <v>2.1</v>
+      </c>
+      <c r="S44">
+        <v>1.4</v>
+      </c>
+      <c r="T44">
+        <v>2.69</v>
+      </c>
+      <c r="U44">
+        <v>2.89</v>
+      </c>
+      <c r="V44">
+        <v>1.33</v>
+      </c>
+      <c r="W44">
+        <v>1.04</v>
+      </c>
+      <c r="X44">
+        <v>1.06</v>
+      </c>
+      <c r="Y44">
+        <v>1.3</v>
+      </c>
+      <c r="Z44">
+        <v>3.4</v>
+      </c>
+      <c r="AA44">
+        <v>2</v>
+      </c>
+      <c r="AB44">
+        <v>1.8</v>
+      </c>
+      <c r="AC44">
         <v>3.3</v>
       </c>
-      <c r="Q44">
-        <v>2.5</v>
-      </c>
-      <c r="R44">
-        <v>2.16</v>
-      </c>
-      <c r="S44">
-        <v>1.32</v>
-      </c>
-      <c r="T44">
-        <v>2.86</v>
-      </c>
-      <c r="U44">
-        <v>2.59</v>
-      </c>
-      <c r="V44">
-        <v>1.5</v>
-      </c>
-      <c r="W44">
-        <v>1.07</v>
-      </c>
-      <c r="X44">
-        <v>1.04</v>
-      </c>
-      <c r="Y44">
-        <v>1.18</v>
-      </c>
-      <c r="Z44">
-        <v>4.33</v>
-      </c>
-      <c r="AA44">
-        <v>1.67</v>
-      </c>
-      <c r="AB44">
-        <v>2.14</v>
-      </c>
-      <c r="AC44">
-        <v>2.82</v>
-      </c>
       <c r="AD44">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AF44">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O45">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="Q45">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R45">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S45">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="T45">
+        <v>2.85</v>
+      </c>
+      <c r="U45">
+        <v>2.73</v>
+      </c>
+      <c r="V45">
+        <v>1.4</v>
+      </c>
+      <c r="W45">
+        <v>1.06</v>
+      </c>
+      <c r="X45">
+        <v>1.04</v>
+      </c>
+      <c r="Y45">
+        <v>1.25</v>
+      </c>
+      <c r="Z45">
         <v>3.3</v>
       </c>
-      <c r="U45">
-        <v>2.41</v>
-      </c>
-      <c r="V45">
-        <v>1.5</v>
-      </c>
-      <c r="W45">
+      <c r="AA45">
+        <v>1.9</v>
+      </c>
+      <c r="AB45">
+        <v>1.9</v>
+      </c>
+      <c r="AC45">
+        <v>3.3</v>
+      </c>
+      <c r="AD45">
+        <v>1.34</v>
+      </c>
+      <c r="AE45">
         <v>1.08</v>
       </c>
-      <c r="X45">
-        <v>1.01</v>
-      </c>
-      <c r="Y45">
-        <v>1.2</v>
-      </c>
-      <c r="Z45">
-        <v>4.5</v>
-      </c>
-      <c r="AA45">
-        <v>1.66</v>
-      </c>
-      <c r="AB45">
-        <v>2.18</v>
-      </c>
-      <c r="AC45">
-        <v>2.54</v>
-      </c>
-      <c r="AD45">
-        <v>1.41</v>
-      </c>
-      <c r="AE45">
-        <v>1.14</v>
-      </c>
       <c r="AF45">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK45">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
+        <v>2.5</v>
+      </c>
+      <c r="O46">
+        <v>3.4</v>
+      </c>
+      <c r="P46">
         <v>2.7</v>
       </c>
-      <c r="O46">
-        <v>3.6</v>
-      </c>
-      <c r="P46">
-        <v>2.45</v>
-      </c>
       <c r="Q46">
-        <v>3.22</v>
+        <v>2.89</v>
       </c>
       <c r="R46">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="S46">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="V46">
+        <v>1.42</v>
+      </c>
+      <c r="W46">
+        <v>1.06</v>
+      </c>
+      <c r="X46">
+        <v>1.04</v>
+      </c>
+      <c r="Y46">
+        <v>1.28</v>
+      </c>
+      <c r="Z46">
+        <v>3.7</v>
+      </c>
+      <c r="AA46">
+        <v>1.9</v>
+      </c>
+      <c r="AB46">
+        <v>1.9</v>
+      </c>
+      <c r="AC46">
+        <v>3.05</v>
+      </c>
+      <c r="AD46">
+        <v>1.35</v>
+      </c>
+      <c r="AE46">
+        <v>1.08</v>
+      </c>
+      <c r="AF46">
+        <v>1.68</v>
+      </c>
+      <c r="AG46">
+        <v>2.06</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>1.3</v>
+      </c>
+      <c r="AK46">
         <v>1.47</v>
-      </c>
-      <c r="W46">
-        <v>1.07</v>
-      </c>
-      <c r="X46">
-        <v>1.05</v>
-      </c>
-      <c r="Y46">
-        <v>1.22</v>
-      </c>
-      <c r="Z46">
-        <v>3.92</v>
-      </c>
-      <c r="AA46">
-        <v>1.72</v>
-      </c>
-      <c r="AB46">
-        <v>2.08</v>
-      </c>
-      <c r="AC46">
-        <v>2.64</v>
-      </c>
-      <c r="AD46">
-        <v>1.44</v>
-      </c>
-      <c r="AE46">
-        <v>1.11</v>
-      </c>
-      <c r="AF46">
-        <v>1.56</v>
-      </c>
-      <c r="AG46">
-        <v>2.3</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.39</v>
-      </c>
-      <c r="AK46">
-        <v>1.44</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.74</v>
+        <v>2.7</v>
       </c>
       <c r="O47">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
-        <v>4.46</v>
+        <v>2.45</v>
       </c>
       <c r="Q47">
-        <v>2.3</v>
+        <v>3.22</v>
       </c>
       <c r="R47">
         <v>2.17</v>
       </c>
       <c r="S47">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T47">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V47">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W47">
         <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>4.03</v>
+        <v>3.92</v>
       </c>
       <c r="AA47">
         <v>1.72</v>
       </c>
       <c r="AB47">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC47">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AD47">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AG47">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AK47">
-        <v>2.04</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="O48">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
-        <v>4.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q48">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="R48">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S48">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T48">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>2.69</v>
+        <v>2.41</v>
       </c>
       <c r="V48">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>3.44</v>
+        <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AB48">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AC48">
-        <v>2.86</v>
+        <v>2.54</v>
       </c>
       <c r="AD48">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE48">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF48">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AG48">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK48">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,34 +8296,34 @@
         </is>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="P49">
-        <v>3.5</v>
+        <v>4.46</v>
       </c>
       <c r="Q49">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="R49">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="S49">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T49">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="U49">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="V49">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
         <v>1.04</v>
@@ -8332,28 +8332,28 @@
         <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>3.3</v>
+        <v>4.03</v>
       </c>
       <c r="AA49">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB49">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AC49">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="AD49">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="P51">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q51">
-        <v>2.89</v>
+        <v>2.32</v>
       </c>
       <c r="R51">
         <v>2.12</v>
       </c>
       <c r="S51">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="U51">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="V51">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W51">
         <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z51">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AA51">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB51">
         <v>1.9</v>
       </c>
       <c r="AC51">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG51">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.47</v>
+        <v>2.02</v>
       </c>
       <c r="AL51">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -953,11 +953,11 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1276,14 +1276,14 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1593,13 +1593,13 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "45+5"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1935,68 +1935,68 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
+        <v>2.45</v>
+      </c>
+      <c r="R10">
+        <v>2</v>
+      </c>
+      <c r="S10">
+        <v>1.5</v>
+      </c>
+      <c r="T10">
         <v>2.48</v>
       </c>
-      <c r="R10">
-        <v>1.96</v>
-      </c>
-      <c r="S10">
-        <v>1.48</v>
-      </c>
-      <c r="T10">
-        <v>2.55</v>
-      </c>
       <c r="U10">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="V10">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y10">
         <v>1.4</v>
       </c>
       <c r="Z10">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="AA10">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AB10">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC10">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="AD10">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG10">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,37 +2009,37 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2254,14 +2254,14 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2271,101 +2271,101 @@
         <v>3.4</v>
       </c>
       <c r="P12">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="Q12">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U12">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z12">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="AA12">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AB12">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AC12">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AD12">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AG12">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["77"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2417,14 +2417,14 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66", "72"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2571,13 +2571,13 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "21"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "38"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.6</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="P16">
-        <v>2.71</v>
+        <v>1.33</v>
       </c>
       <c r="Q16">
-        <v>3.7</v>
+        <v>8.75</v>
       </c>
       <c r="R16">
-        <v>1.83</v>
+        <v>2.22</v>
       </c>
       <c r="S16">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>2.13</v>
+        <v>2.84</v>
       </c>
       <c r="U16">
-        <v>3.88</v>
+        <v>2.78</v>
       </c>
       <c r="V16">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="Z16">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="AA16">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="AB16">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AC16">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AG16">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.4</v>
+        <v>2.94</v>
       </c>
       <c r="AK16">
-        <v>1.4</v>
+        <v>1.03</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="O17">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="P17">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q17">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="R17">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="T17">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="U17">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="W17">
         <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="Z17">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AA17">
-        <v>2.09</v>
+        <v>2.43</v>
       </c>
       <c r="AB17">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AC17">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AD17">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AE17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AG17">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>2.84</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="O19">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="P19">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="Q19">
+        <v>5.42</v>
+      </c>
+      <c r="R19">
+        <v>2.62</v>
+      </c>
+      <c r="S19">
+        <v>1.19</v>
+      </c>
+      <c r="T19">
         <v>4</v>
       </c>
-      <c r="R19">
-        <v>2.33</v>
-      </c>
-      <c r="S19">
-        <v>1.25</v>
-      </c>
-      <c r="T19">
-        <v>3.5</v>
-      </c>
       <c r="U19">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="V19">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>5.33</v>
+        <v>5.75</v>
       </c>
       <c r="AA19">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AB19">
-        <v>2.52</v>
+        <v>2.87</v>
       </c>
       <c r="AC19">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AD19">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AE19">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AF19">
         <v>1.51</v>
       </c>
       <c r="AG19">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>2.04</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P20">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q20">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R20">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S20">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="T20">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="U20">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="V20">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="W20">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z20">
-        <v>5.58</v>
+        <v>6.45</v>
       </c>
       <c r="AA20">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AC20">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AD20">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="AE20">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF20">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AG20">
-        <v>2.73</v>
+        <v>3.16</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="O21">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P21">
-        <v>4.8</v>
+        <v>4.41</v>
       </c>
       <c r="Q21">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="R21">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="S21">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="U21">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="V21">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA21">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AB21">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AC21">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AD21">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AE21">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AG21">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O22">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P22">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Q22">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="R22">
         <v>2.6</v>
       </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T22">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="U22">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="V22">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="W22">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -3931,28 +3931,28 @@
         <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA22">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB22">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC22">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AD22">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AE22">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AF22">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AG22">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
+        <v>1.18</v>
+      </c>
+      <c r="AK22">
         <v>1.16</v>
-      </c>
-      <c r="AK22">
-        <v>1.14</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O23">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R23">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>3.9</v>
+        <v>3.18</v>
       </c>
       <c r="U23">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="V23">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z23">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="AA23">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AB23">
-        <v>2.46</v>
+        <v>2.19</v>
       </c>
       <c r="AC23">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="AD23">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AE23">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AF23">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG23">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="O24">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="P24">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q24">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="R24">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="S24">
         <v>1.21</v>
@@ -4242,43 +4242,43 @@
         <v>3.58</v>
       </c>
       <c r="U24">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V24">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W24">
         <v>1.12</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
         <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AA24">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB24">
         <v>2.4</v>
       </c>
       <c r="AC24">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD24">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE24">
         <v>1.19</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK24">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O25">
         <v>4.5</v>
       </c>
       <c r="P25">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q25">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="R25">
-        <v>2.57</v>
+        <v>2.72</v>
       </c>
       <c r="S25">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T25">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="U25">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V25">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="W25">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z25">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA25">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB25">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC25">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AD25">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AE25">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AF25">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG25">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK25">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>7.78</v>
       </c>
       <c r="Q26">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="R26">
+        <v>2.7</v>
+      </c>
+      <c r="S26">
+        <v>1.28</v>
+      </c>
+      <c r="T26">
+        <v>3.15</v>
+      </c>
+      <c r="U26">
         <v>2.31</v>
       </c>
-      <c r="S26">
-        <v>1.34</v>
-      </c>
-      <c r="T26">
-        <v>2.88</v>
-      </c>
-      <c r="U26">
-        <v>2.56</v>
-      </c>
       <c r="V26">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA26">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB26">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AC26">
-        <v>2.74</v>
+        <v>2.43</v>
       </c>
       <c r="AD26">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF26">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AG26">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AK26">
-        <v>2.94</v>
+        <v>4.05</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,22 +4710,22 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q27">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="R27">
         <v>2.13</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
         <v>2.9</v>
@@ -4746,10 +4746,10 @@
         <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AA27">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AB27">
         <v>1.87</v>
@@ -4767,7 +4767,7 @@
         <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="O28">
         <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="Q28">
-        <v>3.02</v>
+        <v>3.9</v>
       </c>
       <c r="R28">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="U28">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
         <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
+        <v>1.24</v>
+      </c>
+      <c r="Z28">
+        <v>3.34</v>
+      </c>
+      <c r="AA28">
+        <v>1.88</v>
+      </c>
+      <c r="AB28">
+        <v>1.87</v>
+      </c>
+      <c r="AC28">
+        <v>3.08</v>
+      </c>
+      <c r="AD28">
+        <v>1.28</v>
+      </c>
+      <c r="AE28">
+        <v>1.07</v>
+      </c>
+      <c r="AF28">
+        <v>1.71</v>
+      </c>
+      <c r="AG28">
+        <v>2.02</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.27</v>
+      </c>
+      <c r="AK28">
         <v>1.3</v>
-      </c>
-      <c r="Z28">
-        <v>3.08</v>
-      </c>
-      <c r="AA28">
-        <v>1.95</v>
-      </c>
-      <c r="AB28">
-        <v>1.78</v>
-      </c>
-      <c r="AC28">
-        <v>3.34</v>
-      </c>
-      <c r="AD28">
-        <v>1.24</v>
-      </c>
-      <c r="AE28">
-        <v>1.05</v>
-      </c>
-      <c r="AF28">
-        <v>1.75</v>
-      </c>
-      <c r="AG28">
-        <v>1.97</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.28</v>
-      </c>
-      <c r="AK28">
-        <v>1.43</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,31 +5036,31 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O29">
         <v>3.4</v>
       </c>
       <c r="P29">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q29">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="R29">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
+        <v>1.37</v>
+      </c>
+      <c r="T29">
+        <v>2.81</v>
+      </c>
+      <c r="U29">
+        <v>2.77</v>
+      </c>
+      <c r="V29">
         <v>1.38</v>
-      </c>
-      <c r="T29">
-        <v>2.77</v>
-      </c>
-      <c r="U29">
-        <v>2.93</v>
-      </c>
-      <c r="V29">
-        <v>1.39</v>
       </c>
       <c r="W29">
         <v>1.05</v>
@@ -5069,19 +5069,19 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z29">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="AA29">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB29">
         <v>1.85</v>
       </c>
       <c r="AC29">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD29">
         <v>1.26</v>
@@ -5090,7 +5090,7 @@
         <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG29">
         <v>2.01</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="Q30">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S30">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>2.59</v>
+        <v>3.16</v>
       </c>
       <c r="U30">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="V30">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z30">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="AA30">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB30">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC30">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AD30">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE30">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AG30">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O31">
+        <v>4</v>
+      </c>
+      <c r="P31">
+        <v>4.6</v>
+      </c>
+      <c r="Q31">
+        <v>2.07</v>
+      </c>
+      <c r="R31">
+        <v>2.36</v>
+      </c>
+      <c r="S31">
+        <v>1.28</v>
+      </c>
+      <c r="T31">
         <v>3.6</v>
       </c>
-      <c r="P31">
-        <v>4.41</v>
-      </c>
-      <c r="Q31">
-        <v>2.27</v>
-      </c>
-      <c r="R31">
-        <v>2.25</v>
-      </c>
-      <c r="S31">
-        <v>1.32</v>
-      </c>
-      <c r="T31">
-        <v>3.05</v>
-      </c>
       <c r="U31">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="V31">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>3.5</v>
+        <v>4.64</v>
       </c>
       <c r="AA31">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AB31">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="AC31">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF31">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK31">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
+        <v>1.91</v>
+      </c>
+      <c r="Q32">
         <v>4.2</v>
       </c>
-      <c r="Q32">
-        <v>2.33</v>
-      </c>
       <c r="R32">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
         <v>1.33</v>
       </c>
       <c r="T32">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U32">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="V32">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z32">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AA32">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB32">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC32">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AD32">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK32">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,65 +5688,65 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
+        <v>2.93</v>
+      </c>
+      <c r="Q33">
+        <v>2.82</v>
+      </c>
+      <c r="R33">
+        <v>2.05</v>
+      </c>
+      <c r="S33">
+        <v>1.38</v>
+      </c>
+      <c r="T33">
+        <v>2.77</v>
+      </c>
+      <c r="U33">
+        <v>2.95</v>
+      </c>
+      <c r="V33">
+        <v>1.34</v>
+      </c>
+      <c r="W33">
+        <v>1.02</v>
+      </c>
+      <c r="X33">
+        <v>1.04</v>
+      </c>
+      <c r="Y33">
+        <v>1.34</v>
+      </c>
+      <c r="Z33">
+        <v>3.24</v>
+      </c>
+      <c r="AA33">
+        <v>2.04</v>
+      </c>
+      <c r="AB33">
+        <v>1.72</v>
+      </c>
+      <c r="AC33">
+        <v>3.5</v>
+      </c>
+      <c r="AD33">
+        <v>1.22</v>
+      </c>
+      <c r="AE33">
+        <v>1.03</v>
+      </c>
+      <c r="AF33">
+        <v>1.79</v>
+      </c>
+      <c r="AG33">
         <v>1.92</v>
       </c>
-      <c r="Q33">
-        <v>4.34</v>
-      </c>
-      <c r="R33">
-        <v>2.16</v>
-      </c>
-      <c r="S33">
-        <v>1.33</v>
-      </c>
-      <c r="T33">
-        <v>3.24</v>
-      </c>
-      <c r="U33">
-        <v>2.65</v>
-      </c>
-      <c r="V33">
-        <v>1.47</v>
-      </c>
-      <c r="W33">
-        <v>1.06</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.21</v>
-      </c>
-      <c r="Z33">
-        <v>3.65</v>
-      </c>
-      <c r="AA33">
-        <v>1.79</v>
-      </c>
-      <c r="AB33">
-        <v>1.95</v>
-      </c>
-      <c r="AC33">
-        <v>2.83</v>
-      </c>
-      <c r="AD33">
-        <v>1.33</v>
-      </c>
-      <c r="AE33">
-        <v>1.09</v>
-      </c>
-      <c r="AF33">
-        <v>1.66</v>
-      </c>
-      <c r="AG33">
-        <v>2.06</v>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,49 +5854,49 @@
         <v>3.6</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q34">
-        <v>4.13</v>
+        <v>4.18</v>
       </c>
       <c r="R34">
         <v>2.17</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T34">
-        <v>3.07</v>
+        <v>2.98</v>
       </c>
       <c r="U34">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z34">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA34">
+        <v>1.86</v>
+      </c>
+      <c r="AB34">
         <v>1.95</v>
       </c>
-      <c r="AB34">
-        <v>1.85</v>
-      </c>
       <c r="AC34">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="AD34">
         <v>1.28</v>
@@ -5905,10 +5905,10 @@
         <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG34">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="O35">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="P35">
-        <v>5.5</v>
+        <v>5.59</v>
       </c>
       <c r="Q35">
+        <v>2</v>
+      </c>
+      <c r="R35">
+        <v>2.16</v>
+      </c>
+      <c r="S35">
+        <v>1.38</v>
+      </c>
+      <c r="T35">
+        <v>2.77</v>
+      </c>
+      <c r="U35">
+        <v>2.81</v>
+      </c>
+      <c r="V35">
+        <v>1.37</v>
+      </c>
+      <c r="W35">
+        <v>1.04</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.27</v>
+      </c>
+      <c r="Z35">
+        <v>3.14</v>
+      </c>
+      <c r="AA35">
         <v>2.01</v>
       </c>
-      <c r="R35">
-        <v>2.34</v>
-      </c>
-      <c r="S35">
-        <v>1.29</v>
-      </c>
-      <c r="T35">
-        <v>3.3</v>
-      </c>
-      <c r="U35">
-        <v>2.52</v>
-      </c>
-      <c r="V35">
-        <v>1.52</v>
-      </c>
-      <c r="W35">
-        <v>1.1</v>
-      </c>
-      <c r="X35">
-        <v>1.03</v>
-      </c>
-      <c r="Y35">
-        <v>1.21</v>
-      </c>
-      <c r="Z35">
-        <v>4.32</v>
-      </c>
-      <c r="AA35">
-        <v>1.66</v>
-      </c>
       <c r="AB35">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>2.65</v>
+        <v>3.28</v>
       </c>
       <c r="AD35">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG35">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="O36">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="Q36">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R36">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="S36">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="U36">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="V36">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W36">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z36">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA36">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB36">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD36">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AG36">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,43 +6340,43 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.99</v>
+        <v>3.7</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q37">
-        <v>3.88</v>
+        <v>4.08</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V37">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W37">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
         <v>1.16</v>
       </c>
       <c r="Z37">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA37">
         <v>1.66</v>
@@ -6385,19 +6385,19 @@
         <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD37">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE37">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG37">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Q38">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="R38">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S38">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="V38">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>3.42</v>
+        <v>3.74</v>
       </c>
       <c r="AA38">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB38">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC38">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="AD38">
+        <v>1.33</v>
+      </c>
+      <c r="AE38">
+        <v>1.08</v>
+      </c>
+      <c r="AF38">
+        <v>1.61</v>
+      </c>
+      <c r="AG38">
+        <v>2.18</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.27</v>
       </c>
-      <c r="AE38">
-        <v>1.06</v>
-      </c>
-      <c r="AF38">
-        <v>1.69</v>
-      </c>
-      <c r="AG38">
-        <v>2.05</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.34</v>
-      </c>
       <c r="AK38">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="O39">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="P39">
-        <v>4.74</v>
+        <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>2.22</v>
+        <v>2.9</v>
       </c>
       <c r="R39">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="U39">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V39">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
         <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
         <v>3.3</v>
       </c>
       <c r="AA39">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AB39">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC39">
-        <v>2.71</v>
+        <v>3.37</v>
       </c>
       <c r="AD39">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK39">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P40">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="Q40">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="R40">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="U40">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="V40">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W40">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z40">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AA40">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AC40">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD40">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK40">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O41">
         <v>3.5</v>
       </c>
       <c r="P41">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="Q41">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R41">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="S41">
+        <v>1.4</v>
+      </c>
+      <c r="T41">
+        <v>2.73</v>
+      </c>
+      <c r="U41">
+        <v>2.98</v>
+      </c>
+      <c r="V41">
+        <v>1.37</v>
+      </c>
+      <c r="W41">
+        <v>1.04</v>
+      </c>
+      <c r="X41">
+        <v>1.02</v>
+      </c>
+      <c r="Y41">
         <v>1.3</v>
       </c>
-      <c r="T41">
-        <v>3.2</v>
-      </c>
-      <c r="U41">
-        <v>2.65</v>
-      </c>
-      <c r="V41">
-        <v>1.42</v>
-      </c>
-      <c r="W41">
-        <v>1.08</v>
-      </c>
-      <c r="X41">
-        <v>1.03</v>
-      </c>
-      <c r="Y41">
-        <v>1.23</v>
-      </c>
       <c r="Z41">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA41">
         <v>1.9</v>
       </c>
       <c r="AB41">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC41">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="AD41">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE41">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AG41">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.03</v>
+        <v>1.63</v>
       </c>
       <c r="O42">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P42">
-        <v>3.3</v>
+        <v>5.07</v>
       </c>
       <c r="Q42">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="R42">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T42">
-        <v>2.86</v>
+        <v>2.99</v>
       </c>
       <c r="U42">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AA42">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB42">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC42">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="AD42">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AG42">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK42">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.57</v>
+        <v>1.85</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q43">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="R43">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U43">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="V43">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W43">
+        <v>1.04</v>
+      </c>
+      <c r="X43">
+        <v>1.01</v>
+      </c>
+      <c r="Y43">
+        <v>1.23</v>
+      </c>
+      <c r="Z43">
+        <v>3.44</v>
+      </c>
+      <c r="AA43">
+        <v>1.89</v>
+      </c>
+      <c r="AB43">
+        <v>1.89</v>
+      </c>
+      <c r="AC43">
+        <v>3.25</v>
+      </c>
+      <c r="AD43">
+        <v>1.28</v>
+      </c>
+      <c r="AE43">
         <v>1.06</v>
       </c>
-      <c r="X43">
-        <v>1.04</v>
-      </c>
-      <c r="Y43">
-        <v>1.24</v>
-      </c>
-      <c r="Z43">
-        <v>3.3</v>
-      </c>
-      <c r="AA43">
-        <v>1.91</v>
-      </c>
-      <c r="AB43">
-        <v>1.96</v>
-      </c>
-      <c r="AC43">
-        <v>3.21</v>
-      </c>
-      <c r="AD43">
-        <v>1.36</v>
-      </c>
-      <c r="AE43">
-        <v>1.14</v>
-      </c>
       <c r="AF43">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG43">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="O44">
         <v>3.4</v>
       </c>
       <c r="P44">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q44">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="R44">
         <v>2.1</v>
       </c>
       <c r="S44">
+        <v>1.38</v>
+      </c>
+      <c r="T44">
+        <v>2.81</v>
+      </c>
+      <c r="U44">
+        <v>2.73</v>
+      </c>
+      <c r="V44">
         <v>1.4</v>
       </c>
-      <c r="T44">
-        <v>2.69</v>
-      </c>
-      <c r="U44">
-        <v>2.89</v>
-      </c>
-      <c r="V44">
-        <v>1.33</v>
-      </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
+        <v>1.25</v>
+      </c>
+      <c r="Z44">
+        <v>3.3</v>
+      </c>
+      <c r="AA44">
+        <v>1.9</v>
+      </c>
+      <c r="AB44">
+        <v>1.9</v>
+      </c>
+      <c r="AC44">
+        <v>2.99</v>
+      </c>
+      <c r="AD44">
         <v>1.3</v>
       </c>
-      <c r="Z44">
-        <v>3.4</v>
-      </c>
-      <c r="AA44">
-        <v>2</v>
-      </c>
-      <c r="AB44">
-        <v>1.8</v>
-      </c>
-      <c r="AC44">
-        <v>3.3</v>
-      </c>
-      <c r="AD44">
-        <v>1.25</v>
-      </c>
       <c r="AE44">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF44">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG44">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O45">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P45">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q45">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="R45">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="S45">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T45">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="U45">
-        <v>2.73</v>
+        <v>2.39</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z45">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA45">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AB45">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="AC45">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="AD45">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AE45">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF45">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AG45">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.27</v>
       </c>
       <c r="AK45">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
+        <v>1.75</v>
+      </c>
+      <c r="O46">
+        <v>3.9</v>
+      </c>
+      <c r="P46">
+        <v>4.33</v>
+      </c>
+      <c r="Q46">
+        <v>2.29</v>
+      </c>
+      <c r="R46">
+        <v>2.23</v>
+      </c>
+      <c r="S46">
+        <v>1.31</v>
+      </c>
+      <c r="T46">
+        <v>3.15</v>
+      </c>
+      <c r="U46">
         <v>2.5</v>
       </c>
-      <c r="O46">
-        <v>3.4</v>
-      </c>
-      <c r="P46">
-        <v>2.7</v>
-      </c>
-      <c r="Q46">
-        <v>2.89</v>
-      </c>
-      <c r="R46">
-        <v>2.12</v>
-      </c>
-      <c r="S46">
-        <v>1.37</v>
-      </c>
-      <c r="T46">
-        <v>2.85</v>
-      </c>
-      <c r="U46">
-        <v>2.73</v>
-      </c>
       <c r="V46">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W46">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z46">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA46">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AB46">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AC46">
-        <v>3.05</v>
+        <v>2.61</v>
       </c>
       <c r="AD46">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE46">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG46">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>1.47</v>
+        <v>2.02</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="O47">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="P47">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="Q47">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="R47">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="S47">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="U47">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V47">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W47">
+        <v>1.05</v>
+      </c>
+      <c r="X47">
+        <v>1.01</v>
+      </c>
+      <c r="Y47">
+        <v>1.26</v>
+      </c>
+      <c r="Z47">
+        <v>3.24</v>
+      </c>
+      <c r="AA47">
+        <v>1.93</v>
+      </c>
+      <c r="AB47">
+        <v>1.84</v>
+      </c>
+      <c r="AC47">
+        <v>3.18</v>
+      </c>
+      <c r="AD47">
+        <v>1.27</v>
+      </c>
+      <c r="AE47">
         <v>1.07</v>
       </c>
-      <c r="X47">
-        <v>1.05</v>
-      </c>
-      <c r="Y47">
-        <v>1.22</v>
-      </c>
-      <c r="Z47">
-        <v>3.92</v>
-      </c>
-      <c r="AA47">
-        <v>1.72</v>
-      </c>
-      <c r="AB47">
-        <v>2.08</v>
-      </c>
-      <c r="AC47">
-        <v>2.64</v>
-      </c>
-      <c r="AD47">
-        <v>1.44</v>
-      </c>
-      <c r="AE47">
-        <v>1.11</v>
-      </c>
       <c r="AF47">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AK47">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8142,10 +8142,10 @@
         <v>3.33</v>
       </c>
       <c r="Q48">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R48">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
         <v>1.28</v>
@@ -8166,10 +8166,10 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z48">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA48">
         <v>1.66</v>
@@ -8184,13 +8184,13 @@
         <v>1.41</v>
       </c>
       <c r="AE48">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
         <v>1.58</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.74</v>
+        <v>2.32</v>
       </c>
       <c r="O49">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="P49">
-        <v>4.46</v>
+        <v>2.96</v>
       </c>
       <c r="Q49">
-        <v>2.3</v>
+        <v>3.01</v>
       </c>
       <c r="R49">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="S49">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T49">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="U49">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
         <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>4.03</v>
+        <v>3.3</v>
       </c>
       <c r="AA49">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AB49">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="AC49">
-        <v>2.76</v>
+        <v>3.24</v>
       </c>
       <c r="AD49">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE49">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG49">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>2.04</v>
+        <v>1.54</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,31 +8459,31 @@
         </is>
       </c>
       <c r="N50">
+        <v>2.15</v>
+      </c>
+      <c r="O50">
+        <v>3.2</v>
+      </c>
+      <c r="P50">
+        <v>3.5</v>
+      </c>
+      <c r="Q50">
         <v>2.6</v>
       </c>
-      <c r="O50">
-        <v>3.4</v>
-      </c>
-      <c r="P50">
-        <v>2.7</v>
-      </c>
-      <c r="Q50">
-        <v>3.14</v>
-      </c>
       <c r="R50">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T50">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="U50">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="V50">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W50">
         <v>1.03</v>
@@ -8492,31 +8492,31 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z50">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="AA50">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB50">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC50">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="AD50">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE50">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF50">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AG50">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.77</v>
+        <v>2.46</v>
       </c>
       <c r="O51">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="R51">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T51">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="U51">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
         <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z51">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA51">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB51">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC51">
-        <v>2.86</v>
+        <v>3.27</v>
       </c>
       <c r="AD51">
         <v>1.3</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK51">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="O52">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q52">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="R52">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S52">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T52">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="U52">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V52">
         <v>1.45</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AA52">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
         <v>2</v>
       </c>
       <c r="AC52">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="AD52">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG52">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK52">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="Q53">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="R53">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S53">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T53">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U53">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="V53">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z53">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AA53">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB53">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AC53">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AD53">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE53">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG53">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="O55">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P55">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="Q55">
-        <v>4.08</v>
+        <v>4.25</v>
       </c>
       <c r="R55">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="S55">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="T55">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="U55">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="V55">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W55">
         <v>1.01</v>
       </c>
       <c r="X55">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="Z55">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="AA55">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="AB55">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AC55">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD55">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE55">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF55">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AG55">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AK55">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL55">
         <v>0</v>

--- a/jogos_2026-09-01.xlsx
+++ b/jogos_2026-09-01.xlsx
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2897,23 +2897,23 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "54", "79", "90+2"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -3232,118 +3232,118 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O18">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q18">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="R18">
-        <v>2.67</v>
+        <v>2.95</v>
       </c>
       <c r="S18">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="T18">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="U18">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="V18">
+        <v>2.36</v>
+      </c>
+      <c r="W18">
+        <v>1.44</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1.03</v>
+      </c>
+      <c r="Z18">
+        <v>13</v>
+      </c>
+      <c r="AA18">
+        <v>1.14</v>
+      </c>
+      <c r="AB18">
+        <v>5</v>
+      </c>
+      <c r="AC18">
+        <v>1.33</v>
+      </c>
+      <c r="AD18">
+        <v>2.81</v>
+      </c>
+      <c r="AE18">
+        <v>1.9</v>
+      </c>
+      <c r="AF18">
+        <v>1.14</v>
+      </c>
+      <c r="AG18">
+        <v>4.9</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>["90+6"]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>["90+2"]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.18</v>
+      </c>
+      <c r="AK18">
+        <v>1.47</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>4</v>
+      </c>
+      <c r="AN18">
+        <v>4</v>
+      </c>
+      <c r="AO18">
+        <v>20</v>
+      </c>
+      <c r="AP18">
+        <v>18</v>
+      </c>
+      <c r="AQ18">
         <v>2.2</v>
       </c>
-      <c r="W18">
-        <v>1.36</v>
-      </c>
-      <c r="X18">
-        <v>1</v>
-      </c>
-      <c r="Y18">
-        <v>1.01</v>
-      </c>
-      <c r="Z18">
-        <v>11</v>
-      </c>
-      <c r="AA18">
-        <v>1.13</v>
-      </c>
-      <c r="AB18">
-        <v>3.2</v>
-      </c>
-      <c r="AC18">
-        <v>1.4</v>
-      </c>
-      <c r="AD18">
-        <v>2.14</v>
-      </c>
-      <c r="AE18">
-        <v>1.52</v>
-      </c>
-      <c r="AF18">
-        <v>1.18</v>
-      </c>
-      <c r="AG18">
-        <v>2.8</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.19</v>
-      </c>
-      <c r="AK18">
-        <v>1.39</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>-1</v>
-      </c>
-      <c r="AN18">
-        <v>-1</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>-1</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3398,11 +3398,11 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54", "68", "84"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -3558,14 +3558,14 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "72", "90"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,26 +3872,26 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "60"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "44"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,26 +4035,26 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "90+2"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,26 +4198,26 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "23", "86"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,26 +4361,26 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "86"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "32", "55", "73"]</t>
         </is>
       </c>
       <c r="AJ25">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -4536,14 +4536,14 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "54", "88"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4678,19 +4678,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -4699,118 +4699,118 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q27">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="R27">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T27">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="U27">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>4.64</v>
       </c>
       <c r="AA27">
-        <v>1.97</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="AC27">
-        <v>3.08</v>
+        <v>2.42</v>
       </c>
       <c r="AD27">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
+        <v>2.11</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>["83", "90"]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>["71"]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.19</v>
+      </c>
+      <c r="AK27">
+        <v>2.29</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>7</v>
+      </c>
+      <c r="AN27">
         <v>2</v>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.28</v>
-      </c>
-      <c r="AK27">
-        <v>1.62</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>31</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4841,139 +4841,139 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="Q28">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R28">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="U28">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z28">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AA28">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB28">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AG28">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "65", "86"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "73"]</t>
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK28">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5004,63 +5004,63 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O29">
         <v>3.4</v>
       </c>
       <c r="P29">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q29">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S29">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T29">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U29">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="V29">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
         <v>1.05</v>
@@ -5069,74 +5069,74 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z29">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AA29">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB29">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC29">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="AD29">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
         <v>1.7</v>
       </c>
       <c r="AG29">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
+          <t>["33", "43", "80"]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5167,139 +5167,139 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.47</v>
+        <v>2.06</v>
       </c>
       <c r="Q30">
-        <v>2.41</v>
+        <v>3.9</v>
       </c>
       <c r="R30">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
+        <v>1.34</v>
+      </c>
+      <c r="T30">
+        <v>2.95</v>
+      </c>
+      <c r="U30">
+        <v>2.69</v>
+      </c>
+      <c r="V30">
+        <v>1.4</v>
+      </c>
+      <c r="W30">
+        <v>1.05</v>
+      </c>
+      <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.24</v>
+      </c>
+      <c r="Z30">
+        <v>3.34</v>
+      </c>
+      <c r="AA30">
+        <v>1.88</v>
+      </c>
+      <c r="AB30">
+        <v>1.87</v>
+      </c>
+      <c r="AC30">
+        <v>3.08</v>
+      </c>
+      <c r="AD30">
+        <v>1.28</v>
+      </c>
+      <c r="AE30">
+        <v>1.07</v>
+      </c>
+      <c r="AF30">
+        <v>1.71</v>
+      </c>
+      <c r="AG30">
+        <v>2.02</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>["13", "71", "90+4"]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>["2"]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.27</v>
+      </c>
+      <c r="AK30">
         <v>1.3</v>
       </c>
-      <c r="T30">
-        <v>3.16</v>
-      </c>
-      <c r="U30">
-        <v>2.54</v>
-      </c>
-      <c r="V30">
-        <v>1.44</v>
-      </c>
-      <c r="W30">
-        <v>1.06</v>
-      </c>
-      <c r="X30">
-        <v>1.03</v>
-      </c>
-      <c r="Y30">
-        <v>1.19</v>
-      </c>
-      <c r="Z30">
-        <v>3.8</v>
-      </c>
-      <c r="AA30">
-        <v>1.72</v>
-      </c>
-      <c r="AB30">
-        <v>2.07</v>
-      </c>
-      <c r="AC30">
-        <v>2.83</v>
-      </c>
-      <c r="AD30">
-        <v>1.33</v>
-      </c>
-      <c r="AE30">
-        <v>1.09</v>
-      </c>
-      <c r="AF30">
-        <v>1.65</v>
-      </c>
-      <c r="AG30">
-        <v>2.11</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.25</v>
-      </c>
-      <c r="AK30">
-        <v>1.83</v>
-      </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5330,139 +5330,139 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O31">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>4.6</v>
+        <v>3.47</v>
       </c>
       <c r="Q31">
+        <v>2.41</v>
+      </c>
+      <c r="R31">
+        <v>2.23</v>
+      </c>
+      <c r="S31">
+        <v>1.3</v>
+      </c>
+      <c r="T31">
+        <v>3.16</v>
+      </c>
+      <c r="U31">
+        <v>2.54</v>
+      </c>
+      <c r="V31">
+        <v>1.44</v>
+      </c>
+      <c r="W31">
+        <v>1.06</v>
+      </c>
+      <c r="X31">
+        <v>1.03</v>
+      </c>
+      <c r="Y31">
+        <v>1.19</v>
+      </c>
+      <c r="Z31">
+        <v>3.8</v>
+      </c>
+      <c r="AA31">
+        <v>1.72</v>
+      </c>
+      <c r="AB31">
         <v>2.07</v>
       </c>
-      <c r="R31">
-        <v>2.36</v>
-      </c>
-      <c r="S31">
-        <v>1.28</v>
-      </c>
-      <c r="T31">
-        <v>3.6</v>
-      </c>
-      <c r="U31">
-        <v>2.44</v>
-      </c>
-      <c r="V31">
-        <v>1.55</v>
-      </c>
-      <c r="W31">
-        <v>1.1</v>
-      </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
-        <v>1.15</v>
-      </c>
-      <c r="Z31">
-        <v>4.64</v>
-      </c>
-      <c r="AA31">
-        <v>1.62</v>
-      </c>
-      <c r="AB31">
-        <v>2.24</v>
-      </c>
       <c r="AC31">
-        <v>2.42</v>
+        <v>2.83</v>
       </c>
       <c r="AD31">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG31">
         <v>2.11</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
+          <t>["27", "90+3"]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ31">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5493,139 +5493,139 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="Q32">
-        <v>4.2</v>
+        <v>2.94</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T32">
-        <v>3.12</v>
+        <v>2.81</v>
       </c>
       <c r="U32">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="Z32">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AA32">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC32">
-        <v>2.83</v>
+        <v>3.45</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45"]</t>
         </is>
       </c>
       <c r="AJ32">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5656,139 +5656,139 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>2.93</v>
+        <v>2</v>
       </c>
       <c r="Q33">
-        <v>2.82</v>
+        <v>4.18</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S33">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T33">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="U33">
-        <v>2.95</v>
+        <v>2.66</v>
       </c>
       <c r="V33">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W33">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="Z33">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="AA33">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AB33">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD33">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF33">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG33">
         <v>1.92</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+7", "60"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "38"]</t>
         </is>
       </c>
       <c r="AJ33">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="AL33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5819,139 +5819,139 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
+        <v>3.3</v>
+      </c>
+      <c r="P34">
+        <v>2.93</v>
+      </c>
+      <c r="Q34">
+        <v>2.82</v>
+      </c>
+      <c r="R34">
+        <v>2.05</v>
+      </c>
+      <c r="S34">
+        <v>1.38</v>
+      </c>
+      <c r="T34">
+        <v>2.77</v>
+      </c>
+      <c r="U34">
+        <v>2.95</v>
+      </c>
+      <c r="V34">
+        <v>1.34</v>
+      </c>
+      <c r="W34">
+        <v>1.02</v>
+      </c>
+      <c r="X34">
+        <v>1.04</v>
+      </c>
+      <c r="Y34">
+        <v>1.34</v>
+      </c>
+      <c r="Z34">
+        <v>3.24</v>
+      </c>
+      <c r="AA34">
+        <v>2.04</v>
+      </c>
+      <c r="AB34">
+        <v>1.72</v>
+      </c>
+      <c r="AC34">
         <v>3.5</v>
       </c>
-      <c r="P34">
-        <v>2</v>
-      </c>
-      <c r="Q34">
-        <v>4.18</v>
-      </c>
-      <c r="R34">
-        <v>2.17</v>
-      </c>
-      <c r="S34">
-        <v>1.37</v>
-      </c>
-      <c r="T34">
-        <v>2.98</v>
-      </c>
-      <c r="U34">
-        <v>2.66</v>
-      </c>
-      <c r="V34">
-        <v>1.41</v>
-      </c>
-      <c r="W34">
-        <v>1.07</v>
-      </c>
-      <c r="X34">
+      <c r="AD34">
+        <v>1.22</v>
+      </c>
+      <c r="AE34">
         <v>1.03</v>
       </c>
-      <c r="Y34">
-        <v>1.23</v>
-      </c>
-      <c r="Z34">
-        <v>3.42</v>
-      </c>
-      <c r="AA34">
-        <v>1.86</v>
-      </c>
-      <c r="AB34">
-        <v>1.95</v>
-      </c>
-      <c r="AC34">
-        <v>3.05</v>
-      </c>
-      <c r="AD34">
-        <v>1.28</v>
-      </c>
-      <c r="AE34">
-        <v>1.07</v>
-      </c>
       <c r="AF34">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AG34">
         <v>1.92</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "87"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84", "90+6"]</t>
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -6006,11 +6006,11 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AJ35">
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6154,13 +6154,13 @@
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -6169,11 +6169,11 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AJ36">
@@ -6256,28 +6256,28 @@
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6317,10 +6317,10 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -6329,14 +6329,14 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60"]</t>
         </is>
       </c>
       <c r="AJ37">
@@ -6419,28 +6419,28 @@
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6480,26 +6480,26 @@
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "90+2"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "57"]</t>
         </is>
       </c>
       <c r="AJ38">
@@ -6582,28 +6582,28 @@
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
@@ -6745,28 +6745,28 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6806,26 +6806,26 @@
         </is>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "42", "53", "64"]</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "69"]</t>
         </is>
       </c>
       <c r="AJ40">
@@ -6908,28 +6908,28 @@
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6972,23 +6972,23 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "62"]</t>
         </is>
       </c>
       <c r="AJ41">
@@ -7071,28 +7071,28 @@
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7132,26 +7132,26 @@
         </is>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "68", "90+3"]</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "67"]</t>
         </is>
       </c>
       <c r="AJ42">
@@ -7234,28 +7234,28 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7295,13 +7295,13 @@
         </is>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "29"]</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
@@ -7397,28 +7397,28 @@
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7458,26 +7458,26 @@
         </is>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "79", "86"]</t>
         </is>
       </c>
       <c r="AJ44">
@@ -7560,28 +7560,28 @@
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7612,22 +7612,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -7636,115 +7636,115 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="O45">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="P45">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q45">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R45">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="S45">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T45">
-        <v>3.28</v>
+        <v>2.81</v>
       </c>
       <c r="U45">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="V45">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="W45">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="Z45">
-        <v>4.25</v>
+        <v>3.24</v>
       </c>
       <c r="AA45">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AB45">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="AC45">
-        <v>2.61</v>
+        <v>3.18</v>
       </c>
       <c r="AD45">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AE45">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF45">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AG45">
-        <v>2.39</v>
+        <v>2.02</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36"]</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64"]</t>
         </is>
       </c>
       <c r="AJ45">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL45">
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7775,22 +7775,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -7803,38 +7803,38 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="O46">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P46">
-        <v>4.33</v>
+        <v>3.33</v>
       </c>
       <c r="Q46">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="R46">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T46">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V46">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
         <v>1.01</v>
@@ -7843,32 +7843,32 @@
         <v>1.16</v>
       </c>
       <c r="Z46">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA46">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB46">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AC46">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="AD46">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE46">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG46">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3", "45+5"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
@@ -7880,34 +7880,34 @@
         <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AL46">
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,23 +7966,23 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="O47">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="P47">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="Q47">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="R47">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="S47">
         <v>1.38</v>
@@ -7991,43 +7991,43 @@
         <v>2.81</v>
       </c>
       <c r="U47">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="V47">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA47">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AB47">
         <v>1.84</v>
       </c>
       <c r="AC47">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="AD47">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE47">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF47">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG47">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,37 +8040,37 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK47">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL47">
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8101,96 +8101,96 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
-        <v>1.94</v>
+        <v>2.46</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>3.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q48">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="S48">
+        <v>1.38</v>
+      </c>
+      <c r="T48">
+        <v>2.81</v>
+      </c>
+      <c r="U48">
+        <v>2.75</v>
+      </c>
+      <c r="V48">
+        <v>1.4</v>
+      </c>
+      <c r="W48">
+        <v>1.06</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
         <v>1.28</v>
       </c>
-      <c r="T48">
+      <c r="Z48">
         <v>3.3</v>
       </c>
-      <c r="U48">
-        <v>2.41</v>
-      </c>
-      <c r="V48">
-        <v>1.5</v>
-      </c>
-      <c r="W48">
+      <c r="AA48">
+        <v>1.89</v>
+      </c>
+      <c r="AB48">
+        <v>1.88</v>
+      </c>
+      <c r="AC48">
+        <v>3.27</v>
+      </c>
+      <c r="AD48">
+        <v>1.3</v>
+      </c>
+      <c r="AE48">
         <v>1.08</v>
       </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>1.16</v>
-      </c>
-      <c r="Z48">
-        <v>4.15</v>
-      </c>
-      <c r="AA48">
-        <v>1.66</v>
-      </c>
-      <c r="AB48">
-        <v>2.18</v>
-      </c>
-      <c r="AC48">
-        <v>2.54</v>
-      </c>
-      <c r="AD48">
-        <v>1.41</v>
-      </c>
-      <c r="AE48">
-        <v>1.13</v>
-      </c>
       <c r="AF48">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG48">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8199,41 +8199,41 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "46", "51", "66", "90+1"]</t>
         </is>
       </c>
       <c r="AJ48">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK48">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="AL48">
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN48">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO48">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP48">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8264,19 +8264,19 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -8285,118 +8285,118 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N49">
-        <v>2.32</v>
+        <v>1.75</v>
       </c>
       <c r="O49">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="P49">
-        <v>2.96</v>
+        <v>4.33</v>
       </c>
       <c r="Q49">
-        <v>3.01</v>
+        <v>2.29</v>
       </c>
       <c r="R49">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="S49">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="U49">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="V49">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="W49">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z49">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA49">
-        <v>2.01</v>
+        <v>1.69</v>
       </c>
       <c r="AB49">
-        <v>1.84</v>
+        <v>2.13</v>
       </c>
       <c r="AC49">
-        <v>3.24</v>
+        <v>2.61</v>
       </c>
       <c r="AD49">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF49">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG49">
+        <v>2.1</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>["56", "74", "77"]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>["70"]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.24</v>
+      </c>
+      <c r="AK49">
+        <v>2.02</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>11</v>
+      </c>
+      <c r="AN49">
         <v>2</v>
       </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.3</v>
-      </c>
-      <c r="AK49">
-        <v>1.54</v>
-      </c>
-      <c r="AL49">
-        <v>0</v>
-      </c>
-      <c r="AM49">
-        <v>-1</v>
-      </c>
-      <c r="AN49">
-        <v>-1</v>
-      </c>
       <c r="AO49">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP49">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AR49">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS49">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT49">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -8448,14 +8448,14 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N50">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "88"]</t>
         </is>
       </c>
       <c r="AJ50">
@@ -8538,28 +8538,28 @@
         <v>0</v>
       </c>
       <c r="AM50">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN50">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO50">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP50">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AR50">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS50">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT50">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
@@ -8590,25 +8590,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -8618,111 +8618,111 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N51">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q51">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R51">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>2.81</v>
+        <v>3.28</v>
       </c>
       <c r="U51">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="V51">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z51">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA51">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AB51">
-        <v>1.88</v>
+        <v>2.21</v>
       </c>
       <c r="AC51">
-        <v>3.27</v>
+        <v>2.61</v>
       </c>
       <c r="AD51">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AG51">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6"]</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "45+8"]</t>
         </is>
       </c>
       <c r="AJ51">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK51">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN51">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO51">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP51">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
@@ -8762,13 +8762,13 @@
         </is>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>0</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N52">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
@@ -8864,28 +8864,28 @@
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN52">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO52">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP52">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
@@ -8925,26 +8925,26 @@
         </is>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N53">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55"]</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3"]</t>
         </is>
       </c>
       <c r="AJ53">
@@ -9027,28 +9027,28 @@
         <v>0</v>
       </c>
       <c r="AM53">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN53">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO53">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP53">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ53">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR53">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS53">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT53">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
@@ -9114,37 +9114,37 @@
         <v>1.94</v>
       </c>
       <c r="O54">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="P54">
-        <v>4.15</v>
+        <v>3.43</v>
       </c>
       <c r="Q54">
         <v>2.61</v>
       </c>
       <c r="R54">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S54">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="T54">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="U54">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="V54">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W54">
         <v>1.02</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y54">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z54">
         <v>2.59</v>
@@ -9156,19 +9156,19 @@
         <v>1.55</v>
       </c>
       <c r="AC54">
-        <v>4.51</v>
+        <v>4.3</v>
       </c>
       <c r="AD54">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE54">
         <v>1.01</v>
       </c>
       <c r="AF54">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AG54">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK54">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O56">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="P56">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q56">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="R56">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="S56">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T56">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="U56">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V56">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z56">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="AA56">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AB56">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC56">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD56">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE56">
         <v>1.06</v>
       </c>
       <c r="AF56">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AG56">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="AL56">
         <v>0</v>
